--- a/research/traditional_assets/database/data/hong_kong/hong_kong_transportation_railroads.xlsx
+++ b/research/traditional_assets/database/data/hong_kong/hong_kong_transportation_railroads.xlsx
@@ -650,10 +650,10 @@
         <v>0.05467180988949739</v>
       </c>
       <c r="X2">
-        <v>0.0799540554255937</v>
+        <v>0.07993810514498703</v>
       </c>
       <c r="Y2">
-        <v>-0.0252822455360963</v>
+        <v>-0.02526629525548964</v>
       </c>
       <c r="Z2">
         <v>0.2780285316837837</v>
@@ -662,10 +662,10 @@
         <v>0.04721819075930126</v>
       </c>
       <c r="AB2">
-        <v>0.07041486284287765</v>
+        <v>0.0704036069004771</v>
       </c>
       <c r="AC2">
-        <v>-0.02319667208357639</v>
+        <v>-0.02318541614117584</v>
       </c>
       <c r="AD2">
         <v>9057.5</v>
@@ -787,10 +787,10 @@
         <v>0.05467180988949739</v>
       </c>
       <c r="X3">
-        <v>0.0799540554255937</v>
+        <v>0.07993810514498703</v>
       </c>
       <c r="Y3">
-        <v>-0.0252822455360963</v>
+        <v>-0.02526629525548964</v>
       </c>
       <c r="Z3">
         <v>0.2780285316837837</v>
@@ -799,10 +799,10 @@
         <v>0.04721819075930126</v>
       </c>
       <c r="AB3">
-        <v>0.07041486284287765</v>
+        <v>0.0704036069004771</v>
       </c>
       <c r="AC3">
-        <v>-0.02319667208357639</v>
+        <v>-0.02318541614117584</v>
       </c>
       <c r="AD3">
         <v>9057.5</v>
@@ -1139,7 +1139,7 @@
         <v>5.76665383134386</v>
       </c>
       <c r="F2">
-        <v>9.381073691449529</v>
+        <v>9.614613757468099</v>
       </c>
       <c r="G2">
         <v>4.00508512049525</v>
@@ -1157,13 +1157,13 @@
         <v>21717.8</v>
       </c>
       <c r="L2">
-        <v>27401.2264618038</v>
+        <v>27514.8423050983</v>
       </c>
       <c r="M2">
         <v>27616.5</v>
       </c>
       <c r="N2">
-        <v>27012.2034618038</v>
+        <v>27125.8193050983</v>
       </c>
       <c r="O2">
         <v>9057.5</v>
@@ -1172,16 +1172,16 @@
         <v>2769.777</v>
       </c>
       <c r="Q2">
-        <v>0.07041486284287771</v>
+        <v>0.0704036069004771</v>
       </c>
       <c r="R2">
-        <v>0.0709655278941445</v>
+        <v>0.0708486631325204</v>
       </c>
       <c r="S2">
         <v>0.047542074913216</v>
       </c>
       <c r="T2">
-        <v>0.048126574913216</v>
+        <v>0.046957574913216</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.0799540554255937</v>
+        <v>0.079938105144987</v>
       </c>
       <c r="X2">
-        <v>0.0732243254417088</v>
+        <v>0.0732115180113527</v>
       </c>
       <c r="Y2">
         <v>0.665415210497489</v>
@@ -1236,7 +1236,7 @@
         <v>21717.8</v>
       </c>
       <c r="AK2">
-        <v>0.05132743418963755</v>
+        <v>0.05130346377183672</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.07113232112059591</v>
+        <v>0.07112049067688267</v>
       </c>
       <c r="C2">
-        <v>29993.14954358181</v>
+        <v>29993.41069683655</v>
       </c>
       <c r="D2">
-        <v>26834.34954358181</v>
+        <v>26834.61069683655</v>
       </c>
       <c r="E2">
         <v>-9057.5</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.07113232112059591</v>
+        <v>0.07112049067688267</v>
       </c>
       <c r="T2">
         <v>0.4935434922969562</v>
       </c>
       <c r="U2">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V2">
         <v>0.165</v>
       </c>
       <c r="W2">
-        <v>0.04812657491321597</v>
+        <v>0.04695757491321597</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.07111378853987908</v>
+        <v>0.07109028761639796</v>
       </c>
       <c r="C3">
-        <v>29705.04234840144</v>
+        <v>29717.70507337309</v>
       </c>
       <c r="D3">
-        <v>26853.99534840144</v>
+        <v>26866.6580733731</v>
       </c>
       <c r="E3">
         <v>-8749.746999999999</v>
@@ -1539,37 +1539,37 @@
         <v>1497.6</v>
       </c>
       <c r="M3">
-        <v>17.73784168774485</v>
+        <v>17.30698748774486</v>
       </c>
       <c r="N3">
-        <v>1479.862158312255</v>
+        <v>1480.293012512255</v>
       </c>
       <c r="O3">
-        <v>244.1772561215221</v>
+        <v>244.2483470645221</v>
       </c>
       <c r="P3">
-        <v>1235.684902190733</v>
+        <v>1236.044665447733</v>
       </c>
       <c r="Q3">
-        <v>1999.584902190733</v>
+        <v>1999.944665447733</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.07134598261691609</v>
+        <v>0.07133405239117759</v>
       </c>
       <c r="T3">
         <v>0.4977062076107739</v>
       </c>
       <c r="U3">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V3">
         <v>0.165</v>
       </c>
       <c r="W3">
-        <v>0.04812657491321597</v>
+        <v>0.04695757491321597</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>84.42966322304578</v>
+        <v>86.53152381721291</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.07109525595916226</v>
+        <v>0.07106008455591327</v>
       </c>
       <c r="C4">
-        <v>29416.96394023664</v>
+        <v>29442.07608693352</v>
       </c>
       <c r="D4">
-        <v>26873.66994023664</v>
+        <v>26898.78208693352</v>
       </c>
       <c r="E4">
         <v>-8441.994000000001</v>
@@ -1621,37 +1621,37 @@
         <v>1497.6</v>
       </c>
       <c r="M4">
-        <v>35.47568337548971</v>
+        <v>34.61397497548971</v>
       </c>
       <c r="N4">
-        <v>1462.12431662451</v>
+        <v>1462.98602502451</v>
       </c>
       <c r="O4">
-        <v>241.2505122430442</v>
+        <v>241.3926941290442</v>
       </c>
       <c r="P4">
-        <v>1220.873804381466</v>
+        <v>1221.593330895466</v>
       </c>
       <c r="Q4">
-        <v>1984.773804381466</v>
+        <v>1985.493330895466</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.07156400455193668</v>
+        <v>0.07155197250780505</v>
       </c>
       <c r="T4">
         <v>0.501953876298343</v>
       </c>
       <c r="U4">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V4">
         <v>0.165</v>
       </c>
       <c r="W4">
-        <v>0.04812657491321597</v>
+        <v>0.04695757491321597</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>42.21483161152288</v>
+        <v>43.26576190860646</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.07107672337844544</v>
+        <v>0.07102988149542858</v>
       </c>
       <c r="C5">
-        <v>29128.91438240627</v>
+        <v>29166.52401274776</v>
       </c>
       <c r="D5">
-        <v>26893.37338240627</v>
+        <v>26930.98301274775</v>
       </c>
       <c r="E5">
         <v>-8134.241</v>
@@ -1703,37 +1703,37 @@
         <v>1497.6</v>
       </c>
       <c r="M5">
-        <v>53.21352506323456</v>
+        <v>51.92096246323457</v>
       </c>
       <c r="N5">
-        <v>1444.386474936765</v>
+        <v>1445.679037536765</v>
       </c>
       <c r="O5">
-        <v>238.3237683645663</v>
+        <v>238.5370411935663</v>
       </c>
       <c r="P5">
-        <v>1206.062706572199</v>
+        <v>1207.141996343199</v>
       </c>
       <c r="Q5">
-        <v>1969.962706572199</v>
+        <v>1971.041996343199</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.07178652178458655</v>
+        <v>0.0717743858227135</v>
       </c>
       <c r="T5">
         <v>0.5062891257835941</v>
       </c>
       <c r="U5">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V5">
         <v>0.165</v>
       </c>
       <c r="W5">
-        <v>0.04812657491321597</v>
+        <v>0.04695757491321597</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>28.14322107434859</v>
+        <v>28.8438412724043</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.07105819079772863</v>
+        <v>0.07099967843494387</v>
       </c>
       <c r="C6">
-        <v>28840.89373841498</v>
+        <v>28891.04912736523</v>
       </c>
       <c r="D6">
-        <v>26913.10573841498</v>
+        <v>26963.26112736523</v>
       </c>
       <c r="E6">
         <v>-7826.488</v>
@@ -1785,37 +1785,37 @@
         <v>1497.6</v>
       </c>
       <c r="M6">
-        <v>70.95136675097942</v>
+        <v>69.22794995097942</v>
       </c>
       <c r="N6">
-        <v>1426.648633249021</v>
+        <v>1428.372050049021</v>
       </c>
       <c r="O6">
-        <v>235.3970244860884</v>
+        <v>235.6813882580884</v>
       </c>
       <c r="P6">
-        <v>1191.251608762932</v>
+        <v>1192.690661790932</v>
       </c>
       <c r="Q6">
-        <v>1955.151608762932</v>
+        <v>1956.590661790932</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.07201367479291665</v>
+        <v>0.07200143274834921</v>
       </c>
       <c r="T6">
         <v>0.5107146929664544</v>
       </c>
       <c r="U6">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V6">
         <v>0.165</v>
       </c>
       <c r="W6">
-        <v>0.04812657491321597</v>
+        <v>0.04695757491321597</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>21.10741580576144</v>
+        <v>21.63288095430323</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.07103965821701179</v>
+        <v>0.07096947537445919</v>
       </c>
       <c r="C7">
-        <v>28552.90207195403</v>
+        <v>28615.65170866274</v>
       </c>
       <c r="D7">
-        <v>26932.86707195403</v>
+        <v>26995.61670866274</v>
       </c>
       <c r="E7">
         <v>-7518.735</v>
@@ -1867,37 +1867,37 @@
         <v>1497.6</v>
       </c>
       <c r="M7">
-        <v>88.68920843872429</v>
+        <v>86.53493743872428</v>
       </c>
       <c r="N7">
-        <v>1408.910791561276</v>
+        <v>1411.065062561276</v>
       </c>
       <c r="O7">
-        <v>232.4702806076105</v>
+        <v>232.8257353226105</v>
       </c>
       <c r="P7">
-        <v>1176.440510953665</v>
+        <v>1178.239327238665</v>
       </c>
       <c r="Q7">
-        <v>1940.340510953665</v>
+        <v>1942.139327238665</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.07224560996984315</v>
+        <v>0.07223325960926147</v>
       </c>
       <c r="T7">
         <v>0.5152334299847435</v>
       </c>
       <c r="U7">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V7">
         <v>0.165</v>
       </c>
       <c r="W7">
-        <v>0.04812657491321597</v>
+        <v>0.04695757491321597</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>16.88593264460915</v>
+        <v>17.30630476344258</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.07102112563629498</v>
+        <v>0.07093927231397448</v>
       </c>
       <c r="C8">
-        <v>28264.93944690176</v>
+        <v>28340.33203585259</v>
       </c>
       <c r="D8">
-        <v>26952.65744690176</v>
+        <v>27028.05003585259</v>
       </c>
       <c r="E8">
         <v>-7210.982</v>
@@ -1949,37 +1949,37 @@
         <v>1497.6</v>
       </c>
       <c r="M8">
-        <v>106.4270501264691</v>
+        <v>103.8419249264691</v>
       </c>
       <c r="N8">
-        <v>1391.172949873531</v>
+        <v>1393.758075073531</v>
       </c>
       <c r="O8">
-        <v>229.5435367291326</v>
+        <v>229.9700823871326</v>
       </c>
       <c r="P8">
-        <v>1161.629413144398</v>
+        <v>1163.787992686398</v>
       </c>
       <c r="Q8">
-        <v>1925.529413144398</v>
+        <v>1927.687992686398</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.0724824799377681</v>
+        <v>0.07247001895657609</v>
       </c>
       <c r="T8">
         <v>0.5198483103438472</v>
       </c>
       <c r="U8">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V8">
         <v>0.165</v>
       </c>
       <c r="W8">
-        <v>0.04812657491321597</v>
+        <v>0.04695757491321597</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>14.0716105371743</v>
+        <v>14.42192063620215</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.07100259305557814</v>
+        <v>0.07090906925348978</v>
       </c>
       <c r="C9">
-        <v>27977.00592732452</v>
+        <v>28065.0903894904</v>
       </c>
       <c r="D9">
-        <v>26972.47692732452</v>
+        <v>27060.5613894904</v>
       </c>
       <c r="E9">
         <v>-6903.228999999999</v>
@@ -2031,37 +2031,37 @@
         <v>1497.6</v>
       </c>
       <c r="M9">
-        <v>124.164891814214</v>
+        <v>121.148912414214</v>
       </c>
       <c r="N9">
-        <v>1373.435108185786</v>
+        <v>1376.451087585786</v>
       </c>
       <c r="O9">
-        <v>226.6167928506547</v>
+        <v>227.1144294516547</v>
       </c>
       <c r="P9">
-        <v>1146.818315335131</v>
+        <v>1149.336658134131</v>
       </c>
       <c r="Q9">
-        <v>1910.718315335131</v>
+        <v>1913.236658134131</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.07272444388349789</v>
+        <v>0.07271186990275771</v>
       </c>
       <c r="T9">
         <v>0.5245624354418563</v>
       </c>
       <c r="U9">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V9">
         <v>0.165</v>
       </c>
       <c r="W9">
-        <v>0.04812657491321597</v>
+        <v>0.04695757491321597</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>12.06138046043511</v>
+        <v>12.36164625960184</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.07098406047486133</v>
+        <v>0.0708788661930051</v>
       </c>
       <c r="C10">
-        <v>27689.10157747714</v>
+        <v>27789.92705148333</v>
       </c>
       <c r="D10">
-        <v>26992.32557747714</v>
+        <v>27093.15105148334</v>
       </c>
       <c r="E10">
         <v>-6595.476000000001</v>
@@ -2113,37 +2113,37 @@
         <v>1497.6</v>
       </c>
       <c r="M10">
-        <v>141.9027335019588</v>
+        <v>138.4558999019588</v>
       </c>
       <c r="N10">
-        <v>1355.697266498041</v>
+        <v>1359.144100098041</v>
       </c>
       <c r="O10">
-        <v>223.6900489721768</v>
+        <v>224.2587765161768</v>
       </c>
       <c r="P10">
-        <v>1132.007217525864</v>
+        <v>1134.885323581864</v>
       </c>
       <c r="Q10">
-        <v>1895.907217525864</v>
+        <v>1898.785323581864</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.0729716679150044</v>
+        <v>0.07295897847820415</v>
       </c>
       <c r="T10">
         <v>0.5293790415202568</v>
       </c>
       <c r="U10">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V10">
         <v>0.165</v>
       </c>
       <c r="W10">
-        <v>0.04812657491321597</v>
+        <v>0.04695757491321597</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>10.55370790288072</v>
+        <v>10.81644047715161</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.0709655278941445</v>
+        <v>0.07084866313252039</v>
       </c>
       <c r="C11">
-        <v>27401.22646180382</v>
+        <v>27514.84230509831</v>
       </c>
       <c r="D11">
-        <v>27012.20346180382</v>
+        <v>27125.81930509831</v>
       </c>
       <c r="E11">
         <v>-6287.723</v>
@@ -2195,37 +2195,37 @@
         <v>1497.6</v>
       </c>
       <c r="M11">
-        <v>159.6405751897037</v>
+        <v>155.7628873897037</v>
       </c>
       <c r="N11">
-        <v>1337.959424810296</v>
+        <v>1341.837112610296</v>
       </c>
       <c r="O11">
-        <v>220.7633050936989</v>
+        <v>221.4031235806989</v>
       </c>
       <c r="P11">
-        <v>1117.196119716597</v>
+        <v>1120.433989029597</v>
       </c>
       <c r="Q11">
-        <v>1881.096119716598</v>
+        <v>1884.333989029597</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.07322432544170884</v>
+        <v>0.0732115180113527</v>
       </c>
       <c r="T11">
         <v>0.534301507072908</v>
       </c>
       <c r="U11">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V11">
         <v>0.165</v>
       </c>
       <c r="W11">
-        <v>0.04812657491321597</v>
+        <v>0.04695757491321597</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>9.381073691449529</v>
+        <v>9.614613757468101</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.07103884531342766</v>
+        <v>0.0709437100720357</v>
       </c>
       <c r="C12">
-        <v>27015.00453731949</v>
+        <v>27104.54969978913</v>
       </c>
       <c r="D12">
-        <v>26933.73453731949</v>
+        <v>27023.27969978913</v>
       </c>
       <c r="E12">
         <v>-5979.969999999999</v>
@@ -2277,37 +2277,37 @@
         <v>1497.6</v>
       </c>
       <c r="M12">
-        <v>180.7636998774486</v>
+        <v>177.6861698774486</v>
       </c>
       <c r="N12">
-        <v>1316.836300122551</v>
+        <v>1319.913830122551</v>
       </c>
       <c r="O12">
-        <v>217.277989520221</v>
+        <v>217.785781970221</v>
       </c>
       <c r="P12">
-        <v>1099.55831060233</v>
+        <v>1102.12804815233</v>
       </c>
       <c r="Q12">
-        <v>1863.458310602331</v>
+        <v>1866.02804815233</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.07348259758011785</v>
+        <v>0.07346966953412679</v>
       </c>
       <c r="T12">
         <v>0.5393333607489516</v>
       </c>
       <c r="U12">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V12">
         <v>0.165</v>
       </c>
       <c r="W12">
-        <v>0.04904507491321597</v>
+        <v>0.04821007491321597</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>8.28484923142932</v>
+        <v>8.428343078321209</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.07102949773271085</v>
+        <v>0.070926032011551</v>
       </c>
       <c r="C13">
-        <v>26717.23054127193</v>
+        <v>26815.80961726087</v>
       </c>
       <c r="D13">
-        <v>26943.71354127193</v>
+        <v>27042.29261726087</v>
       </c>
       <c r="E13">
         <v>-5672.217000000001</v>
@@ -2359,37 +2359,37 @@
         <v>1497.6</v>
       </c>
       <c r="M13">
-        <v>198.8400698651934</v>
+        <v>195.4547868651934</v>
       </c>
       <c r="N13">
-        <v>1298.759930134806</v>
+        <v>1302.145213134806</v>
       </c>
       <c r="O13">
-        <v>214.2953884722431</v>
+        <v>214.8539601672431</v>
       </c>
       <c r="P13">
-        <v>1084.464541662563</v>
+        <v>1087.291252967563</v>
       </c>
       <c r="Q13">
-        <v>1848.364541662563</v>
+        <v>1851.191252967563</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.07374667358680571</v>
+        <v>0.07373362221471601</v>
       </c>
       <c r="T13">
         <v>0.5444782897885015</v>
       </c>
       <c r="U13">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V13">
         <v>0.165</v>
       </c>
       <c r="W13">
-        <v>0.04904507491321597</v>
+        <v>0.04821007491321597</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>7.531681119481199</v>
+        <v>7.662130071201099</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.07102015015199402</v>
+        <v>0.0709083539510663</v>
       </c>
       <c r="C14">
-        <v>26419.46394244798</v>
+        <v>26527.09630761511</v>
       </c>
       <c r="D14">
-        <v>26953.69994244798</v>
+        <v>27061.33230761511</v>
       </c>
       <c r="E14">
         <v>-5364.464</v>
@@ -2441,37 +2441,37 @@
         <v>1497.6</v>
       </c>
       <c r="M14">
-        <v>216.9164398529383</v>
+        <v>213.2234038529382</v>
       </c>
       <c r="N14">
-        <v>1280.683560147062</v>
+        <v>1284.376596147062</v>
       </c>
       <c r="O14">
-        <v>211.3127874242652</v>
+        <v>211.9221383642652</v>
       </c>
       <c r="P14">
-        <v>1069.370772722796</v>
+        <v>1072.454457782796</v>
       </c>
       <c r="Q14">
-        <v>1833.270772722796</v>
+        <v>1836.354457782797</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.0740167513209183</v>
+        <v>0.07400357381986408</v>
       </c>
       <c r="T14">
         <v>0.5497401490334959</v>
       </c>
       <c r="U14">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V14">
         <v>0.165</v>
       </c>
       <c r="W14">
-        <v>0.04904507491321597</v>
+        <v>0.04821007491321597</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>6.9040410261911</v>
+        <v>7.023619231934341</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.0712496125712772</v>
+        <v>0.07107521089058159</v>
       </c>
       <c r="C15">
-        <v>25868.68715652178</v>
+        <v>26040.69510137056</v>
       </c>
       <c r="D15">
-        <v>26710.67615652178</v>
+        <v>26882.68410137056</v>
       </c>
       <c r="E15">
         <v>-5056.710999999999</v>
@@ -2523,37 +2523,37 @@
         <v>1497.6</v>
       </c>
       <c r="M15">
-        <v>243.7945456406831</v>
+        <v>237.7933621406831</v>
       </c>
       <c r="N15">
-        <v>1253.805454359317</v>
+        <v>1259.806637859317</v>
       </c>
       <c r="O15">
-        <v>206.8778999692873</v>
+        <v>207.8680952467872</v>
       </c>
       <c r="P15">
-        <v>1046.92755439003</v>
+        <v>1051.938542612529</v>
       </c>
       <c r="Q15">
-        <v>1810.827554390029</v>
+        <v>1815.838542612529</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.07429303773857371</v>
+        <v>0.07427973120903854</v>
       </c>
       <c r="T15">
         <v>0.5551229705599844</v>
       </c>
       <c r="U15">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V15">
         <v>0.165</v>
       </c>
       <c r="W15">
-        <v>0.05088207491321597</v>
+        <v>0.04962957491321596</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>6.14287738088792</v>
+        <v>6.297904981527578</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.07125863499056038</v>
+        <v>0.07107172783009691</v>
       </c>
       <c r="C16">
-        <v>25551.46801979799</v>
+        <v>25736.64719092143</v>
       </c>
       <c r="D16">
-        <v>26701.21001979799</v>
+        <v>26886.38919092143</v>
       </c>
       <c r="E16">
         <v>-4748.958</v>
@@ -2605,37 +2605,37 @@
         <v>1497.6</v>
       </c>
       <c r="M16">
-        <v>262.547972228428</v>
+        <v>256.085159228428</v>
       </c>
       <c r="N16">
-        <v>1235.052027771572</v>
+        <v>1241.514840771572</v>
       </c>
       <c r="O16">
-        <v>203.7835845823094</v>
+        <v>204.8499487273094</v>
       </c>
       <c r="P16">
-        <v>1031.268443189262</v>
+        <v>1036.664892044263</v>
       </c>
       <c r="Q16">
-        <v>1795.168443189262</v>
+        <v>1800.564892044263</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.07457574942175597</v>
+        <v>0.07456231086307753</v>
       </c>
       <c r="T16">
         <v>0.5606309739824378</v>
       </c>
       <c r="U16">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V16">
         <v>0.165</v>
       </c>
       <c r="W16">
-        <v>0.05088207491321597</v>
+        <v>0.04962957491321596</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.70410042511021</v>
+        <v>5.84805462570418</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.07145553240984356</v>
+        <v>0.07116844476961222</v>
       </c>
       <c r="C17">
-        <v>25038.79238320444</v>
+        <v>25326.39010362799</v>
       </c>
       <c r="D17">
-        <v>26496.28738320444</v>
+        <v>26783.88510362798</v>
       </c>
       <c r="E17">
         <v>-4441.205</v>
@@ -2687,37 +2687,37 @@
         <v>1497.6</v>
       </c>
       <c r="M17">
-        <v>288.2258413161728</v>
+        <v>278.0699923161728</v>
       </c>
       <c r="N17">
-        <v>1209.374158683827</v>
+        <v>1219.530007683827</v>
       </c>
       <c r="O17">
-        <v>199.5467361828315</v>
+        <v>201.2224512678315</v>
       </c>
       <c r="P17">
-        <v>1009.827422500996</v>
+        <v>1018.307556415996</v>
       </c>
       <c r="Q17">
-        <v>1773.727422500996</v>
+        <v>1782.207556415995</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.07486511314454254</v>
+        <v>0.07485153945015273</v>
       </c>
       <c r="T17">
         <v>0.5662685774854195</v>
       </c>
       <c r="U17">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V17">
         <v>0.165</v>
       </c>
       <c r="W17">
-        <v>0.05213457491321597</v>
+        <v>0.05029757491321597</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.195925504671143</v>
+        <v>5.38569439847069</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.07147707982912672</v>
+        <v>0.07117164170912751</v>
       </c>
       <c r="C18">
-        <v>24708.80451002212</v>
+        <v>25015.26221517407</v>
       </c>
       <c r="D18">
-        <v>26474.05251002212</v>
+        <v>26780.51021517407</v>
       </c>
       <c r="E18">
         <v>-4133.452</v>
@@ -2769,37 +2769,37 @@
         <v>1497.6</v>
       </c>
       <c r="M18">
-        <v>307.4408974039177</v>
+        <v>296.6079918039177</v>
       </c>
       <c r="N18">
-        <v>1190.159102596082</v>
+        <v>1200.992008196082</v>
       </c>
       <c r="O18">
-        <v>196.3762519283536</v>
+        <v>198.1636813523536</v>
       </c>
       <c r="P18">
-        <v>993.7828506677287</v>
+        <v>1002.828326843729</v>
       </c>
       <c r="Q18">
-        <v>1757.682850667729</v>
+        <v>1766.728326843729</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.07516136647977639</v>
+        <v>0.07514765443215829</v>
       </c>
       <c r="T18">
         <v>0.572040409643234</v>
       </c>
       <c r="U18">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V18">
         <v>0.165</v>
       </c>
       <c r="W18">
-        <v>0.05213457491321597</v>
+        <v>0.05029757491321597</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>4.871180160629196</v>
+        <v>5.049088498566272</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.07149862724840991</v>
+        <v>0.07117483864864281</v>
       </c>
       <c r="C19">
-        <v>24378.85392319989</v>
+        <v>24704.13517711487</v>
       </c>
       <c r="D19">
-        <v>26451.85492319989</v>
+        <v>26777.13617711487</v>
       </c>
       <c r="E19">
         <v>-3825.699</v>
@@ -2851,37 +2851,37 @@
         <v>1497.6</v>
       </c>
       <c r="M19">
-        <v>326.6559534916626</v>
+        <v>315.1459912916626</v>
       </c>
       <c r="N19">
-        <v>1170.944046508337</v>
+        <v>1182.454008708337</v>
       </c>
       <c r="O19">
-        <v>193.2057676738757</v>
+        <v>195.1049114368757</v>
       </c>
       <c r="P19">
-        <v>977.7382788344617</v>
+        <v>987.3490972714617</v>
       </c>
       <c r="Q19">
-        <v>1741.638278834462</v>
+        <v>1751.249097271462</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.07546475844959422</v>
+        <v>0.07545090471493507</v>
       </c>
       <c r="T19">
         <v>0.5779513220940079</v>
       </c>
       <c r="U19">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V19">
         <v>0.165</v>
       </c>
       <c r="W19">
-        <v>0.05213457491321597</v>
+        <v>0.05029757491321597</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>4.58464015118042</v>
+        <v>4.752083292768256</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.07152017466769309</v>
+        <v>0.07117803558815813</v>
       </c>
       <c r="C20">
-        <v>24048.94052902637</v>
+        <v>24393.00898912896</v>
       </c>
       <c r="D20">
-        <v>26429.69452902637</v>
+        <v>26773.76298912896</v>
       </c>
       <c r="E20">
         <v>-3517.946</v>
@@ -2933,37 +2933,37 @@
         <v>1497.6</v>
       </c>
       <c r="M20">
-        <v>345.8710095794074</v>
+        <v>333.6839907794074</v>
       </c>
       <c r="N20">
-        <v>1151.728990420592</v>
+        <v>1163.916009220593</v>
       </c>
       <c r="O20">
-        <v>190.0352834193978</v>
+        <v>192.0461415213978</v>
       </c>
       <c r="P20">
-        <v>961.6937070011948</v>
+        <v>971.8698676991947</v>
       </c>
       <c r="Q20">
-        <v>1725.593707001195</v>
+        <v>1735.769867699195</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.07577555022355391</v>
+        <v>0.07576155134607226</v>
       </c>
       <c r="T20">
         <v>0.5840064031411422</v>
       </c>
       <c r="U20">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V20">
         <v>0.165</v>
       </c>
       <c r="W20">
-        <v>0.05213457491321597</v>
+        <v>0.05029757491321597</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>4.329937920559285</v>
+        <v>4.488078665392242</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.07176383208697626</v>
+        <v>0.07118123252767343</v>
       </c>
       <c r="C21">
-        <v>23493.15822657931</v>
+        <v>24081.8836508952</v>
       </c>
       <c r="D21">
-        <v>26181.66522657932</v>
+        <v>26770.3906508952</v>
       </c>
       <c r="E21">
         <v>-3210.193</v>
@@ -3015,45 +3015,45 @@
         <v>1497.6</v>
       </c>
       <c r="M21">
-        <v>373.2722954671522</v>
+        <v>352.2219902671523</v>
       </c>
       <c r="N21">
-        <v>1124.327704532848</v>
+        <v>1145.378009732848</v>
       </c>
       <c r="O21">
-        <v>185.5140712479199</v>
+        <v>188.9873716059199</v>
       </c>
       <c r="P21">
-        <v>938.8136332849278</v>
+        <v>956.3906381269278</v>
       </c>
       <c r="Q21">
-        <v>1702.713633284928</v>
+        <v>1720.290638126928</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.07609401586847558</v>
+        <v>0.07607986826439801</v>
       </c>
       <c r="T21">
         <v>0.5902109923622797</v>
       </c>
       <c r="U21">
-        <v>0.0638366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V21">
         <v>0.165</v>
       </c>
       <c r="W21">
-        <v>0.05330357491321597</v>
+        <v>0.05029757491321597</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y21">
-        <v>4.012084524316881</v>
+        <v>4.251863998792651</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.07179706950625944</v>
+        <v>0.07135142946718873</v>
       </c>
       <c r="C22">
-        <v>23151.93180048957</v>
+        <v>23595.81426494653</v>
       </c>
       <c r="D22">
-        <v>26148.19180048957</v>
+        <v>26592.07426494654</v>
       </c>
       <c r="E22">
         <v>-2902.44</v>
@@ -3097,37 +3097,37 @@
         <v>1497.6</v>
       </c>
       <c r="M22">
-        <v>392.9182057548971</v>
+        <v>376.9150497548972</v>
       </c>
       <c r="N22">
-        <v>1104.681794245103</v>
+        <v>1120.684950245103</v>
       </c>
       <c r="O22">
-        <v>182.272496050442</v>
+        <v>184.913016790442</v>
       </c>
       <c r="P22">
-        <v>922.4092981946608</v>
+        <v>935.7719334546608</v>
       </c>
       <c r="Q22">
-        <v>1686.309298194661</v>
+        <v>1699.671933454661</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.0764204431545203</v>
+        <v>0.07640614310568192</v>
       </c>
       <c r="T22">
         <v>0.5965706963139458</v>
       </c>
       <c r="U22">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V22">
         <v>0.165</v>
       </c>
       <c r="W22">
-        <v>0.05330357491321597</v>
+        <v>0.05113257491321597</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>3.811480298101037</v>
+        <v>3.973309107646058</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.07183030692554261</v>
+        <v>0.07136297640670403</v>
       </c>
       <c r="C23">
-        <v>22810.79085708746</v>
+        <v>23276.04947616895</v>
       </c>
       <c r="D23">
-        <v>26114.80385708746</v>
+        <v>26580.06247616895</v>
       </c>
       <c r="E23">
         <v>-2594.687000000001</v>
@@ -3179,37 +3179,37 @@
         <v>1497.6</v>
       </c>
       <c r="M23">
-        <v>412.5641160426419</v>
+        <v>395.7608022426419</v>
       </c>
       <c r="N23">
-        <v>1085.035883957358</v>
+        <v>1101.839197757358</v>
       </c>
       <c r="O23">
-        <v>179.0309208529641</v>
+        <v>181.803467629964</v>
       </c>
       <c r="P23">
-        <v>906.0049631043939</v>
+        <v>920.0357301273938</v>
       </c>
       <c r="Q23">
-        <v>1669.904963104394</v>
+        <v>1683.935730127394</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.0767551344224902</v>
+        <v>0.07674067806952997</v>
       </c>
       <c r="T23">
         <v>0.603091405428945</v>
       </c>
       <c r="U23">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V23">
         <v>0.165</v>
       </c>
       <c r="W23">
-        <v>0.05330357491321597</v>
+        <v>0.05113257491321597</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>3.629981236286703</v>
+        <v>3.784103912043865</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.07186354434482579</v>
+        <v>0.07137452334621934</v>
       </c>
       <c r="C24">
-        <v>22469.73506933871</v>
+        <v>22956.29553407628</v>
       </c>
       <c r="D24">
-        <v>26081.5010693387</v>
+        <v>26568.06153407628</v>
       </c>
       <c r="E24">
         <v>-2286.934</v>
@@ -3261,37 +3261,37 @@
         <v>1497.6</v>
       </c>
       <c r="M24">
-        <v>432.2100263303868</v>
+        <v>414.6065547303868</v>
       </c>
       <c r="N24">
-        <v>1065.389973669613</v>
+        <v>1082.993445269613</v>
       </c>
       <c r="O24">
-        <v>175.7893456554862</v>
+        <v>178.6939184694861</v>
       </c>
       <c r="P24">
-        <v>889.6006280141269</v>
+        <v>904.2995268001268</v>
       </c>
       <c r="Q24">
-        <v>1653.500628014127</v>
+        <v>1668.199526800127</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.07709840751784394</v>
+        <v>0.07708379085296388</v>
       </c>
       <c r="T24">
         <v>0.6097793122135599</v>
       </c>
       <c r="U24">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V24">
         <v>0.165</v>
       </c>
       <c r="W24">
-        <v>0.05330357491321597</v>
+        <v>0.05113257491321597</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>3.464982089182761</v>
+        <v>3.612099188769144</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.07189678176410896</v>
+        <v>0.07138607028573464</v>
       </c>
       <c r="C25">
-        <v>22128.76411187514</v>
+        <v>22636.5524239833</v>
       </c>
       <c r="D25">
-        <v>26048.28311187514</v>
+        <v>26556.0714239833</v>
       </c>
       <c r="E25">
         <v>-1979.181</v>
@@ -3343,37 +3343,37 @@
         <v>1497.6</v>
       </c>
       <c r="M25">
-        <v>451.8559366181317</v>
+        <v>433.4523072181317</v>
       </c>
       <c r="N25">
-        <v>1045.744063381868</v>
+        <v>1064.147692781868</v>
       </c>
       <c r="O25">
-        <v>172.5477704580083</v>
+        <v>175.5843693090083</v>
       </c>
       <c r="P25">
-        <v>873.19629292386</v>
+        <v>888.56332347286</v>
       </c>
       <c r="Q25">
-        <v>1637.09629292386</v>
+        <v>1652.46332347286</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.07745059679749258</v>
+        <v>0.0774358156567467</v>
       </c>
       <c r="T25">
         <v>0.6166409308627099</v>
       </c>
       <c r="U25">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V25">
         <v>0.165</v>
       </c>
       <c r="W25">
-        <v>0.05330357491321597</v>
+        <v>0.05113257491321597</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>3.314330694000902</v>
+        <v>3.455051397953094</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.07193001918339215</v>
+        <v>0.07139761722524994</v>
       </c>
       <c r="C26">
-        <v>21787.87766098404</v>
+        <v>22316.82013123123</v>
       </c>
       <c r="D26">
-        <v>26015.14966098404</v>
+        <v>26544.09213123123</v>
       </c>
       <c r="E26">
         <v>-1671.428000000001</v>
@@ -3425,37 +3425,37 @@
         <v>1497.6</v>
       </c>
       <c r="M26">
-        <v>471.5018469058765</v>
+        <v>452.2980597058765</v>
       </c>
       <c r="N26">
-        <v>1026.098153094124</v>
+        <v>1045.301940294123</v>
       </c>
       <c r="O26">
-        <v>169.3061952605304</v>
+        <v>172.4748201485304</v>
       </c>
       <c r="P26">
-        <v>856.7919578335932</v>
+        <v>872.827120145593</v>
       </c>
       <c r="Q26">
-        <v>1620.691957833593</v>
+        <v>1636.727120145593</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.07781205421607935</v>
+        <v>0.07779710427115541</v>
       </c>
       <c r="T26">
         <v>0.6236831184236798</v>
       </c>
       <c r="U26">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V26">
         <v>0.165</v>
       </c>
       <c r="W26">
-        <v>0.05330357491321597</v>
+        <v>0.05113257491321597</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.176233581750865</v>
+        <v>3.311090923038382</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.07196325660267533</v>
+        <v>0.07140916416476525</v>
       </c>
       <c r="C27">
-        <v>21447.07539459766</v>
+        <v>21997.09864118773</v>
       </c>
       <c r="D27">
-        <v>25982.10039459767</v>
+        <v>26532.12364118774</v>
       </c>
       <c r="E27">
         <v>-1363.675</v>
@@ -3507,37 +3507,37 @@
         <v>1497.6</v>
       </c>
       <c r="M27">
-        <v>491.1477571936214</v>
+        <v>471.1438121936214</v>
       </c>
       <c r="N27">
-        <v>1006.452242806379</v>
+        <v>1026.456187806378</v>
       </c>
       <c r="O27">
-        <v>166.0646200630525</v>
+        <v>169.3652709880525</v>
       </c>
       <c r="P27">
-        <v>840.3876227433261</v>
+        <v>857.090916818326</v>
       </c>
       <c r="Q27">
-        <v>1604.287622743326</v>
+        <v>1620.990916818326</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.07818315049916177</v>
+        <v>0.078168027248615</v>
       </c>
       <c r="T27">
         <v>0.6309130976529422</v>
       </c>
       <c r="U27">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V27">
         <v>0.165</v>
       </c>
       <c r="W27">
-        <v>0.05330357491321597</v>
+        <v>0.05113257491321597</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.04918423848083</v>
+        <v>3.178647286116846</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.07256095402195849</v>
+        <v>0.07142071110428055</v>
       </c>
       <c r="C28">
-        <v>20559.02042402276</v>
+        <v>21677.3879392469</v>
       </c>
       <c r="D28">
-        <v>25401.79842402276</v>
+        <v>26520.1659392469</v>
       </c>
       <c r="E28">
         <v>-1055.922</v>
@@ -3589,45 +3589,45 @@
         <v>1497.6</v>
       </c>
       <c r="M28">
-        <v>531.5977702813663</v>
+        <v>489.9895646813663</v>
       </c>
       <c r="N28">
-        <v>966.0022297186337</v>
+        <v>1007.610435318634</v>
       </c>
       <c r="O28">
-        <v>159.3903679035746</v>
+        <v>166.2557218275745</v>
       </c>
       <c r="P28">
-        <v>806.6118618150591</v>
+        <v>841.354713491059</v>
       </c>
       <c r="Q28">
-        <v>1570.511861815059</v>
+        <v>1605.254713491059</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.07856427641151667</v>
+        <v>0.07854897517141135</v>
       </c>
       <c r="T28">
         <v>0.6383384817262389</v>
       </c>
       <c r="U28">
-        <v>0.06643661666253409</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V28">
         <v>0.165</v>
       </c>
       <c r="W28">
-        <v>0.05547457491321596</v>
+        <v>0.05113257491321597</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y28">
-        <v>2.817167572406002</v>
+        <v>3.056391621266198</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.07261590144124166</v>
+        <v>0.07199588304379585</v>
       </c>
       <c r="C29">
-        <v>20199.21758815914</v>
+        <v>20787.34285716506</v>
       </c>
       <c r="D29">
-        <v>25349.74858815914</v>
+        <v>25937.87385716506</v>
       </c>
       <c r="E29">
         <v>-748.1689999999999</v>
@@ -3671,37 +3671,37 @@
         <v>1497.6</v>
       </c>
       <c r="M29">
-        <v>552.0438383691111</v>
+        <v>529.6086446691111</v>
       </c>
       <c r="N29">
-        <v>945.5561616308888</v>
+        <v>967.9913553308888</v>
       </c>
       <c r="O29">
-        <v>156.0167666690967</v>
+        <v>159.7185736295967</v>
       </c>
       <c r="P29">
-        <v>789.5393949617921</v>
+        <v>808.2727817012922</v>
       </c>
       <c r="Q29">
-        <v>1553.439394961792</v>
+        <v>1572.172781701292</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.07895584412968953</v>
+        <v>0.07894036002359937</v>
       </c>
       <c r="T29">
         <v>0.6459673009796256</v>
       </c>
       <c r="U29">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V29">
         <v>0.165</v>
       </c>
       <c r="W29">
-        <v>0.05547457491321596</v>
+        <v>0.05322007491321597</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.712828032687261</v>
+        <v>2.827748404551951</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.07267084886052486</v>
+        <v>0.07202830498331116</v>
       </c>
       <c r="C30">
-        <v>19839.62762269418</v>
+        <v>20447.5269320966</v>
       </c>
       <c r="D30">
-        <v>25297.91162269419</v>
+        <v>25905.8109320966</v>
       </c>
       <c r="E30">
         <v>-440.4159999999993</v>
@@ -3753,37 +3753,37 @@
         <v>1497.6</v>
       </c>
       <c r="M30">
-        <v>572.4899064568559</v>
+        <v>549.223779656856</v>
       </c>
       <c r="N30">
-        <v>925.110093543144</v>
+        <v>948.3762203431439</v>
       </c>
       <c r="O30">
-        <v>152.6431654346188</v>
+        <v>156.4820763566188</v>
       </c>
       <c r="P30">
-        <v>772.4669281085253</v>
+        <v>791.8941439865251</v>
       </c>
       <c r="Q30">
-        <v>1536.366928108525</v>
+        <v>1555.794143986525</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.07935828872892275</v>
+        <v>0.07934261667723706</v>
       </c>
       <c r="T30">
         <v>0.65380803187894</v>
       </c>
       <c r="U30">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V30">
         <v>0.165</v>
       </c>
       <c r="W30">
-        <v>0.05547457491321596</v>
+        <v>0.05322007491321597</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.615941317234145</v>
+        <v>2.726757390103667</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.07272579627980802</v>
+        <v>0.07206072692282646</v>
       </c>
       <c r="C31">
-        <v>19480.24922441533</v>
+        <v>20107.79017789194</v>
       </c>
       <c r="D31">
-        <v>25246.28622441533</v>
+        <v>25873.82717789194</v>
       </c>
       <c r="E31">
         <v>-132.6630000000005</v>
@@ -3835,37 +3835,37 @@
         <v>1497.6</v>
       </c>
       <c r="M31">
-        <v>592.9359745446008</v>
+        <v>568.8389146446008</v>
       </c>
       <c r="N31">
-        <v>904.6640254553992</v>
+        <v>928.7610853553991</v>
       </c>
       <c r="O31">
-        <v>149.2695642001409</v>
+        <v>153.2455790836409</v>
       </c>
       <c r="P31">
-        <v>755.3944612552583</v>
+        <v>775.5155062717582</v>
       </c>
       <c r="Q31">
-        <v>1519.294461255258</v>
+        <v>1539.415506271758</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.07977206979573999</v>
+        <v>0.07975620450421667</v>
       </c>
       <c r="T31">
         <v>0.6618696284373898</v>
       </c>
       <c r="U31">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V31">
         <v>0.165</v>
       </c>
       <c r="W31">
-        <v>0.05547457491321596</v>
+        <v>0.05322007491321597</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.525736444226071</v>
+        <v>2.63273127320354</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.07345709369909119</v>
+        <v>0.07209314886234176</v>
       </c>
       <c r="C32">
-        <v>18504.94437810525</v>
+        <v>19768.13230167559</v>
       </c>
       <c r="D32">
-        <v>24578.73437810525</v>
+        <v>25841.92230167559</v>
       </c>
       <c r="E32">
         <v>175.0900000000001</v>
@@ -3917,45 +3917,45 @@
         <v>1497.6</v>
       </c>
       <c r="M32">
-        <v>638.3100356323457</v>
+        <v>588.4540496323457</v>
       </c>
       <c r="N32">
-        <v>859.2899643676542</v>
+        <v>909.1459503676542</v>
       </c>
       <c r="O32">
-        <v>141.782844120663</v>
+        <v>150.009081810663</v>
       </c>
       <c r="P32">
-        <v>717.5071202469912</v>
+        <v>759.1368685569912</v>
       </c>
       <c r="Q32">
-        <v>1481.407120246991</v>
+        <v>1523.036868556991</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.08019767317875201</v>
+        <v>0.08018160912625283</v>
       </c>
       <c r="T32">
         <v>0.6701615563260812</v>
       </c>
       <c r="U32">
-        <v>0.06913661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V32">
         <v>0.165</v>
       </c>
       <c r="W32">
-        <v>0.05772907491321597</v>
+        <v>0.05322007491321597</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>2.34619529131544</v>
+        <v>2.544973564096756</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.07353458611837436</v>
+        <v>0.07303154580185707</v>
       </c>
       <c r="C33">
-        <v>18128.51663452881</v>
+        <v>18569.86867934321</v>
       </c>
       <c r="D33">
-        <v>24510.05963452881</v>
+        <v>24951.4116793432</v>
       </c>
       <c r="E33">
         <v>482.8429999999989</v>
@@ -3999,37 +3999,37 @@
         <v>1497.6</v>
       </c>
       <c r="M33">
-        <v>659.5870368200905</v>
+        <v>641.4603851200905</v>
       </c>
       <c r="N33">
-        <v>838.0129631799094</v>
+        <v>856.1396148799095</v>
       </c>
       <c r="O33">
-        <v>138.2721389246851</v>
+        <v>141.2630364551851</v>
       </c>
       <c r="P33">
-        <v>699.7408242552244</v>
+        <v>714.8765784247244</v>
       </c>
       <c r="Q33">
-        <v>1463.640824255224</v>
+        <v>1478.776578424724</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.08063561289170641</v>
+        <v>0.08061934431704365</v>
       </c>
       <c r="T33">
         <v>0.6786938299506766</v>
       </c>
       <c r="U33">
-        <v>0.06913661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V33">
         <v>0.165</v>
       </c>
       <c r="W33">
-        <v>0.05772907491321597</v>
+        <v>0.05614257491321597</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.270511572240748</v>
+        <v>2.334672623188769</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.07486791853765756</v>
+        <v>0.07309319274137235</v>
       </c>
       <c r="C34">
-        <v>16696.49816409464</v>
+        <v>18205.75810398758</v>
       </c>
       <c r="D34">
-        <v>23385.79416409464</v>
+        <v>24895.05410398758</v>
       </c>
       <c r="E34">
         <v>790.5959999999995</v>
@@ -4081,45 +4081,45 @@
         <v>1497.6</v>
       </c>
       <c r="M34">
-        <v>727.1500892078354</v>
+        <v>662.1526556078353</v>
       </c>
       <c r="N34">
-        <v>770.4499107921645</v>
+        <v>835.4473443921646</v>
       </c>
       <c r="O34">
-        <v>127.1242352807071</v>
+        <v>137.8488118247072</v>
       </c>
       <c r="P34">
-        <v>643.3256755114573</v>
+        <v>697.5985325674575</v>
       </c>
       <c r="Q34">
-        <v>1407.225675511457</v>
+        <v>1461.498532567457</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.0810864331844536</v>
+        <v>0.0810699540722695</v>
       </c>
       <c r="T34">
         <v>0.6874770527995249</v>
       </c>
       <c r="U34">
-        <v>0.0738366166625341</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V34">
         <v>0.165</v>
       </c>
       <c r="W34">
-        <v>0.06165357491321598</v>
+        <v>0.05614257491321597</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>2.059547295980532</v>
+        <v>2.26171410371412</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.07754727095694071</v>
+        <v>0.07392637968088767</v>
       </c>
       <c r="C35">
-        <v>14415.07050540005</v>
+        <v>17160.53962946495</v>
       </c>
       <c r="D35">
-        <v>21412.11950540005</v>
+        <v>24157.58862946495</v>
       </c>
       <c r="E35">
         <v>1098.349</v>
@@ -4163,45 +4163,45 @@
         <v>1497.6</v>
       </c>
       <c r="M35">
-        <v>844.3229251955802</v>
+        <v>711.2813032955802</v>
       </c>
       <c r="N35">
-        <v>653.2770748044197</v>
+        <v>786.3186967044197</v>
       </c>
       <c r="O35">
-        <v>107.7907173427293</v>
+        <v>129.7425849562293</v>
       </c>
       <c r="P35">
-        <v>545.4863574616904</v>
+        <v>656.5761117481904</v>
       </c>
       <c r="Q35">
-        <v>1309.38635746169</v>
+        <v>1420.47611174819</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.08155071079937232</v>
+        <v>0.08153401486496478</v>
       </c>
       <c r="T35">
         <v>0.696522461405055</v>
       </c>
       <c r="U35">
-        <v>0.08313661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V35">
         <v>0.165</v>
       </c>
       <c r="W35">
-        <v>0.06941907491321596</v>
+        <v>0.05848057491321597</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y35">
-        <v>1.773728931561456</v>
+        <v>2.105496085811856</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.0790759933762239</v>
+        <v>0.07401140662040297</v>
       </c>
       <c r="C36">
-        <v>13123.62975302587</v>
+        <v>16779.97757549358</v>
       </c>
       <c r="D36">
-        <v>20428.43175302587</v>
+        <v>24084.77957549359</v>
       </c>
       <c r="E36">
         <v>1406.102000000001</v>
@@ -4245,45 +4245,45 @@
         <v>1497.6</v>
       </c>
       <c r="M36">
-        <v>919.0873977833251</v>
+        <v>732.8352821833251</v>
       </c>
       <c r="N36">
-        <v>578.5126022166748</v>
+        <v>764.7647178166748</v>
       </c>
       <c r="O36">
-        <v>95.45457936575136</v>
+        <v>126.1861784397513</v>
       </c>
       <c r="P36">
-        <v>483.0580228509235</v>
+        <v>638.5785393769235</v>
       </c>
       <c r="Q36">
-        <v>1246.958022850923</v>
+        <v>1402.478539376923</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.08202905743292496</v>
+        <v>0.08201213810592356</v>
       </c>
       <c r="T36">
         <v>0.705841973301662</v>
       </c>
       <c r="U36">
-        <v>0.08783661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V36">
         <v>0.165</v>
       </c>
       <c r="W36">
-        <v>0.07334357491321596</v>
+        <v>0.05848057491321597</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y36">
-        <v>1.629442426924734</v>
+        <v>2.043569730346801</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.07930963079550707</v>
+        <v>0.07637598355991829</v>
       </c>
       <c r="C37">
-        <v>12673.44468315599</v>
+        <v>14609.64134032409</v>
       </c>
       <c r="D37">
-        <v>20285.99968315599</v>
+        <v>22222.1963403241</v>
       </c>
       <c r="E37">
         <v>1713.855000000001</v>
@@ -4327,45 +4327,45 @@
         <v>1497.6</v>
       </c>
       <c r="M37">
-        <v>946.1193800710701</v>
+        <v>838.4058300710702</v>
       </c>
       <c r="N37">
-        <v>551.4806199289299</v>
+        <v>659.1941699289297</v>
       </c>
       <c r="O37">
-        <v>90.99430228827343</v>
+        <v>108.7670380382734</v>
       </c>
       <c r="P37">
-        <v>460.4863176406564</v>
+        <v>550.4271318906563</v>
       </c>
       <c r="Q37">
-        <v>1224.386317640656</v>
+        <v>1314.327131890656</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.08252212242443308</v>
+        <v>0.08250497283121953</v>
       </c>
       <c r="T37">
         <v>0.7154482394104723</v>
       </c>
       <c r="U37">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V37">
         <v>0.165</v>
       </c>
       <c r="W37">
-        <v>0.07334357491321596</v>
+        <v>0.06499357491321597</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>1.582886929012599</v>
+        <v>1.786247120768532</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.07954326821479026</v>
+        <v>0.07769848049943359</v>
       </c>
       <c r="C38">
-        <v>12225.23200440221</v>
+        <v>13380.5658763933</v>
       </c>
       <c r="D38">
-        <v>20145.54000440221</v>
+        <v>21300.8738763933</v>
       </c>
       <c r="E38">
         <v>2021.608</v>
@@ -4409,37 +4409,37 @@
         <v>1497.6</v>
       </c>
       <c r="M38">
-        <v>973.1513623588147</v>
+        <v>905.5688035588148</v>
       </c>
       <c r="N38">
-        <v>524.4486376411852</v>
+        <v>592.0311964411851</v>
       </c>
       <c r="O38">
-        <v>86.53402521079556</v>
+        <v>97.68514741279554</v>
       </c>
       <c r="P38">
-        <v>437.9146124303896</v>
+        <v>494.3460490283895</v>
       </c>
       <c r="Q38">
-        <v>1201.81461243039</v>
+        <v>1258.24604902839</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.08303059569692579</v>
+        <v>0.08301320864168099</v>
       </c>
       <c r="T38">
         <v>0.7253547013351828</v>
       </c>
       <c r="U38">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V38">
         <v>0.165</v>
       </c>
       <c r="W38">
-        <v>0.07334357491321596</v>
+        <v>0.06825007491321597</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>1.538917847651138</v>
+        <v>1.653767216929899</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.08481279063407343</v>
+        <v>0.07788120243894889</v>
       </c>
       <c r="C39">
-        <v>9196.387460413904</v>
+        <v>12951.49145786255</v>
       </c>
       <c r="D39">
-        <v>17424.4484604139</v>
+        <v>21179.55245786255</v>
       </c>
       <c r="E39">
         <v>2329.360999999999</v>
@@ -4491,45 +4491,45 @@
         <v>1497.6</v>
       </c>
       <c r="M39">
-        <v>1185.78917894656</v>
+        <v>930.7234925465596</v>
       </c>
       <c r="N39">
-        <v>311.8108210534403</v>
+        <v>566.8765074534404</v>
       </c>
       <c r="O39">
-        <v>51.44878547381766</v>
+        <v>93.53462372981767</v>
       </c>
       <c r="P39">
-        <v>260.3620355796227</v>
+        <v>473.3418837236227</v>
       </c>
       <c r="Q39">
-        <v>1024.262035579623</v>
+        <v>1237.241883723623</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.08355521097806909</v>
+        <v>0.08353757892231584</v>
       </c>
       <c r="T39">
         <v>0.735575654114646</v>
       </c>
       <c r="U39">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V39">
         <v>0.165</v>
       </c>
       <c r="W39">
-        <v>0.08695407491321597</v>
+        <v>0.06825007491321597</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y39">
-        <v>1.262956372506662</v>
+        <v>1.609070805661524</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.09621048980535227</v>
+        <v>0.07806392437846418</v>
       </c>
       <c r="C40">
-        <v>4949.005574757562</v>
+        <v>12523.79121096937</v>
       </c>
       <c r="D40">
-        <v>13484.81957475756</v>
+        <v>21059.60521096937</v>
       </c>
       <c r="E40">
         <v>2637.114</v>
@@ -4573,45 +4573,45 @@
         <v>1497.6</v>
       </c>
       <c r="M40">
-        <v>1600.251412934305</v>
+        <v>955.8781815343044</v>
       </c>
       <c r="N40">
-        <v>-102.6514129343047</v>
+        <v>541.7218184656955</v>
       </c>
       <c r="O40">
-        <v>-16.93748313416028</v>
+        <v>89.38410004683976</v>
       </c>
       <c r="P40">
-        <v>-85.71392980014446</v>
+        <v>452.3377184188557</v>
       </c>
       <c r="Q40">
-        <v>678.1860701998555</v>
+        <v>1216.237718418856</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.08426108337888653</v>
+        <v>0.08407886437329373</v>
       </c>
       <c r="T40">
-        <v>0.7493279955663827</v>
+        <v>0.7461263150482854</v>
       </c>
       <c r="U40">
-        <v>0.1368366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V40">
-        <v>0.1544157361791652</v>
+        <v>0.165</v>
       </c>
       <c r="W40">
-        <v>0.1157068897643227</v>
+        <v>0.06825007491321597</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y40">
-        <v>0.9358529465403953</v>
+        <v>1.566726837091484</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.0971208559719776</v>
+        <v>0.07824664631797949</v>
       </c>
       <c r="C41">
-        <v>4402.04916960373</v>
+        <v>12097.44191994243</v>
       </c>
       <c r="D41">
-        <v>13245.61616960373</v>
+        <v>20941.00891994243</v>
       </c>
       <c r="E41">
         <v>2944.867</v>
@@ -4655,45 +4655,45 @@
         <v>1497.6</v>
       </c>
       <c r="M41">
-        <v>1642.363292222049</v>
+        <v>981.0328705220494</v>
       </c>
       <c r="N41">
-        <v>-144.7632922220496</v>
+        <v>516.5671294779505</v>
       </c>
       <c r="O41">
-        <v>-23.88594321663818</v>
+        <v>85.23357636386184</v>
       </c>
       <c r="P41">
-        <v>-120.8773490054114</v>
+        <v>431.3335531140887</v>
       </c>
       <c r="Q41">
-        <v>643.0226509945886</v>
+        <v>1195.233553114089</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.08489159294247484</v>
+        <v>0.08463789688823814</v>
       </c>
       <c r="T41">
-        <v>0.761612061067471</v>
+        <v>0.7570228992912246</v>
       </c>
       <c r="U41">
-        <v>0.1368366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V41">
-        <v>0.1504563583284174</v>
+        <v>0.165</v>
       </c>
       <c r="W41">
-        <v>0.1162486776335076</v>
+        <v>0.06825007491321597</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y41">
-        <v>0.9118567171419236</v>
+        <v>1.526554354089138</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.09803122213860294</v>
+        <v>0.08317216825749479</v>
       </c>
       <c r="C42">
-        <v>3863.431175005016</v>
+        <v>9029.73669667059</v>
       </c>
       <c r="D42">
-        <v>13014.75117500502</v>
+        <v>18181.05669667059</v>
       </c>
       <c r="E42">
         <v>3252.620000000001</v>
@@ -4737,45 +4737,45 @@
         <v>1497.6</v>
       </c>
       <c r="M42">
-        <v>1684.475171509794</v>
+        <v>1180.991263509794</v>
       </c>
       <c r="N42">
-        <v>-186.8751715097944</v>
+        <v>316.6087364902055</v>
       </c>
       <c r="O42">
-        <v>-30.83440329911608</v>
+        <v>52.24044152088391</v>
       </c>
       <c r="P42">
-        <v>-156.0407682106784</v>
+        <v>264.3682949693216</v>
       </c>
       <c r="Q42">
-        <v>607.8592317893216</v>
+        <v>1028.268294969322</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.08554311949151608</v>
+        <v>0.08521556382034734</v>
       </c>
       <c r="T42">
-        <v>0.7743055954185954</v>
+        <v>0.7682827030089284</v>
       </c>
       <c r="U42">
-        <v>0.1368366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V42">
-        <v>0.146694949370207</v>
+        <v>0.165</v>
       </c>
       <c r="W42">
-        <v>0.1167633761092332</v>
+        <v>0.08010707491321598</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y42">
-        <v>0.8890602992133756</v>
+        <v>1.268087280806188</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.09894158830522828</v>
+        <v>0.09374070974902919</v>
       </c>
       <c r="C43">
-        <v>3332.723056149332</v>
+        <v>4713.965186627704</v>
       </c>
       <c r="D43">
-        <v>12791.79605614933</v>
+        <v>14173.03818662771</v>
       </c>
       <c r="E43">
         <v>3560.373000000001</v>
@@ -4819,37 +4819,37 @@
         <v>1497.6</v>
       </c>
       <c r="M43">
-        <v>1726.587050797539</v>
+        <v>1571.387212897539</v>
       </c>
       <c r="N43">
-        <v>-228.9870507975395</v>
+        <v>-73.78721289753935</v>
       </c>
       <c r="O43">
-        <v>-37.78286338159402</v>
+        <v>-12.17489012809399</v>
       </c>
       <c r="P43">
-        <v>-191.2041874159455</v>
+        <v>-61.61232276944536</v>
       </c>
       <c r="Q43">
-        <v>572.6958125840545</v>
+        <v>702.2876772305547</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.08621673168628755</v>
+        <v>0.08594914091306874</v>
       </c>
       <c r="T43">
-        <v>0.7874294190697582</v>
+        <v>0.782581485952393</v>
       </c>
       <c r="U43">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V43">
-        <v>0.1431170237758117</v>
+        <v>0.1572521387292924</v>
       </c>
       <c r="W43">
-        <v>0.1172529673422406</v>
+        <v>0.1049529673422406</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.8673759016715858</v>
+        <v>0.9530432650260146</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.09985195447185363</v>
+        <v>0.09452807591565454</v>
       </c>
       <c r="C44">
-        <v>2809.525148491944</v>
+        <v>4177.199024569842</v>
       </c>
       <c r="D44">
-        <v>12576.35114849194</v>
+        <v>13944.02502456984</v>
       </c>
       <c r="E44">
         <v>3868.125999999998</v>
@@ -4901,37 +4901,37 @@
         <v>1497.6</v>
       </c>
       <c r="M44">
-        <v>1768.698930085284</v>
+        <v>1609.713730285284</v>
       </c>
       <c r="N44">
-        <v>-271.0989300852839</v>
+        <v>-112.113730285284</v>
       </c>
       <c r="O44">
-        <v>-44.73132346407184</v>
+        <v>-18.49876549707185</v>
       </c>
       <c r="P44">
-        <v>-226.367606621212</v>
+        <v>-93.61496478821211</v>
       </c>
       <c r="Q44">
-        <v>537.5323933787879</v>
+        <v>670.2850352117879</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.08691357188777526</v>
+        <v>0.08664136748053544</v>
       </c>
       <c r="T44">
-        <v>0.8010057883640643</v>
+        <v>0.7960742701929513</v>
       </c>
       <c r="U44">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V44">
-        <v>0.1397094755906733</v>
+        <v>0.1535080401881188</v>
       </c>
       <c r="W44">
-        <v>0.1177192447070095</v>
+        <v>0.1054192447070095</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.8467240944889293</v>
+        <v>0.9303517587158715</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.100762320638479</v>
+        <v>0.09531544208227988</v>
       </c>
       <c r="C45">
-        <v>2293.464266797962</v>
+        <v>3647.71613447456</v>
       </c>
       <c r="D45">
-        <v>12368.04326679796</v>
+        <v>13722.29513447456</v>
       </c>
       <c r="E45">
         <v>4175.878999999999</v>
@@ -4983,37 +4983,37 @@
         <v>1497.6</v>
       </c>
       <c r="M45">
-        <v>1810.810809373029</v>
+        <v>1648.040247673029</v>
       </c>
       <c r="N45">
-        <v>-313.210809373029</v>
+        <v>-150.4402476730288</v>
       </c>
       <c r="O45">
-        <v>-51.67978354654978</v>
+        <v>-24.82264086604975</v>
       </c>
       <c r="P45">
-        <v>-261.5310258264792</v>
+        <v>-125.6176068069791</v>
       </c>
       <c r="Q45">
-        <v>502.3689741735208</v>
+        <v>638.2823931930209</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.08763486262264851</v>
+        <v>0.08735788269949218</v>
       </c>
       <c r="T45">
-        <v>0.8150585214932584</v>
+        <v>0.8100404854594943</v>
       </c>
       <c r="U45">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V45">
-        <v>0.1364604180187972</v>
+        <v>0.1499380857651393</v>
       </c>
       <c r="W45">
-        <v>0.1181638347524868</v>
+        <v>0.1058638347524868</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.8270328364775588</v>
+        <v>0.9087156713038745</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1016726868051043</v>
+        <v>0.09610280824890521</v>
       </c>
       <c r="C46">
-        <v>1784.191547928409</v>
+        <v>3125.174511464274</v>
       </c>
       <c r="D46">
-        <v>12166.52354792841</v>
+        <v>13507.50651146427</v>
       </c>
       <c r="E46">
         <v>4483.632</v>
@@ -5065,37 +5065,37 @@
         <v>1497.6</v>
       </c>
       <c r="M46">
-        <v>1852.922688660774</v>
+        <v>1686.366765060774</v>
       </c>
       <c r="N46">
-        <v>-355.3226886607738</v>
+        <v>-188.7667650607737</v>
       </c>
       <c r="O46">
-        <v>-58.62824362902768</v>
+        <v>-31.14651623502765</v>
       </c>
       <c r="P46">
-        <v>-296.6944450317461</v>
+        <v>-157.620248825746</v>
       </c>
       <c r="Q46">
-        <v>467.2055549682539</v>
+        <v>606.279751174254</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.08838191374091009</v>
+        <v>0.08809998774769742</v>
       </c>
       <c r="T46">
-        <v>0.8296131379484952</v>
+        <v>0.8245054941284139</v>
       </c>
       <c r="U46">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V46">
-        <v>0.1333590448820064</v>
+        <v>0.1465304019977498</v>
       </c>
       <c r="W46">
-        <v>0.1185882161595333</v>
+        <v>0.1062882161595333</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.8082366356485233</v>
+        <v>0.8880630424106046</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1413571946775077</v>
+        <v>0.09689017441553055</v>
       </c>
       <c r="C47">
-        <v>-3576.268379551046</v>
+        <v>2609.253233624817</v>
       </c>
       <c r="D47">
-        <v>7113.816620448954</v>
+        <v>13299.33823362482</v>
       </c>
       <c r="E47">
         <v>4791.385</v>
@@ -5147,45 +5147,45 @@
         <v>1497.6</v>
       </c>
       <c r="M47">
-        <v>3070.804904448519</v>
+        <v>1724.693282448519</v>
       </c>
       <c r="N47">
-        <v>-1573.204904448519</v>
+        <v>-227.0932824485187</v>
       </c>
       <c r="O47">
-        <v>-259.5788092340056</v>
+        <v>-37.47039160400559</v>
       </c>
       <c r="P47">
-        <v>-1313.626095214513</v>
+        <v>-189.6228908445131</v>
       </c>
       <c r="Q47">
-        <v>-549.7260952145133</v>
+        <v>574.2771091554869</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.09019093345579576</v>
+        <v>0.08886907843401919</v>
       </c>
       <c r="T47">
-        <v>0.8648578320082443</v>
+        <v>0.8394965031125668</v>
       </c>
       <c r="U47">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V47">
-        <v>0.08046880465835946</v>
+        <v>0.1432741708422442</v>
       </c>
       <c r="W47">
-        <v>0.2038937361707111</v>
+        <v>0.1066937361707111</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y47">
-        <v>0.4876897252021785</v>
+        <v>0.8683283081348133</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.143116560844133</v>
+        <v>0.09767754058215591</v>
       </c>
       <c r="C48">
-        <v>-4012.630612851439</v>
+        <v>2099.650862082615</v>
       </c>
       <c r="D48">
-        <v>6985.207387148561</v>
+        <v>13097.48886208262</v>
       </c>
       <c r="E48">
         <v>5099.138000000001</v>
@@ -5229,45 +5229,45 @@
         <v>1497.6</v>
       </c>
       <c r="M48">
-        <v>3139.045013436264</v>
+        <v>1763.019799836263</v>
       </c>
       <c r="N48">
-        <v>-1641.445013436264</v>
+        <v>-265.4197998362636</v>
       </c>
       <c r="O48">
-        <v>-270.8384272169835</v>
+        <v>-43.79426697298349</v>
       </c>
       <c r="P48">
-        <v>-1370.60658621928</v>
+        <v>-221.6255328632801</v>
       </c>
       <c r="Q48">
-        <v>-606.7065862192802</v>
+        <v>542.27446713672</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.09101298777905126</v>
+        <v>0.0896666539605751</v>
       </c>
       <c r="T48">
-        <v>0.8808737177861748</v>
+        <v>0.8550427346516886</v>
       </c>
       <c r="U48">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V48">
-        <v>0.07871948281796032</v>
+        <v>0.1401595149543693</v>
       </c>
       <c r="W48">
-        <v>0.2042816248770551</v>
+        <v>0.1070816248770551</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y48">
-        <v>0.477087774654305</v>
+        <v>0.8494516057840565</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1448759270107584</v>
+        <v>0.09846490674878125</v>
       </c>
       <c r="C49">
-        <v>-4444.425223307187</v>
+        <v>1596.08398459968</v>
       </c>
       <c r="D49">
-        <v>6861.165776692814</v>
+        <v>12901.67498459968</v>
       </c>
       <c r="E49">
         <v>5406.891000000001</v>
@@ -5311,45 +5311,45 @@
         <v>1497.6</v>
       </c>
       <c r="M49">
-        <v>3207.285122424009</v>
+        <v>1801.346317224009</v>
       </c>
       <c r="N49">
-        <v>-1709.685122424009</v>
+        <v>-303.7463172240086</v>
       </c>
       <c r="O49">
-        <v>-282.0980451999615</v>
+        <v>-50.11814234196143</v>
       </c>
       <c r="P49">
-        <v>-1427.587077224048</v>
+        <v>-253.6281748820472</v>
       </c>
       <c r="Q49">
-        <v>-663.6870772240476</v>
+        <v>510.2718251179527</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.09186606302016542</v>
+        <v>0.09049432667681237</v>
       </c>
       <c r="T49">
-        <v>0.8974939766123291</v>
+        <v>0.8711756164375695</v>
       </c>
       <c r="U49">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V49">
-        <v>0.07704460020481223</v>
+        <v>0.1371773976149147</v>
       </c>
       <c r="W49">
-        <v>0.2046530076810015</v>
+        <v>0.1074530076810015</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y49">
-        <v>0.4669369709382559</v>
+        <v>0.8313781673631191</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1466352931773837</v>
+        <v>0.09925227291540659</v>
       </c>
       <c r="C50">
-        <v>-4871.891297477414</v>
+        <v>1098.285887887951</v>
       </c>
       <c r="D50">
-        <v>6741.452702522584</v>
+        <v>12711.62988788795</v>
       </c>
       <c r="E50">
         <v>5714.643999999998</v>
@@ -5393,45 +5393,45 @@
         <v>1497.6</v>
       </c>
       <c r="M50">
-        <v>3275.525231411753</v>
+        <v>1839.672834611753</v>
       </c>
       <c r="N50">
-        <v>-1777.925231411753</v>
+        <v>-342.072834611753</v>
       </c>
       <c r="O50">
-        <v>-293.3576631829392</v>
+        <v>-56.44201771093925</v>
       </c>
       <c r="P50">
-        <v>-1484.567568228814</v>
+        <v>-285.6308169008138</v>
       </c>
       <c r="Q50">
-        <v>-720.6675682288138</v>
+        <v>478.2691830991862</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.0927519488474763</v>
+        <v>0.09135383295905876</v>
       </c>
       <c r="T50">
-        <v>0.9147534761625662</v>
+        <v>0.8879289936767535</v>
       </c>
       <c r="U50">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V50">
-        <v>0.07543950436721199</v>
+        <v>0.134319535164604</v>
       </c>
       <c r="W50">
-        <v>0.20500891620145</v>
+        <v>0.1078089162014501</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y50">
-        <v>0.4572091173770424</v>
+        <v>0.8140577888763876</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.148394659344009</v>
+        <v>0.1141590496513008</v>
       </c>
       <c r="C51">
-        <v>-5295.251521815993</v>
+        <v>-1981.439947525212</v>
       </c>
       <c r="D51">
-        <v>6625.845478184006</v>
+        <v>9939.657052474786</v>
       </c>
       <c r="E51">
         <v>6022.396999999999</v>
@@ -5475,45 +5475,45 @@
         <v>1497.6</v>
       </c>
       <c r="M51">
-        <v>3343.765340399498</v>
+        <v>2303.252447399498</v>
       </c>
       <c r="N51">
-        <v>-1846.165340399498</v>
+        <v>-805.6524473994978</v>
       </c>
       <c r="O51">
-        <v>-304.6172811659172</v>
+        <v>-132.9326538209171</v>
       </c>
       <c r="P51">
-        <v>-1541.548059233581</v>
+        <v>-672.7197935785806</v>
       </c>
       <c r="Q51">
-        <v>-777.6480592335807</v>
+        <v>91.18020642141937</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.09367257529546602</v>
+        <v>0.09283804648623414</v>
       </c>
       <c r="T51">
-        <v>0.9326898188324203</v>
+        <v>0.9168590778865869</v>
       </c>
       <c r="U51">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V51">
-        <v>0.07389992264543216</v>
+        <v>0.1072848094784375</v>
       </c>
       <c r="W51">
-        <v>0.205350297843513</v>
+        <v>0.136350297843513</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y51">
-        <v>0.4478783190632252</v>
+        <v>0.6502109665359848</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1501540255106344</v>
+        <v>0.1425760982821221</v>
       </c>
       <c r="C52">
-        <v>-5714.713565166858</v>
+        <v>-5207.844586181343</v>
       </c>
       <c r="D52">
-        <v>6514.136434833142</v>
+        <v>7021.005413818656</v>
       </c>
       <c r="E52">
         <v>6330.15</v>
@@ -5557,37 +5557,37 @@
         <v>1497.6</v>
       </c>
       <c r="M52">
-        <v>3412.005449387243</v>
+        <v>3181.190699387243</v>
       </c>
       <c r="N52">
-        <v>-1914.405449387243</v>
+        <v>-1683.590699387243</v>
       </c>
       <c r="O52">
-        <v>-315.8768991488951</v>
+        <v>-277.792465398895</v>
       </c>
       <c r="P52">
-        <v>-1598.528550238348</v>
+        <v>-1405.798233988348</v>
       </c>
       <c r="Q52">
-        <v>-834.6285502383481</v>
+        <v>-641.8982339883477</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.09463002680137536</v>
+        <v>0.09447417234435083</v>
       </c>
       <c r="T52">
-        <v>0.9513436152090688</v>
+        <v>0.9487502161807397</v>
       </c>
       <c r="U52">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V52">
-        <v>0.0724219241925235</v>
+        <v>0.07767657564433245</v>
       </c>
       <c r="W52">
-        <v>0.2056780242198934</v>
+        <v>0.1906780242198934</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.4389207526819606</v>
+        <v>0.4707671251171663</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1519133916772597</v>
+        <v>0.1441854644487475</v>
       </c>
       <c r="C53">
-        <v>-6130.471323728194</v>
+        <v>-5630.445532796257</v>
       </c>
       <c r="D53">
-        <v>6406.131676271806</v>
+        <v>6906.157467203743</v>
       </c>
       <c r="E53">
         <v>6637.903</v>
@@ -5639,37 +5639,37 @@
         <v>1497.6</v>
       </c>
       <c r="M53">
-        <v>3480.245558374988</v>
+        <v>3244.814513374988</v>
       </c>
       <c r="N53">
-        <v>-1982.645558374988</v>
+        <v>-1747.214513374988</v>
       </c>
       <c r="O53">
-        <v>-327.1365171318731</v>
+        <v>-288.290394706873</v>
       </c>
       <c r="P53">
-        <v>-1655.509041243115</v>
+        <v>-1458.924118668115</v>
       </c>
       <c r="Q53">
-        <v>-891.609041243115</v>
+        <v>-695.0241186681147</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.09562655796058711</v>
+        <v>0.095467522800358</v>
       </c>
       <c r="T53">
-        <v>0.9707587910296622</v>
+        <v>0.9681124654905509</v>
       </c>
       <c r="U53">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V53">
-        <v>0.07100188646325833</v>
+        <v>0.07615350553365925</v>
       </c>
       <c r="W53">
-        <v>0.2059928985815138</v>
+        <v>0.1909928985815138</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.4303144634136868</v>
+        <v>0.4615363971736924</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1536727578438851</v>
+        <v>0.1457948306153728</v>
       </c>
       <c r="C54">
-        <v>-6542.706044187133</v>
+        <v>-6049.349640315568</v>
       </c>
       <c r="D54">
-        <v>6301.649955812868</v>
+        <v>6795.006359684432</v>
       </c>
       <c r="E54">
         <v>6945.656000000001</v>
@@ -5721,37 +5721,37 @@
         <v>1497.6</v>
       </c>
       <c r="M54">
-        <v>3548.485667362733</v>
+        <v>3308.438327362733</v>
       </c>
       <c r="N54">
-        <v>-2050.885667362733</v>
+        <v>-1810.838327362733</v>
       </c>
       <c r="O54">
-        <v>-338.3961351148509</v>
+        <v>-298.7883240148509</v>
       </c>
       <c r="P54">
-        <v>-1712.489532247882</v>
+        <v>-1512.050003347882</v>
       </c>
       <c r="Q54">
-        <v>-948.5895322478819</v>
+        <v>-748.150003347882</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.09666461125143266</v>
+        <v>0.0965022628586988</v>
       </c>
       <c r="T54">
-        <v>0.9909829325094469</v>
+        <v>0.9882814751882707</v>
       </c>
       <c r="U54">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V54">
-        <v>0.06963646556973413</v>
+        <v>0.07468901504262734</v>
       </c>
       <c r="W54">
-        <v>0.2062956623907642</v>
+        <v>0.1912956623907642</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.4220391852711159</v>
+        <v>0.4526606972280445</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1554321240105104</v>
+        <v>0.1474041967819982</v>
       </c>
       <c r="C55">
-        <v>-6951.587338710648</v>
+        <v>-6464.732577696439</v>
       </c>
       <c r="D55">
-        <v>6200.521661289352</v>
+        <v>6687.37642230356</v>
       </c>
       <c r="E55">
         <v>7253.409</v>
@@ -5803,37 +5803,37 @@
         <v>1497.6</v>
       </c>
       <c r="M55">
-        <v>3616.725776350478</v>
+        <v>3372.062141350477</v>
       </c>
       <c r="N55">
-        <v>-2119.125776350478</v>
+        <v>-1874.462141350477</v>
       </c>
       <c r="O55">
-        <v>-349.6557530978288</v>
+        <v>-309.2862533228288</v>
       </c>
       <c r="P55">
-        <v>-1769.470023252649</v>
+        <v>-1565.175888027649</v>
       </c>
       <c r="Q55">
-        <v>-1005.570023252649</v>
+        <v>-801.2758880276486</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.09774683702273976</v>
+        <v>0.09758103440888388</v>
       </c>
       <c r="T55">
-        <v>1.012067675754329</v>
+        <v>1.009308740617808</v>
       </c>
       <c r="U55">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V55">
-        <v>0.0683225699929467</v>
+        <v>0.07327978834370985</v>
       </c>
       <c r="W55">
-        <v>0.2065870011506089</v>
+        <v>0.1915870011506089</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.4140761817754345</v>
+        <v>0.4441199293558172</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1571914901771358</v>
+        <v>0.1490135629486235</v>
       </c>
       <c r="C56">
-        <v>-7357.274103749181</v>
+        <v>-6876.759057364034</v>
       </c>
       <c r="D56">
-        <v>6102.587896250819</v>
+        <v>6583.102942635966</v>
       </c>
       <c r="E56">
         <v>7561.162</v>
@@ -5885,37 +5885,37 @@
         <v>1497.6</v>
       </c>
       <c r="M56">
-        <v>3684.965885338223</v>
+        <v>3435.685955338222</v>
       </c>
       <c r="N56">
-        <v>-2187.365885338223</v>
+        <v>-1938.085955338222</v>
       </c>
       <c r="O56">
-        <v>-360.9153710808067</v>
+        <v>-319.7841826308067</v>
       </c>
       <c r="P56">
-        <v>-1826.450514257416</v>
+        <v>-1618.301772707416</v>
       </c>
       <c r="Q56">
-        <v>-1062.550514257416</v>
+        <v>-854.4017727074157</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.09887611608845148</v>
+        <v>0.09870670906994655</v>
       </c>
       <c r="T56">
-        <v>1.034069146966379</v>
+        <v>1.031250234979065</v>
       </c>
       <c r="U56">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V56">
-        <v>0.06705733721529954</v>
+        <v>0.07192275522623374</v>
       </c>
       <c r="W56">
-        <v>0.206867549586015</v>
+        <v>0.191867549586015</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.4064081043351487</v>
+        <v>0.4358954862195984</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1589508563437611</v>
+        <v>0.1506229291152488</v>
       </c>
       <c r="C57">
-        <v>-7759.915353122233</v>
+        <v>-7285.583676300019</v>
       </c>
       <c r="D57">
-        <v>6007.699646877768</v>
+        <v>6482.031323699981</v>
       </c>
       <c r="E57">
         <v>7868.915000000001</v>
@@ -5967,37 +5967,37 @@
         <v>1497.6</v>
       </c>
       <c r="M57">
-        <v>3753.205994325967</v>
+        <v>3499.309769325967</v>
       </c>
       <c r="N57">
-        <v>-2255.605994325967</v>
+        <v>-2001.709769325967</v>
       </c>
       <c r="O57">
-        <v>-372.1749890637847</v>
+        <v>-330.2821119387847</v>
       </c>
       <c r="P57">
-        <v>-1883.431005262183</v>
+        <v>-1671.427657387183</v>
       </c>
       <c r="Q57">
-        <v>-1119.531005262183</v>
+        <v>-907.5276573871828</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1000555853348615</v>
+        <v>0.09988241371594539</v>
       </c>
       <c r="T57">
-        <v>1.05704846134341</v>
+        <v>1.054166906867489</v>
       </c>
       <c r="U57">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V57">
-        <v>0.06583811290229409</v>
+        <v>0.07061506876757494</v>
       </c>
       <c r="W57">
-        <v>0.2071378962601335</v>
+        <v>0.1921378962601335</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3990188660745096</v>
+        <v>0.4279701137428784</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1607102225103865</v>
+        <v>0.1522322952818742</v>
       </c>
       <c r="C58">
-        <v>-8159.65097457272</v>
+        <v>-7691.351680822288</v>
       </c>
       <c r="D58">
-        <v>5915.717025427281</v>
+        <v>6384.016319177713</v>
       </c>
       <c r="E58">
         <v>8176.668000000001</v>
@@ -6049,37 +6049,37 @@
         <v>1497.6</v>
       </c>
       <c r="M58">
-        <v>3821.446103313713</v>
+        <v>3562.933583313712</v>
       </c>
       <c r="N58">
-        <v>-2323.846103313713</v>
+        <v>-2065.333583313712</v>
       </c>
       <c r="O58">
-        <v>-383.4346070467626</v>
+        <v>-340.7800412467625</v>
       </c>
       <c r="P58">
-        <v>-1940.41149626695</v>
+        <v>-1724.55354206695</v>
       </c>
       <c r="Q58">
-        <v>-1176.51149626695</v>
+        <v>-960.6535420669496</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1012886668197447</v>
+        <v>0.1011115594822169</v>
       </c>
       <c r="T58">
-        <v>1.081072290010306</v>
+        <v>1.078125245659932</v>
       </c>
       <c r="U58">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V58">
-        <v>0.06466243231475312</v>
+        <v>0.0693540853967254</v>
       </c>
       <c r="W58">
-        <v>0.2073985876958906</v>
+        <v>0.1923985876958906</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3918935291803219</v>
+        <v>0.4203277902831842</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1624695886770118</v>
+        <v>0.1538416614484995</v>
       </c>
       <c r="C59">
-        <v>-8556.612417868766</v>
+        <v>-8094.199663012712</v>
       </c>
       <c r="D59">
-        <v>5826.508582131236</v>
+        <v>6288.92133698729</v>
       </c>
       <c r="E59">
         <v>8484.421000000002</v>
@@ -6131,37 +6131,37 @@
         <v>1497.6</v>
       </c>
       <c r="M59">
-        <v>3889.686212301458</v>
+        <v>3626.557397301457</v>
       </c>
       <c r="N59">
-        <v>-2392.086212301458</v>
+        <v>-2128.957397301457</v>
       </c>
       <c r="O59">
-        <v>-394.6942250297406</v>
+        <v>-351.2779705547404</v>
       </c>
       <c r="P59">
-        <v>-1997.391987271717</v>
+        <v>-1777.679426746717</v>
       </c>
       <c r="Q59">
-        <v>-1233.491987271717</v>
+        <v>-1013.779426746717</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1025791009318318</v>
+        <v>0.1023978748190126</v>
       </c>
       <c r="T59">
-        <v>1.106213506057057</v>
+        <v>1.103197925791558</v>
       </c>
       <c r="U59">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V59">
-        <v>0.06352800367765218</v>
+        <v>0.06813734705643196</v>
       </c>
       <c r="W59">
-        <v>0.2076501320637265</v>
+        <v>0.1926501320637265</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.385018204106983</v>
+        <v>0.4129536185238301</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1642289548436371</v>
+        <v>0.1554510276151249</v>
       </c>
       <c r="C60">
-        <v>-8950.92332157135</v>
+        <v>-8494.256195815346</v>
       </c>
       <c r="D60">
-        <v>5739.950678428648</v>
+        <v>6196.617804184652</v>
       </c>
       <c r="E60">
         <v>8792.173999999999</v>
@@ -6213,37 +6213,37 @@
         <v>1497.6</v>
       </c>
       <c r="M60">
-        <v>3957.926321289201</v>
+        <v>3690.181211289201</v>
       </c>
       <c r="N60">
-        <v>-2460.326321289202</v>
+        <v>-2192.581211289201</v>
       </c>
       <c r="O60">
-        <v>-405.9538430127183</v>
+        <v>-361.7758998627182</v>
       </c>
       <c r="P60">
-        <v>-2054.372478276483</v>
+        <v>-1830.805311426483</v>
       </c>
       <c r="Q60">
-        <v>-1290.472478276483</v>
+        <v>-1066.905311426483</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1039309842873516</v>
+        <v>0.1037454432670843</v>
       </c>
       <c r="T60">
-        <v>1.132551922867939</v>
+        <v>1.129464543072309</v>
       </c>
       <c r="U60">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V60">
-        <v>0.06243269326941682</v>
+        <v>0.06696256521063143</v>
       </c>
       <c r="W60">
-        <v>0.2078930024878439</v>
+        <v>0.1928930024878439</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3783799592085868</v>
+        <v>0.4058337285492813</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1659883210102625</v>
+        <v>0.1570603937817502</v>
       </c>
       <c r="C61">
-        <v>-9342.700084752661</v>
+        <v>-8891.642413015037</v>
       </c>
       <c r="D61">
-        <v>5655.926915247337</v>
+        <v>6106.984586984961</v>
       </c>
       <c r="E61">
         <v>9099.927</v>
@@ -6295,37 +6295,37 @@
         <v>1497.6</v>
       </c>
       <c r="M61">
-        <v>4026.166430276947</v>
+        <v>3753.805025276946</v>
       </c>
       <c r="N61">
-        <v>-2528.566430276947</v>
+        <v>-2256.205025276946</v>
       </c>
       <c r="O61">
-        <v>-417.2134609956963</v>
+        <v>-372.2738291706962</v>
       </c>
       <c r="P61">
-        <v>-2111.352969281251</v>
+        <v>-1883.93119610625</v>
       </c>
       <c r="Q61">
-        <v>-1347.452969281251</v>
+        <v>-1120.03119610625</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.105348813172409</v>
+        <v>0.1051587467614035</v>
       </c>
       <c r="T61">
-        <v>1.160175140498864</v>
+        <v>1.157012458757</v>
       </c>
       <c r="U61">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V61">
-        <v>0.06137451202756228</v>
+        <v>0.06582760647824784</v>
       </c>
       <c r="W61">
-        <v>0.2081276400162284</v>
+        <v>0.1931276400162284</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3719667395609836</v>
+        <v>0.3989551907772596</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1677476871768878</v>
+        <v>0.1586697599483755</v>
       </c>
       <c r="C62">
-        <v>-9732.052389224569</v>
+        <v>-9286.472539597846</v>
       </c>
       <c r="D62">
-        <v>5574.327610775431</v>
+        <v>6019.907460402153</v>
       </c>
       <c r="E62">
         <v>9407.68</v>
@@ -6377,37 +6377,37 @@
         <v>1497.6</v>
       </c>
       <c r="M62">
-        <v>4094.406539264692</v>
+        <v>3817.428839264691</v>
       </c>
       <c r="N62">
-        <v>-2596.806539264692</v>
+        <v>-2319.828839264691</v>
       </c>
       <c r="O62">
-        <v>-428.4730789786742</v>
+        <v>-382.7717584786741</v>
       </c>
       <c r="P62">
-        <v>-2168.333460286018</v>
+        <v>-1937.057080786017</v>
       </c>
       <c r="Q62">
-        <v>-1404.433460286018</v>
+        <v>-1173.157080786017</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1068375335017192</v>
+        <v>0.1066427154304385</v>
       </c>
       <c r="T62">
-        <v>1.189179519011336</v>
+        <v>1.185937770225925</v>
       </c>
       <c r="U62">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V62">
-        <v>0.06035160349376958</v>
+        <v>0.06473047970361037</v>
       </c>
       <c r="W62">
-        <v>0.2083544562936669</v>
+        <v>0.1933544562936668</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3657672939016339</v>
+        <v>0.3923059375976385</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1695070533435131</v>
+        <v>0.1602791261150009</v>
       </c>
       <c r="C63">
-        <v>-10119.08367720424</v>
+        <v>-9678.854377376138</v>
       </c>
       <c r="D63">
-        <v>5495.049322795759</v>
+        <v>5935.278622623862</v>
       </c>
       <c r="E63">
         <v>9715.433000000001</v>
@@ -6459,37 +6459,37 @@
         <v>1497.6</v>
       </c>
       <c r="M63">
-        <v>4162.646648252437</v>
+        <v>3881.052653252436</v>
       </c>
       <c r="N63">
-        <v>-2665.046648252437</v>
+        <v>-2383.452653252436</v>
       </c>
       <c r="O63">
-        <v>-439.732696961652</v>
+        <v>-393.269687786652</v>
       </c>
       <c r="P63">
-        <v>-2225.313951290785</v>
+        <v>-1990.182965465784</v>
       </c>
       <c r="Q63">
-        <v>-1461.413951290785</v>
+        <v>-1226.282965465784</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1084025984633017</v>
+        <v>0.10820278505686</v>
       </c>
       <c r="T63">
-        <v>1.219671301550088</v>
+        <v>1.216346431000948</v>
       </c>
       <c r="U63">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V63">
-        <v>0.0593622329446914</v>
+        <v>0.06366932429863315</v>
       </c>
       <c r="W63">
-        <v>0.208573835971845</v>
+        <v>0.193573835971845</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3597711087557054</v>
+        <v>0.3858746927189888</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1712664195101385</v>
+        <v>0.1618884922816262</v>
       </c>
       <c r="C64">
-        <v>-10503.89158879102</v>
+        <v>-10068.88975021954</v>
       </c>
       <c r="D64">
-        <v>5417.994411208973</v>
+        <v>5852.996249780456</v>
       </c>
       <c r="E64">
         <v>10023.186</v>
@@ -6541,37 +6541,37 @@
         <v>1497.6</v>
       </c>
       <c r="M64">
-        <v>4230.88675724018</v>
+        <v>3944.676467240181</v>
       </c>
       <c r="N64">
-        <v>-2733.286757240181</v>
+        <v>-2447.076467240181</v>
       </c>
       <c r="O64">
-        <v>-450.9923149446298</v>
+        <v>-403.7676170946298</v>
       </c>
       <c r="P64">
-        <v>-2282.294442295551</v>
+        <v>-2043.308850145551</v>
       </c>
       <c r="Q64">
-        <v>-1518.394442295551</v>
+        <v>-1279.408850145551</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1100500352649676</v>
+        <v>0.1098449636109879</v>
       </c>
       <c r="T64">
-        <v>1.251767914748775</v>
+        <v>1.248355547606236</v>
       </c>
       <c r="U64">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V64">
-        <v>0.05840477757461574</v>
+        <v>0.06264239971317133</v>
       </c>
       <c r="W64">
-        <v>0.208786138886211</v>
+        <v>0.193786138886211</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3539683489370651</v>
+        <v>0.3796509073525536</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1730257856767638</v>
+        <v>0.1634978584482516</v>
       </c>
       <c r="C65">
-        <v>-10886.56836314495</v>
+        <v>-10456.67491275819</v>
       </c>
       <c r="D65">
-        <v>5343.070636855048</v>
+        <v>5772.964087241804</v>
       </c>
       <c r="E65">
         <v>10330.939</v>
@@ -6623,37 +6623,37 @@
         <v>1497.6</v>
       </c>
       <c r="M65">
-        <v>4299.126866227926</v>
+        <v>4008.300281227926</v>
       </c>
       <c r="N65">
-        <v>-2801.526866227926</v>
+        <v>-2510.700281227926</v>
       </c>
       <c r="O65">
-        <v>-462.2519329276079</v>
+        <v>-414.2655464026078</v>
       </c>
       <c r="P65">
-        <v>-2339.274933300318</v>
+        <v>-2096.434734825318</v>
       </c>
       <c r="Q65">
-        <v>-1575.374933300318</v>
+        <v>-1332.534734825318</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1117865227045613</v>
+        <v>0.1115759085734471</v>
       </c>
       <c r="T65">
-        <v>1.285599480012255</v>
+        <v>1.282094886730729</v>
       </c>
       <c r="U65">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V65">
-        <v>0.05747771761311389</v>
+        <v>0.06164807590820035</v>
       </c>
       <c r="W65">
-        <v>0.2089917020255177</v>
+        <v>0.1939917020255177</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3483498037158418</v>
+        <v>0.3736247024739415</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1747851518433892</v>
+        <v>0.1651072246148769</v>
       </c>
       <c r="C66">
-        <v>-11267.20120683258</v>
+        <v>-10842.30092600731</v>
       </c>
       <c r="D66">
-        <v>5270.190793167415</v>
+        <v>5695.091073992686</v>
       </c>
       <c r="E66">
         <v>10638.692</v>
@@ -6705,37 +6705,37 @@
         <v>1497.6</v>
       </c>
       <c r="M66">
-        <v>4367.366975215671</v>
+        <v>4071.924095215671</v>
       </c>
       <c r="N66">
-        <v>-2869.766975215671</v>
+        <v>-2574.324095215671</v>
       </c>
       <c r="O66">
-        <v>-473.5115509105858</v>
+        <v>-424.7634757105857</v>
       </c>
       <c r="P66">
-        <v>-2396.255424305085</v>
+        <v>-2149.560619505085</v>
       </c>
       <c r="Q66">
-        <v>-1632.355424305085</v>
+        <v>-1385.660619505085</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1136194816685769</v>
+        <v>0.1134030171449317</v>
       </c>
       <c r="T66">
-        <v>1.321310576679262</v>
+        <v>1.317708633584361</v>
       </c>
       <c r="U66">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V66">
-        <v>0.05657962827540899</v>
+        <v>0.06068482472213473</v>
       </c>
       <c r="W66">
-        <v>0.2091908413167211</v>
+        <v>0.194190841316721</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3429068380327817</v>
+        <v>0.3677868164977862</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1765445180100145</v>
+        <v>0.1667165907815022</v>
       </c>
       <c r="C67">
-        <v>-11645.87263243303</v>
+        <v>-11225.85400299506</v>
       </c>
       <c r="D67">
-        <v>5199.272367566969</v>
+        <v>5619.290997004938</v>
       </c>
       <c r="E67">
         <v>10946.445</v>
@@ -6787,37 +6787,37 @@
         <v>1497.6</v>
       </c>
       <c r="M67">
-        <v>4435.607084203416</v>
+        <v>4135.547909203416</v>
       </c>
       <c r="N67">
-        <v>-2938.007084203416</v>
+        <v>-2637.947909203416</v>
       </c>
       <c r="O67">
-        <v>-484.7711688935637</v>
+        <v>-435.2614050185636</v>
       </c>
       <c r="P67">
-        <v>-2453.235915309852</v>
+        <v>-2202.686504184852</v>
       </c>
       <c r="Q67">
-        <v>-1689.335915309852</v>
+        <v>-1438.786504184852</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1155571811448219</v>
+        <v>0.1153345319205012</v>
       </c>
       <c r="T67">
-        <v>1.359062307441527</v>
+        <v>1.355357451686771</v>
       </c>
       <c r="U67">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V67">
-        <v>0.05570917245578731</v>
+        <v>0.05975121203410188</v>
       </c>
       <c r="W67">
-        <v>0.2093838532451182</v>
+        <v>0.1943838532451182</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3376313482168928</v>
+        <v>0.3621285577824356</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1783038841766398</v>
+        <v>0.1683259569481276</v>
       </c>
       <c r="C68">
-        <v>-12022.66077016811</v>
+        <v>-11607.41582715165</v>
       </c>
       <c r="D68">
-        <v>5130.23722983189</v>
+        <v>5545.482172848348</v>
       </c>
       <c r="E68">
         <v>11254.198</v>
@@ -6869,37 +6869,37 @@
         <v>1497.6</v>
       </c>
       <c r="M68">
-        <v>4503.847193191161</v>
+        <v>4199.171723191161</v>
       </c>
       <c r="N68">
-        <v>-3006.247193191161</v>
+        <v>-2701.571723191161</v>
       </c>
       <c r="O68">
-        <v>-496.0307868765416</v>
+        <v>-445.7593343265415</v>
       </c>
       <c r="P68">
-        <v>-2510.216406314619</v>
+        <v>-2255.812388864619</v>
       </c>
       <c r="Q68">
-        <v>-1746.316406314619</v>
+        <v>-1491.912388864619</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1176088629431991</v>
+        <v>0.1173796652122807</v>
       </c>
       <c r="T68">
-        <v>1.399034728248631</v>
+        <v>1.395220906148147</v>
       </c>
       <c r="U68">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V68">
-        <v>0.05486509408524508</v>
+        <v>0.05884589063964579</v>
       </c>
       <c r="W68">
-        <v>0.2095710163272002</v>
+        <v>0.1945710163272003</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.332515721728758</v>
+        <v>0.3566417614523987</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1800632503432652</v>
+        <v>0.169935323114753</v>
       </c>
       <c r="C69">
-        <v>-12397.63965503125</v>
+        <v>-11987.06384593173</v>
       </c>
       <c r="D69">
-        <v>5063.011344968746</v>
+        <v>5473.587154068271</v>
       </c>
       <c r="E69">
         <v>11561.951</v>
@@ -6951,37 +6951,37 @@
         <v>1497.6</v>
       </c>
       <c r="M69">
-        <v>4572.087302178906</v>
+        <v>4262.795537178906</v>
       </c>
       <c r="N69">
-        <v>-3074.487302178906</v>
+        <v>-2765.195537178906</v>
       </c>
       <c r="O69">
-        <v>-507.2904048595195</v>
+        <v>-456.2572636345195</v>
       </c>
       <c r="P69">
-        <v>-2567.196897319386</v>
+        <v>-2308.938273544386</v>
       </c>
       <c r="Q69">
-        <v>-1803.296897319386</v>
+        <v>-1545.038273544386</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.119784889092993</v>
+        <v>0.1195487459762892</v>
       </c>
       <c r="T69">
-        <v>1.441429720013741</v>
+        <v>1.437500327546576</v>
       </c>
       <c r="U69">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V69">
-        <v>0.05404621208397276</v>
+        <v>0.05796759376442719</v>
       </c>
       <c r="W69">
-        <v>0.2097525924516082</v>
+        <v>0.1947525924516082</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3275528005089258</v>
+        <v>0.3513187500874375</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1818226165098905</v>
+        <v>0.1715446892813783</v>
       </c>
       <c r="C70">
-        <v>-12770.87949163339</v>
+        <v>-12364.87154188888</v>
       </c>
       <c r="D70">
-        <v>4997.52450836661</v>
+        <v>5403.532458111125</v>
       </c>
       <c r="E70">
         <v>11869.704</v>
@@ -7033,37 +7033,37 @@
         <v>1497.6</v>
       </c>
       <c r="M70">
-        <v>4640.327411166651</v>
+        <v>4326.419351166651</v>
       </c>
       <c r="N70">
-        <v>-3142.727411166651</v>
+        <v>-2828.819351166651</v>
       </c>
       <c r="O70">
-        <v>-518.5500228424974</v>
+        <v>-466.7551929424974</v>
       </c>
       <c r="P70">
-        <v>-2624.177388324153</v>
+        <v>-2362.064158224153</v>
       </c>
       <c r="Q70">
-        <v>-1860.277388324153</v>
+        <v>-1598.164158224153</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.122096916877149</v>
+        <v>0.1218533942880482</v>
       </c>
       <c r="T70">
-        <v>1.48647439876417</v>
+        <v>1.482422212782406</v>
       </c>
       <c r="U70">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V70">
-        <v>0.05325141484744375</v>
+        <v>0.05711512915024444</v>
       </c>
       <c r="W70">
-        <v>0.2099288281017689</v>
+        <v>0.1949288281017689</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3227358475602652</v>
+        <v>0.3461522978802692</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1835819826765159</v>
+        <v>0.1731540554480036</v>
       </c>
       <c r="C71">
-        <v>-13142.44689875761</v>
+        <v>-12740.90868319678</v>
       </c>
       <c r="D71">
-        <v>4933.710101242391</v>
+        <v>5335.248316803225</v>
       </c>
       <c r="E71">
         <v>12177.457</v>
@@ -7115,37 +7115,37 @@
         <v>1497.6</v>
       </c>
       <c r="M71">
-        <v>4708.567520154395</v>
+        <v>4390.043165154396</v>
       </c>
       <c r="N71">
-        <v>-3210.967520154396</v>
+        <v>-2892.443165154396</v>
       </c>
       <c r="O71">
-        <v>-529.8096408254753</v>
+        <v>-477.2531222504754</v>
       </c>
       <c r="P71">
-        <v>-2681.15787932892</v>
+        <v>-2415.190042903921</v>
       </c>
       <c r="Q71">
-        <v>-1917.25787932892</v>
+        <v>-1651.29004290392</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1245581077441538</v>
+        <v>0.1243067295876627</v>
       </c>
       <c r="T71">
-        <v>1.534425185821079</v>
+        <v>1.530242284162484</v>
       </c>
       <c r="U71">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V71">
-        <v>0.05247965521197355</v>
+        <v>0.05628737365531335</v>
       </c>
       <c r="W71">
-        <v>0.2100999554722148</v>
+        <v>0.1950999554722148</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3180585164362033</v>
+        <v>0.34113559791099</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1853413488431412</v>
+        <v>0.174763421614629</v>
       </c>
       <c r="C72">
-        <v>-13512.40513541346</v>
+        <v>-13115.24155541253</v>
       </c>
       <c r="D72">
-        <v>4871.504864586544</v>
+        <v>5268.668444587474</v>
       </c>
       <c r="E72">
         <v>12485.21</v>
@@ -7197,37 +7197,37 @@
         <v>1497.6</v>
       </c>
       <c r="M72">
-        <v>4776.807629142141</v>
+        <v>4453.66697914214</v>
       </c>
       <c r="N72">
-        <v>-3279.207629142141</v>
+        <v>-2956.06697914214</v>
       </c>
       <c r="O72">
-        <v>-541.0692588084534</v>
+        <v>-487.7510515584531</v>
       </c>
       <c r="P72">
-        <v>-2738.138370333688</v>
+        <v>-2468.315927583687</v>
       </c>
       <c r="Q72">
-        <v>-1974.238370333688</v>
+        <v>-1704.415927583687</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1271833780022923</v>
+        <v>0.1269236205739181</v>
       </c>
       <c r="T72">
-        <v>1.585572692015115</v>
+        <v>1.581250360301233</v>
       </c>
       <c r="U72">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V72">
-        <v>0.05172994585180249</v>
+        <v>0.05548326831738031</v>
       </c>
       <c r="W72">
-        <v>0.2102661934892193</v>
+        <v>0.1952661934892193</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3135148233442575</v>
+        <v>0.3362622322265474</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1871007150097665</v>
+        <v>0.1763727877812543</v>
       </c>
       <c r="C73">
-        <v>-13880.81431000331</v>
+        <v>-13487.9331761004</v>
       </c>
       <c r="D73">
-        <v>4810.848689996686</v>
+        <v>5203.729823899596</v>
       </c>
       <c r="E73">
         <v>12792.963</v>
@@ -7279,37 +7279,37 @@
         <v>1497.6</v>
       </c>
       <c r="M73">
-        <v>4845.047738129885</v>
+        <v>4517.290793129885</v>
       </c>
       <c r="N73">
-        <v>-3347.447738129885</v>
+        <v>-3019.690793129885</v>
       </c>
       <c r="O73">
-        <v>-552.3288767914311</v>
+        <v>-498.2489808664311</v>
       </c>
       <c r="P73">
-        <v>-2795.118861338454</v>
+        <v>-2521.441812263454</v>
       </c>
       <c r="Q73">
-        <v>-2031.218861338454</v>
+        <v>-1757.541812263454</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1299897013816816</v>
+        <v>0.1297209868006049</v>
       </c>
       <c r="T73">
-        <v>1.640247612429429</v>
+        <v>1.635776234794379</v>
       </c>
       <c r="U73">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V73">
-        <v>0.0510013550651574</v>
+        <v>0.05470181383403693</v>
       </c>
       <c r="W73">
-        <v>0.2104277487451815</v>
+        <v>0.1954277487451815</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3090991216070145</v>
+        <v>0.3315261444487086</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1888600811763919</v>
+        <v>0.1779821539478796</v>
       </c>
       <c r="C74">
-        <v>-14247.73157405471</v>
+        <v>-13859.04349377693</v>
       </c>
       <c r="D74">
-        <v>4751.684425945291</v>
+        <v>5140.37250622307</v>
       </c>
       <c r="E74">
         <v>13100.716</v>
@@ -7361,37 +7361,37 @@
         <v>1497.6</v>
       </c>
       <c r="M74">
-        <v>4913.28784711763</v>
+        <v>4580.91460711763</v>
       </c>
       <c r="N74">
-        <v>-3415.68784711763</v>
+        <v>-3083.31460711763</v>
       </c>
       <c r="O74">
-        <v>-563.588494774409</v>
+        <v>-508.746910174409</v>
       </c>
       <c r="P74">
-        <v>-2852.099352343221</v>
+        <v>-2574.567696943221</v>
       </c>
       <c r="Q74">
-        <v>-2088.199352343221</v>
+        <v>-1810.667696943221</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1329964764310274</v>
+        <v>0.1327181649006265</v>
       </c>
       <c r="T74">
-        <v>1.698827884301908</v>
+        <v>1.694196814608464</v>
       </c>
       <c r="U74">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V74">
-        <v>0.05029300291147466</v>
+        <v>0.0539420664196753</v>
       </c>
       <c r="W74">
-        <v>0.2105848163551448</v>
+        <v>0.1955848163551447</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3048060782513615</v>
+        <v>0.3269216146646988</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1906194473430172</v>
+        <v>0.179591520114505</v>
       </c>
       <c r="C75">
-        <v>-14613.21130183103</v>
+        <v>-14228.62957249736</v>
       </c>
       <c r="D75">
-        <v>4693.957698168964</v>
+        <v>5078.539427502638</v>
       </c>
       <c r="E75">
         <v>13408.469</v>
@@ -7443,37 +7443,37 @@
         <v>1497.6</v>
       </c>
       <c r="M75">
-        <v>4981.527956105374</v>
+        <v>4644.538421105374</v>
       </c>
       <c r="N75">
-        <v>-3483.927956105374</v>
+        <v>-3146.938421105374</v>
       </c>
       <c r="O75">
-        <v>-574.8481127573867</v>
+        <v>-519.2448394823867</v>
       </c>
       <c r="P75">
-        <v>-2909.079843347987</v>
+        <v>-2627.693581622987</v>
       </c>
       <c r="Q75">
-        <v>-2145.179843347987</v>
+        <v>-1863.793581622987</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1362259755581025</v>
+        <v>0.1359373561932423</v>
       </c>
       <c r="T75">
-        <v>1.761747435572349</v>
+        <v>1.756944844779148</v>
       </c>
       <c r="U75">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V75">
-        <v>0.04960405766611199</v>
+        <v>0.05320313400296742</v>
       </c>
       <c r="W75">
-        <v>0.2107375807429172</v>
+        <v>0.1957375807429172</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3006306525218909</v>
+        <v>0.3224432363816208</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1923788135096426</v>
+        <v>0.1812008862811303</v>
       </c>
       <c r="C76">
-        <v>-14977.30525700725</v>
+        <v>-14596.74576327829</v>
       </c>
       <c r="D76">
-        <v>4637.616742992751</v>
+        <v>5018.176236721704</v>
       </c>
       <c r="E76">
         <v>13716.222</v>
@@ -7525,37 +7525,37 @@
         <v>1497.6</v>
       </c>
       <c r="M76">
-        <v>5049.768065093119</v>
+        <v>4708.162235093119</v>
       </c>
       <c r="N76">
-        <v>-3552.168065093119</v>
+        <v>-3210.562235093119</v>
       </c>
       <c r="O76">
-        <v>-586.1077307403647</v>
+        <v>-529.7427687903647</v>
       </c>
       <c r="P76">
-        <v>-2966.060334352754</v>
+        <v>-2680.819466302755</v>
       </c>
       <c r="Q76">
-        <v>-2202.160334352754</v>
+        <v>-1916.919466302755</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1397038976949526</v>
+        <v>0.1394041775852901</v>
       </c>
       <c r="T76">
-        <v>1.829506952325132</v>
+        <v>1.824519646501422</v>
       </c>
       <c r="U76">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V76">
-        <v>0.04893373256251589</v>
+        <v>0.05248417273265706</v>
       </c>
       <c r="W76">
-        <v>0.2108862163634526</v>
+        <v>0.1958862163634525</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2965680761364599</v>
+        <v>0.3180858953494367</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1941381796762679</v>
+        <v>0.1828102524477556</v>
       </c>
       <c r="C77">
-        <v>-15340.06274748437</v>
+        <v>-14963.44386343876</v>
       </c>
       <c r="D77">
-        <v>4582.612252515632</v>
+        <v>4959.23113656124</v>
       </c>
       <c r="E77">
         <v>14023.975</v>
@@ -7607,37 +7607,37 @@
         <v>1497.6</v>
       </c>
       <c r="M77">
-        <v>5118.008174080864</v>
+        <v>4771.786049080863</v>
       </c>
       <c r="N77">
-        <v>-3620.408174080864</v>
+        <v>-3274.186049080864</v>
       </c>
       <c r="O77">
-        <v>-597.3673487233425</v>
+        <v>-540.2406980983425</v>
       </c>
       <c r="P77">
-        <v>-3023.040825357521</v>
+        <v>-2733.945350982521</v>
       </c>
       <c r="Q77">
-        <v>-2259.140825357521</v>
+        <v>-1970.045350982521</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1434600536027507</v>
+        <v>0.1431483446887017</v>
       </c>
       <c r="T77">
-        <v>1.902687230418138</v>
+        <v>1.897500432361479</v>
       </c>
       <c r="U77">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V77">
-        <v>0.04828128279501568</v>
+        <v>0.0517843837628883</v>
       </c>
       <c r="W77">
-        <v>0.2110308883674403</v>
+        <v>0.1960308883674403</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2926138351213071</v>
+        <v>0.313844750078111</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1958975458428933</v>
+        <v>0.184419618614381</v>
       </c>
       <c r="C78">
-        <v>-15701.53076931609</v>
+        <v>-15328.77326484164</v>
       </c>
       <c r="D78">
-        <v>4528.89723068391</v>
+        <v>4901.654735158355</v>
       </c>
       <c r="E78">
         <v>14331.728</v>
@@ -7689,37 +7689,37 @@
         <v>1497.6</v>
       </c>
       <c r="M78">
-        <v>5186.248283068609</v>
+        <v>4835.409863068609</v>
       </c>
       <c r="N78">
-        <v>-3688.64828306861</v>
+        <v>-3337.809863068609</v>
       </c>
       <c r="O78">
-        <v>-608.6269667063206</v>
+        <v>-550.7386274063205</v>
       </c>
       <c r="P78">
-        <v>-3080.021316362289</v>
+        <v>-2787.071235662288</v>
       </c>
       <c r="Q78">
-        <v>-2316.121316362289</v>
+        <v>-2023.171235662288</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1475292225028653</v>
+        <v>0.1472045257173976</v>
       </c>
       <c r="T78">
-        <v>1.981965865018894</v>
+        <v>1.976562950376541</v>
       </c>
       <c r="U78">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V78">
-        <v>0.04764600275823914</v>
+        <v>0.05110301029232398</v>
       </c>
       <c r="W78">
-        <v>0.2111717532134284</v>
+        <v>0.1961717532134284</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2887636530802372</v>
+        <v>0.3097152138928726</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.1976569120095186</v>
+        <v>0.1860289847810063</v>
       </c>
       <c r="C79">
-        <v>-16061.75414063043</v>
+        <v>-15692.78109192723</v>
       </c>
       <c r="D79">
-        <v>4476.426859369571</v>
+        <v>4845.399908072769</v>
       </c>
       <c r="E79">
         <v>14639.481</v>
@@ -7771,37 +7771,37 @@
         <v>1497.6</v>
       </c>
       <c r="M79">
-        <v>5254.488392056354</v>
+        <v>4899.033677056354</v>
       </c>
       <c r="N79">
-        <v>-3756.888392056354</v>
+        <v>-3401.433677056354</v>
       </c>
       <c r="O79">
-        <v>-619.8865846892985</v>
+        <v>-561.2365567142983</v>
       </c>
       <c r="P79">
-        <v>-3137.001807367056</v>
+        <v>-2840.197120342055</v>
       </c>
       <c r="Q79">
-        <v>-2373.101807367056</v>
+        <v>-2076.297120342055</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.151952232176903</v>
+        <v>0.1516134181398931</v>
       </c>
       <c r="T79">
-        <v>2.068138293932758</v>
+        <v>2.06250046995813</v>
       </c>
       <c r="U79">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V79">
-        <v>0.04702722350163863</v>
+        <v>0.05043933483398211</v>
       </c>
       <c r="W79">
-        <v>0.2113089592322479</v>
+        <v>0.1963089592322479</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2850134757675069</v>
+        <v>0.3056929383877703</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1994162781761439</v>
+        <v>0.1876383509476317</v>
       </c>
       <c r="C80">
-        <v>-16420.77562634857</v>
+        <v>-16055.51233034951</v>
       </c>
       <c r="D80">
-        <v>4425.158373651427</v>
+        <v>4790.42166965049</v>
       </c>
       <c r="E80">
         <v>14947.234</v>
@@ -7853,37 +7853,37 @@
         <v>1497.6</v>
       </c>
       <c r="M80">
-        <v>5322.728501044099</v>
+        <v>4962.657491044099</v>
       </c>
       <c r="N80">
-        <v>-3825.128501044099</v>
+        <v>-3465.057491044099</v>
       </c>
       <c r="O80">
-        <v>-631.1462026722764</v>
+        <v>-571.7344860222763</v>
       </c>
       <c r="P80">
-        <v>-3193.982298371823</v>
+        <v>-2893.323005021823</v>
       </c>
       <c r="Q80">
-        <v>-2430.082298371823</v>
+        <v>-2129.423005021823</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1567773336394895</v>
+        <v>0.1564231189644338</v>
       </c>
       <c r="T80">
-        <v>2.162144580020612</v>
+        <v>2.156250491319863</v>
       </c>
       <c r="U80">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V80">
-        <v>0.04642431037982276</v>
+        <v>0.0497926766950849</v>
       </c>
       <c r="W80">
-        <v>0.2114426471480209</v>
+        <v>0.1964426471480208</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2813594568474106</v>
+        <v>0.3017737981520296</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2011756443427693</v>
+        <v>0.189247717114257</v>
       </c>
       <c r="C81">
-        <v>-16778.63605443032</v>
+        <v>-16417.00994695337</v>
       </c>
       <c r="D81">
-        <v>4375.050945569677</v>
+        <v>4736.677053046633</v>
       </c>
       <c r="E81">
         <v>15254.987</v>
@@ -7935,37 +7935,37 @@
         <v>1497.6</v>
       </c>
       <c r="M81">
-        <v>5390.968610031844</v>
+        <v>5026.281305031844</v>
       </c>
       <c r="N81">
-        <v>-3893.368610031844</v>
+        <v>-3528.681305031844</v>
       </c>
       <c r="O81">
-        <v>-642.4058206552543</v>
+        <v>-582.2324153302543</v>
       </c>
       <c r="P81">
-        <v>-3250.96278937659</v>
+        <v>-2946.448889701589</v>
       </c>
       <c r="Q81">
-        <v>-2487.06278937659</v>
+        <v>-2182.548889701589</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1620619685747033</v>
+        <v>0.1616908865341687</v>
       </c>
       <c r="T81">
-        <v>2.265103845735879</v>
+        <v>2.258929086144619</v>
       </c>
       <c r="U81">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V81">
-        <v>0.04583666088134399</v>
+        <v>0.04916238964831167</v>
       </c>
       <c r="W81">
-        <v>0.211572950559597</v>
+        <v>0.1965729505595969</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2777979447354181</v>
+        <v>0.2979538766564344</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2029350105093946</v>
+        <v>0.1908570832808824</v>
       </c>
       <c r="C82">
-        <v>-17135.37442431031</v>
+        <v>-16777.31500176508</v>
       </c>
       <c r="D82">
-        <v>4326.065575689695</v>
+        <v>4684.12499823492</v>
       </c>
       <c r="E82">
         <v>15562.74</v>
@@ -8017,37 +8017,37 @@
         <v>1497.6</v>
       </c>
       <c r="M82">
-        <v>5459.208719019589</v>
+        <v>5089.905119019589</v>
       </c>
       <c r="N82">
-        <v>-3961.608719019589</v>
+        <v>-3592.305119019589</v>
       </c>
       <c r="O82">
-        <v>-653.6654386382322</v>
+        <v>-592.7303446382322</v>
       </c>
       <c r="P82">
-        <v>-3307.943280381357</v>
+        <v>-2999.574774381357</v>
       </c>
       <c r="Q82">
-        <v>-2544.043280381357</v>
+        <v>-2235.674774381357</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.1678750670034384</v>
+        <v>0.1674854308608771</v>
       </c>
       <c r="T82">
-        <v>2.378359038022672</v>
+        <v>2.37187554045185</v>
       </c>
       <c r="U82">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V82">
-        <v>0.04526370262032718</v>
+        <v>0.04854785977770777</v>
       </c>
       <c r="W82">
-        <v>0.2116999963858837</v>
+        <v>0.1966999963858836</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2743254704262253</v>
+        <v>0.2942294531982289</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.20469437667602</v>
+        <v>0.1924664494475077</v>
       </c>
       <c r="C83">
-        <v>-17491.02800813015</v>
+        <v>-17136.46675260961</v>
       </c>
       <c r="D83">
-        <v>4278.164991869854</v>
+        <v>4632.726247390397</v>
       </c>
       <c r="E83">
         <v>15870.493</v>
@@ -8099,37 +8099,37 @@
         <v>1497.6</v>
       </c>
       <c r="M83">
-        <v>5527.448828007334</v>
+        <v>5153.528933007334</v>
       </c>
       <c r="N83">
-        <v>-4029.848828007334</v>
+        <v>-3655.928933007334</v>
       </c>
       <c r="O83">
-        <v>-664.9250566212102</v>
+        <v>-603.2282739462102</v>
       </c>
       <c r="P83">
-        <v>-3364.923771386124</v>
+        <v>-3052.700659061124</v>
       </c>
       <c r="Q83">
-        <v>-2601.023771386124</v>
+        <v>-2288.800659061123</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.1743000705299352</v>
+        <v>0.1738899272219759</v>
       </c>
       <c r="T83">
-        <v>2.50353582949755</v>
+        <v>2.496711095212474</v>
       </c>
       <c r="U83">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V83">
-        <v>0.04470489147686636</v>
+        <v>0.04794850348415583</v>
       </c>
       <c r="W83">
-        <v>0.211823905278188</v>
+        <v>0.196823905278188</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2709387362234325</v>
+        <v>0.2905969908130656</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2064537428426453</v>
+        <v>0.1940758156141331</v>
       </c>
       <c r="C84">
-        <v>-17845.63244531894</v>
+        <v>-17494.50275291486</v>
       </c>
       <c r="D84">
-        <v>4231.313554681061</v>
+        <v>4582.443247085143</v>
       </c>
       <c r="E84">
         <v>16178.246</v>
@@ -8181,37 +8181,37 @@
         <v>1497.6</v>
       </c>
       <c r="M84">
-        <v>5595.68893699508</v>
+        <v>5217.152746995079</v>
       </c>
       <c r="N84">
-        <v>-4098.08893699508</v>
+        <v>-3719.552746995079</v>
       </c>
       <c r="O84">
-        <v>-676.1846746041882</v>
+        <v>-613.726203254188</v>
       </c>
       <c r="P84">
-        <v>-3421.904262390892</v>
+        <v>-3105.826543740891</v>
       </c>
       <c r="Q84">
-        <v>-2658.004262390892</v>
+        <v>-2341.926543740891</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.1814389633371538</v>
+        <v>0.1810060342898635</v>
       </c>
       <c r="T84">
-        <v>2.642621153358525</v>
+        <v>2.635417267168723</v>
       </c>
       <c r="U84">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V84">
-        <v>0.04415970987348994</v>
+        <v>0.04736376563678807</v>
       </c>
       <c r="W84">
-        <v>0.2119447920023874</v>
+        <v>0.1969447920023873</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2676346052938783</v>
+        <v>0.2870531250714429</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2082131090092707</v>
+        <v>0.1956851817807584</v>
       </c>
       <c r="C85">
-        <v>-18199.22183102635</v>
+        <v>-17851.45894321506</v>
       </c>
       <c r="D85">
-        <v>4185.477168973647</v>
+        <v>4533.240056784934</v>
       </c>
       <c r="E85">
         <v>16485.999</v>
@@ -8263,37 +8263,37 @@
         <v>1497.6</v>
       </c>
       <c r="M85">
-        <v>5663.929045982823</v>
+        <v>5280.776560982823</v>
       </c>
       <c r="N85">
-        <v>-4166.329045982824</v>
+        <v>-3783.176560982823</v>
       </c>
       <c r="O85">
-        <v>-687.444292587166</v>
+        <v>-624.2241325621658</v>
       </c>
       <c r="P85">
-        <v>-3478.884753395658</v>
+        <v>-3158.952428420657</v>
       </c>
       <c r="Q85">
-        <v>-2714.984753395658</v>
+        <v>-2395.052428420657</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.1894177258863982</v>
+        <v>0.1889593304245614</v>
       </c>
       <c r="T85">
-        <v>2.798069456497263</v>
+        <v>2.790441812296295</v>
       </c>
       <c r="U85">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V85">
-        <v>0.04362766517621898</v>
+        <v>0.04679311785803159</v>
       </c>
       <c r="W85">
-        <v>0.2120627657934735</v>
+        <v>0.1970627657934734</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2644100919770846</v>
+        <v>0.28359465368504</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.209972475175896</v>
+        <v>0.1972945479473837</v>
       </c>
       <c r="C86">
-        <v>-18551.82879886953</v>
+        <v>-18207.3697368217</v>
       </c>
       <c r="D86">
-        <v>4140.623201130467</v>
+        <v>4485.0822631783</v>
       </c>
       <c r="E86">
         <v>16793.752</v>
@@ -8345,37 +8345,37 @@
         <v>1497.6</v>
       </c>
       <c r="M86">
-        <v>5732.169154970567</v>
+        <v>5344.400374970567</v>
       </c>
       <c r="N86">
-        <v>-4234.569154970568</v>
+        <v>-3846.800374970567</v>
       </c>
       <c r="O86">
-        <v>-698.7039105701438</v>
+        <v>-634.7220618701436</v>
       </c>
       <c r="P86">
-        <v>-3535.865244400424</v>
+        <v>-3212.078313100424</v>
       </c>
       <c r="Q86">
-        <v>-2771.965244400424</v>
+        <v>-2448.178313100424</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.1983938337542979</v>
+        <v>0.1979067885760963</v>
       </c>
       <c r="T86">
-        <v>2.97294879752834</v>
+        <v>2.964844425564811</v>
       </c>
       <c r="U86">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V86">
-        <v>0.04310828820983543</v>
+        <v>0.04623605693115027</v>
       </c>
       <c r="W86">
-        <v>0.2121779306847718</v>
+        <v>0.1971779306847718</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2612623527868813</v>
+        <v>0.2802185268554562</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2117318413425213</v>
+        <v>0.1989039141140091</v>
       </c>
       <c r="C87">
-        <v>-18903.48459841585</v>
+        <v>-18562.26810009121</v>
       </c>
       <c r="D87">
-        <v>4096.720401584144</v>
+        <v>4437.936899908784</v>
       </c>
       <c r="E87">
         <v>17101.505</v>
@@ -8427,37 +8427,37 @@
         <v>1497.6</v>
       </c>
       <c r="M87">
-        <v>5800.409263958312</v>
+        <v>5408.024188958312</v>
       </c>
       <c r="N87">
-        <v>-4302.809263958312</v>
+        <v>-3910.424188958312</v>
       </c>
       <c r="O87">
-        <v>-709.9635285531215</v>
+        <v>-645.2199911781215</v>
       </c>
       <c r="P87">
-        <v>-3592.845735405191</v>
+        <v>-3265.204197780191</v>
       </c>
       <c r="Q87">
-        <v>-2828.945735405191</v>
+        <v>-2501.304197780191</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2085667560045845</v>
+        <v>0.2080472411478361</v>
       </c>
       <c r="T87">
-        <v>3.171145384030229</v>
+        <v>3.162500720602466</v>
       </c>
       <c r="U87">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V87">
-        <v>0.04260113187795501</v>
+        <v>0.04569210332019556</v>
       </c>
       <c r="W87">
-        <v>0.2122903858139219</v>
+        <v>0.1972903858139219</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2581886780482122</v>
+        <v>0.2769218383042155</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2134912075091467</v>
+        <v>0.2005132802806344</v>
       </c>
       <c r="C88">
-        <v>-19254.21916778811</v>
+        <v>-18916.18562768301</v>
       </c>
       <c r="D88">
-        <v>4053.738832211892</v>
+        <v>4391.772372316989</v>
       </c>
       <c r="E88">
         <v>17409.258</v>
@@ -8509,37 +8509,37 @@
         <v>1497.6</v>
       </c>
       <c r="M88">
-        <v>5868.649372946057</v>
+        <v>5471.648002946057</v>
       </c>
       <c r="N88">
-        <v>-4371.049372946058</v>
+        <v>-3974.048002946057</v>
       </c>
       <c r="O88">
-        <v>-721.2231465360995</v>
+        <v>-655.7179204860995</v>
       </c>
       <c r="P88">
-        <v>-3649.826226409958</v>
+        <v>-3318.330082459958</v>
       </c>
       <c r="Q88">
-        <v>-2885.926226409958</v>
+        <v>-2554.430082459958</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2201929528620548</v>
+        <v>0.219636329801253</v>
       </c>
       <c r="T88">
-        <v>3.397655768603817</v>
+        <v>3.388393629216928</v>
       </c>
       <c r="U88">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V88">
-        <v>0.04210576987937414</v>
+        <v>0.04516079979321654</v>
       </c>
       <c r="W88">
-        <v>0.2124002257075105</v>
+        <v>0.1974002257075105</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.255186484117419</v>
+        <v>0.2737018169285851</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.215250573675772</v>
+        <v>0.2021226464472597</v>
       </c>
       <c r="C89">
-        <v>-19604.06120174662</v>
+        <v>-19269.15261316854</v>
       </c>
       <c r="D89">
-        <v>4011.649798253382</v>
+        <v>4346.558386831461</v>
       </c>
       <c r="E89">
         <v>17717.011</v>
@@ -8591,37 +8591,37 @@
         <v>1497.6</v>
       </c>
       <c r="M89">
-        <v>5936.889481933802</v>
+        <v>5535.271816933802</v>
       </c>
       <c r="N89">
-        <v>-4439.289481933802</v>
+        <v>-4037.671816933802</v>
       </c>
       <c r="O89">
-        <v>-732.4827645190774</v>
+        <v>-666.2158497940774</v>
       </c>
       <c r="P89">
-        <v>-3706.806717414725</v>
+        <v>-3371.455967139725</v>
       </c>
       <c r="Q89">
-        <v>-2942.906717414724</v>
+        <v>-2607.555967139725</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.2336077953899052</v>
+        <v>0.2330083551705801</v>
       </c>
       <c r="T89">
-        <v>3.659013904650264</v>
+        <v>3.649039293002845</v>
       </c>
       <c r="U89">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V89">
-        <v>0.04162179551294454</v>
+        <v>0.04464171014042095</v>
       </c>
       <c r="W89">
-        <v>0.2125075405460739</v>
+        <v>0.1975075405460739</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2522533061390579</v>
+        <v>0.2705558190328542</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2170099398423974</v>
+        <v>0.2037320126138851</v>
       </c>
       <c r="C90">
-        <v>-19953.0382155737</v>
+        <v>-19621.19811532344</v>
       </c>
       <c r="D90">
-        <v>3970.425784426302</v>
+        <v>4302.265884676557</v>
       </c>
       <c r="E90">
         <v>18024.764</v>
@@ -8673,37 +8673,37 @@
         <v>1497.6</v>
       </c>
       <c r="M90">
-        <v>6005.129590921548</v>
+        <v>5598.895630921547</v>
       </c>
       <c r="N90">
-        <v>-4507.529590921547</v>
+        <v>-4101.295630921548</v>
       </c>
       <c r="O90">
-        <v>-743.7423825020553</v>
+        <v>-676.7137791020555</v>
       </c>
       <c r="P90">
-        <v>-3763.787208419492</v>
+        <v>-3424.581851819492</v>
       </c>
       <c r="Q90">
-        <v>-2999.887208419492</v>
+        <v>-2660.681851819492</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.2492584450057307</v>
+        <v>0.2486090514347952</v>
       </c>
       <c r="T90">
-        <v>3.963931730037788</v>
+        <v>3.953125900753083</v>
       </c>
       <c r="U90">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V90">
-        <v>0.04114882056393381</v>
+        <v>0.04413441797973434</v>
       </c>
       <c r="W90">
-        <v>0.2126124164110337</v>
+        <v>0.1976124164110337</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2493867912965686</v>
+        <v>0.267481321089299</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2187693060090227</v>
+        <v>0.2053413787805105</v>
       </c>
       <c r="C91">
-        <v>-20301.17660505923</v>
+        <v>-19972.35002040719</v>
       </c>
       <c r="D91">
-        <v>3930.04039494077</v>
+        <v>4258.866979592814</v>
       </c>
       <c r="E91">
         <v>18332.517</v>
@@ -8755,37 +8755,37 @@
         <v>1497.6</v>
       </c>
       <c r="M91">
-        <v>6073.369699909293</v>
+        <v>5662.519444909292</v>
       </c>
       <c r="N91">
-        <v>-4575.769699909293</v>
+        <v>-4164.919444909292</v>
       </c>
       <c r="O91">
-        <v>-755.0020004850334</v>
+        <v>-687.2117084100332</v>
       </c>
       <c r="P91">
-        <v>-3820.76769942426</v>
+        <v>-3477.707736499259</v>
       </c>
       <c r="Q91">
-        <v>-3056.86769942426</v>
+        <v>-2713.807736499259</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.2677546672789789</v>
+        <v>0.2670462379288675</v>
       </c>
       <c r="T91">
-        <v>4.324289160041222</v>
+        <v>4.312500982639727</v>
       </c>
       <c r="U91">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V91">
-        <v>0.04068647426546265</v>
+        <v>0.04363852564288339</v>
       </c>
       <c r="W91">
-        <v>0.2127149355149832</v>
+        <v>0.1977149355149831</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2465846925179553</v>
+        <v>0.2644759129871721</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.220528672175648</v>
+        <v>0.2069507449471358</v>
       </c>
       <c r="C92">
-        <v>-20648.50170286227</v>
+        <v>-20322.63510071102</v>
       </c>
       <c r="D92">
-        <v>3890.468297137733</v>
+        <v>4216.334899288977</v>
       </c>
       <c r="E92">
         <v>18640.27</v>
@@ -8837,37 +8837,37 @@
         <v>1497.6</v>
       </c>
       <c r="M92">
-        <v>6141.609808897038</v>
+        <v>5726.143258897037</v>
       </c>
       <c r="N92">
-        <v>-4644.009808897037</v>
+        <v>-4228.543258897038</v>
       </c>
       <c r="O92">
-        <v>-766.2616184680112</v>
+        <v>-697.7096377180113</v>
       </c>
       <c r="P92">
-        <v>-3877.748190429026</v>
+        <v>-3530.833621179027</v>
       </c>
       <c r="Q92">
-        <v>-3113.848190429026</v>
+        <v>-2766.933621179026</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.2899501340068767</v>
+        <v>0.2891708617217542</v>
       </c>
       <c r="T92">
-        <v>4.756718076045344</v>
+        <v>4.743751080903699</v>
       </c>
       <c r="U92">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V92">
-        <v>0.04023440232917973</v>
+        <v>0.04315365313574025</v>
       </c>
       <c r="W92">
-        <v>0.2128151764166226</v>
+        <v>0.1978151764166226</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2438448626010893</v>
+        <v>0.261537291731759</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2222880383422734</v>
+        <v>0.2085601111137611</v>
       </c>
       <c r="C93">
-        <v>-20995.03783150149</v>
+        <v>-20672.07906963236</v>
       </c>
       <c r="D93">
-        <v>3851.685168498508</v>
+        <v>4174.643930367645</v>
       </c>
       <c r="E93">
         <v>18948.023</v>
@@ -8919,37 +8919,37 @@
         <v>1497.6</v>
       </c>
       <c r="M93">
-        <v>6209.849917884782</v>
+        <v>5789.767072884782</v>
       </c>
       <c r="N93">
-        <v>-4712.249917884783</v>
+        <v>-4292.167072884782</v>
       </c>
       <c r="O93">
-        <v>-777.5212364509892</v>
+        <v>-708.2075670259891</v>
       </c>
       <c r="P93">
-        <v>-3934.728681433794</v>
+        <v>-3583.959505858793</v>
       </c>
       <c r="Q93">
-        <v>-3170.828681433793</v>
+        <v>-2820.059505858793</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.3170779266743076</v>
+        <v>0.3162120685797269</v>
       </c>
       <c r="T93">
-        <v>5.28524230671705</v>
+        <v>5.270834534337444</v>
       </c>
       <c r="U93">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V93">
-        <v>0.03979226603984808</v>
+        <v>0.04267943716721562</v>
       </c>
       <c r="W93">
-        <v>0.2129132142215227</v>
+        <v>0.1979132142215227</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2411652487263519</v>
+        <v>0.2586632555588826</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2240474045088987</v>
+        <v>0.2101694772803864</v>
       </c>
       <c r="C94">
-        <v>-21340.80835320746</v>
+        <v>-21020.70663351371</v>
       </c>
       <c r="D94">
-        <v>3813.667646792544</v>
+        <v>4133.769366486289</v>
       </c>
       <c r="E94">
         <v>19255.776</v>
@@ -9001,37 +9001,37 @@
         <v>1497.6</v>
       </c>
       <c r="M94">
-        <v>6278.090026872527</v>
+        <v>5853.390886872527</v>
       </c>
       <c r="N94">
-        <v>-4780.490026872527</v>
+        <v>-4355.790886872526</v>
       </c>
       <c r="O94">
-        <v>-788.780854433967</v>
+        <v>-718.7054963339668</v>
       </c>
       <c r="P94">
-        <v>-3991.70917243856</v>
+        <v>-3637.085390538559</v>
       </c>
       <c r="Q94">
-        <v>-3227.80917243856</v>
+        <v>-2873.185390538559</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.3509876675085961</v>
+        <v>0.3500135771521929</v>
       </c>
       <c r="T94">
-        <v>5.945897595056683</v>
+        <v>5.929688851129627</v>
       </c>
       <c r="U94">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V94">
-        <v>0.03935974140898016</v>
+        <v>0.04221553024148503</v>
       </c>
       <c r="W94">
-        <v>0.2130091207697946</v>
+        <v>0.1980091207697946</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2385438873271526</v>
+        <v>0.2558516984332426</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2258067706755241</v>
+        <v>0.2117788434470118</v>
       </c>
       <c r="C95">
-        <v>-21685.83571685134</v>
+        <v>-21368.54154046578</v>
       </c>
       <c r="D95">
-        <v>3776.393283148661</v>
+        <v>4093.68745953422</v>
       </c>
       <c r="E95">
         <v>19563.529</v>
@@ -9083,37 +9083,37 @@
         <v>1497.6</v>
       </c>
       <c r="M95">
-        <v>6346.330135860272</v>
+        <v>5917.014700860272</v>
       </c>
       <c r="N95">
-        <v>-4848.730135860273</v>
+        <v>-4419.414700860272</v>
       </c>
       <c r="O95">
-        <v>-800.040472416945</v>
+        <v>-729.2034256419449</v>
       </c>
       <c r="P95">
-        <v>-4048.689663443328</v>
+        <v>-3690.211275218328</v>
       </c>
       <c r="Q95">
-        <v>-3284.789663443328</v>
+        <v>-2926.311275218327</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.3945859057241099</v>
+        <v>0.3934726596025062</v>
       </c>
       <c r="T95">
-        <v>6.795311537207639</v>
+        <v>6.77678725843386</v>
       </c>
       <c r="U95">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V95">
-        <v>0.03893651838307715</v>
+        <v>0.04176159980878089</v>
       </c>
       <c r="W95">
-        <v>0.213102964811652</v>
+        <v>0.198102964811652</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2359788992913766</v>
+        <v>0.2531006049017023</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2275661368421494</v>
+        <v>0.2133882096136371</v>
       </c>
       <c r="C96">
-        <v>-22030.14150214827</v>
+        <v>-21715.60662637744</v>
       </c>
       <c r="D96">
-        <v>3739.840497851733</v>
+        <v>4054.375373622557</v>
       </c>
       <c r="E96">
         <v>19871.282</v>
@@ -9165,37 +9165,37 @@
         <v>1497.6</v>
       </c>
       <c r="M96">
-        <v>6414.570244848018</v>
+        <v>5980.638514848017</v>
       </c>
       <c r="N96">
-        <v>-4916.970244848018</v>
+        <v>-4483.038514848016</v>
       </c>
       <c r="O96">
-        <v>-811.3000903999231</v>
+        <v>-739.7013549499227</v>
       </c>
       <c r="P96">
-        <v>-4105.670154448096</v>
+        <v>-3743.337159898094</v>
       </c>
       <c r="Q96">
-        <v>-3341.770154448096</v>
+        <v>-2979.437159898094</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.4527168900114618</v>
+        <v>0.4514181028695907</v>
       </c>
       <c r="T96">
-        <v>7.927863460075582</v>
+        <v>7.906251801506173</v>
       </c>
       <c r="U96">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V96">
-        <v>0.03852230010240611</v>
+        <v>0.0413173274703896</v>
       </c>
       <c r="W96">
-        <v>0.2131948121717678</v>
+        <v>0.1981948121717678</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2334684854691279</v>
+        <v>0.2504080452750885</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2293255030087747</v>
+        <v>0.2149975757802625</v>
       </c>
       <c r="C97">
-        <v>-22373.74646131811</v>
+        <v>-22061.9238582999</v>
       </c>
       <c r="D97">
-        <v>3703.988538681892</v>
+        <v>4015.811141700101</v>
       </c>
       <c r="E97">
         <v>20179.035</v>
@@ -9247,37 +9247,37 @@
         <v>1497.6</v>
       </c>
       <c r="M97">
-        <v>6482.810353835762</v>
+        <v>6044.262328835761</v>
       </c>
       <c r="N97">
-        <v>-4985.210353835762</v>
+        <v>-4546.66232883576</v>
       </c>
       <c r="O97">
-        <v>-822.5597083829008</v>
+        <v>-750.1992842579006</v>
       </c>
       <c r="P97">
-        <v>-4162.650645452862</v>
+        <v>-3796.46304457786</v>
       </c>
       <c r="Q97">
-        <v>-3398.750645452862</v>
+        <v>-3032.56304457786</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.5341002680137542</v>
+        <v>0.532541723443509</v>
       </c>
       <c r="T97">
-        <v>9.513436152090701</v>
+        <v>9.487502161807411</v>
       </c>
       <c r="U97">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V97">
-        <v>0.03811680220659131</v>
+        <v>0.04088240823385918</v>
       </c>
       <c r="W97">
-        <v>0.2132847259032495</v>
+        <v>0.1982847259032495</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2310109224641897</v>
+        <v>0.2477721711142982</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2310848691754001</v>
+        <v>0.2166069419468878</v>
       </c>
       <c r="C98">
-        <v>-22716.67055837275</v>
+        <v>-22407.5143753782</v>
       </c>
       <c r="D98">
-        <v>3668.817441627247</v>
+        <v>3977.973624621796</v>
       </c>
       <c r="E98">
         <v>20486.788</v>
@@ -9329,37 +9329,37 @@
         <v>1497.6</v>
       </c>
       <c r="M98">
-        <v>6551.050462823506</v>
+        <v>6107.886142823506</v>
       </c>
       <c r="N98">
-        <v>-5053.450462823506</v>
+        <v>-4610.286142823506</v>
       </c>
       <c r="O98">
-        <v>-833.8193263658786</v>
+        <v>-760.6972135658787</v>
       </c>
       <c r="P98">
-        <v>-4219.631136457628</v>
+        <v>-3849.588929257628</v>
       </c>
       <c r="Q98">
-        <v>-3455.731136457628</v>
+        <v>-3085.688929257627</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.6561753350171914</v>
+        <v>0.6542271543043849</v>
       </c>
       <c r="T98">
-        <v>11.89179519011335</v>
+        <v>11.85937770225924</v>
       </c>
       <c r="U98">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V98">
-        <v>0.03771975218360599</v>
+        <v>0.04045654981475648</v>
       </c>
       <c r="W98">
-        <v>0.2133727664319921</v>
+        <v>0.1983727664319921</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2286045586885211</v>
+        <v>0.245191210998524</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2328442353420254</v>
+        <v>0.2182163081135132</v>
       </c>
       <c r="C99">
-        <v>-23058.9330061861</v>
+        <v>-22752.39852749045</v>
       </c>
       <c r="D99">
-        <v>3634.307993813896</v>
+        <v>3940.842472509548</v>
       </c>
       <c r="E99">
         <v>20794.541</v>
@@ -9411,37 +9411,37 @@
         <v>1497.6</v>
       </c>
       <c r="M99">
-        <v>6619.290571811251</v>
+        <v>6171.50995681125</v>
       </c>
       <c r="N99">
-        <v>-5121.69057181125</v>
+        <v>-4673.909956811251</v>
       </c>
       <c r="O99">
-        <v>-845.0789443488563</v>
+        <v>-771.1951428738564</v>
       </c>
       <c r="P99">
-        <v>-4276.611627462394</v>
+        <v>-3902.714813937394</v>
       </c>
       <c r="Q99">
-        <v>-3512.711627462394</v>
+        <v>-3138.814813937394</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>0.8596337800229219</v>
+        <v>0.8570362057391799</v>
       </c>
       <c r="T99">
-        <v>15.85572692015114</v>
+        <v>15.81250360301232</v>
       </c>
       <c r="U99">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V99">
-        <v>0.03733088875903274</v>
+        <v>0.04003947198161467</v>
       </c>
       <c r="W99">
-        <v>0.2134589916921008</v>
+        <v>0.1984589916921008</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2262478106608046</v>
+        <v>0.2426634665552403</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2346036015086508</v>
+        <v>0.2198256742801385</v>
       </c>
       <c r="C100">
-        <v>-23400.55230149149</v>
+        <v>-23096.59591174289</v>
       </c>
       <c r="D100">
-        <v>3600.441698508509</v>
+        <v>3904.398088257105</v>
       </c>
       <c r="E100">
         <v>21102.294</v>
@@ -9493,37 +9493,37 @@
         <v>1497.6</v>
       </c>
       <c r="M100">
-        <v>6687.530680798995</v>
+        <v>6235.133770798995</v>
       </c>
       <c r="N100">
-        <v>-5189.930680798996</v>
+        <v>-4737.533770798995</v>
       </c>
       <c r="O100">
-        <v>-856.3385623318344</v>
+        <v>-781.6930721818342</v>
       </c>
       <c r="P100">
-        <v>-4333.592118467162</v>
+        <v>-3955.84069861716</v>
       </c>
       <c r="Q100">
-        <v>-3569.692118467161</v>
+        <v>-3191.94069861716</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.266550670034383</v>
+        <v>1.26265430860877</v>
       </c>
       <c r="T100">
-        <v>23.7835903802267</v>
+        <v>23.71875540451847</v>
       </c>
       <c r="U100">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V100">
-        <v>0.03694996132271608</v>
+        <v>0.03963090594098594</v>
       </c>
       <c r="W100">
-        <v>0.2135434572530235</v>
+        <v>0.1985434572530235</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2239391595316125</v>
+        <v>0.2401873087332482</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2363629676752761</v>
+        <v>0.2214350404467638</v>
       </c>
       <c r="C101">
-        <v>-23741.54625794037</v>
+        <v>-23440.12540695874</v>
       </c>
       <c r="D101">
-        <v>3567.200742059631</v>
+        <v>3868.621593041262</v>
       </c>
       <c r="E101">
         <v>21410.047</v>
@@ -9575,37 +9575,37 @@
         <v>1497.6</v>
       </c>
       <c r="M101">
-        <v>6755.77078978674</v>
+        <v>6298.75758478674</v>
       </c>
       <c r="N101">
-        <v>-5258.17078978674</v>
+        <v>-4801.157584786741</v>
       </c>
       <c r="O101">
-        <v>-867.5981803148121</v>
+        <v>-792.1910014898123</v>
       </c>
       <c r="P101">
-        <v>-4390.572609471928</v>
+        <v>-4008.966583296929</v>
       </c>
       <c r="Q101">
-        <v>-3626.672609471927</v>
+        <v>-3245.066583296928</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>2.487301340068766</v>
+        <v>2.479508617217539</v>
       </c>
       <c r="T101">
-        <v>47.5671807604534</v>
+        <v>47.43751080903694</v>
       </c>
       <c r="U101">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V101">
-        <v>0.03657672939016339</v>
+        <v>0.03923059375976386</v>
       </c>
       <c r="W101">
-        <v>0.2136262164389782</v>
+        <v>0.1986262164389782</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.2216771478191721</v>
+        <v>0.237761174301599</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/hong_kong/hong_kong_transportation_railroads.xlsx
+++ b/research/traditional_assets/database/data/hong_kong/hong_kong_transportation_railroads.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07112049067688267</v>
+        <v>0.07109028761639796</v>
       </c>
       <c r="C2">
-        <v>29993.41069683655</v>
+        <v>29717.70507337309</v>
       </c>
       <c r="D2">
-        <v>26834.61069683655</v>
+        <v>26866.6580733731</v>
       </c>
       <c r="E2">
-        <v>-9057.5</v>
+        <v>-8749.746999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>307.753</v>
       </c>
       <c r="G2">
         <v>3158.8</v>
@@ -1457,28 +1457,28 @@
         <v>1497.6</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>17.30698748774486</v>
       </c>
       <c r="N2">
-        <v>1497.6</v>
+        <v>1480.293012512255</v>
       </c>
       <c r="O2">
-        <v>247.104</v>
+        <v>244.2483470645221</v>
       </c>
       <c r="P2">
-        <v>1250.496</v>
+        <v>1236.044665447733</v>
       </c>
       <c r="Q2">
-        <v>2014.396</v>
+        <v>1999.944665447733</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07112049067688267</v>
+        <v>0.07133405239117759</v>
       </c>
       <c r="T2">
-        <v>0.4935434922969562</v>
+        <v>0.4977062076107739</v>
       </c>
       <c r="U2">
         <v>0.0562366166625341</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>86.53152381721291</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07109028761639796</v>
+        <v>0.07106008455591327</v>
       </c>
       <c r="C3">
-        <v>29717.70507337309</v>
+        <v>29442.07608693352</v>
       </c>
       <c r="D3">
-        <v>26866.6580733731</v>
+        <v>26898.78208693352</v>
       </c>
       <c r="E3">
-        <v>-8749.746999999999</v>
+        <v>-8441.994000000001</v>
       </c>
       <c r="F3">
-        <v>307.753</v>
+        <v>615.506</v>
       </c>
       <c r="G3">
         <v>3158.8</v>
@@ -1539,28 +1539,28 @@
         <v>1497.6</v>
       </c>
       <c r="M3">
-        <v>17.30698748774486</v>
+        <v>34.61397497548971</v>
       </c>
       <c r="N3">
-        <v>1480.293012512255</v>
+        <v>1462.98602502451</v>
       </c>
       <c r="O3">
-        <v>244.2483470645221</v>
+        <v>241.3926941290442</v>
       </c>
       <c r="P3">
-        <v>1236.044665447733</v>
+        <v>1221.593330895466</v>
       </c>
       <c r="Q3">
-        <v>1999.944665447733</v>
+        <v>1985.493330895466</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07133405239117759</v>
+        <v>0.07155197250780505</v>
       </c>
       <c r="T3">
-        <v>0.4977062076107739</v>
+        <v>0.501953876298343</v>
       </c>
       <c r="U3">
         <v>0.0562366166625341</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>86.53152381721291</v>
+        <v>43.26576190860646</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07106008455591327</v>
+        <v>0.07102988149542858</v>
       </c>
       <c r="C4">
-        <v>29442.07608693352</v>
+        <v>29166.52401274776</v>
       </c>
       <c r="D4">
-        <v>26898.78208693352</v>
+        <v>26930.98301274775</v>
       </c>
       <c r="E4">
-        <v>-8441.994000000001</v>
+        <v>-8134.241</v>
       </c>
       <c r="F4">
-        <v>615.506</v>
+        <v>923.2589999999999</v>
       </c>
       <c r="G4">
         <v>3158.8</v>
@@ -1621,28 +1621,28 @@
         <v>1497.6</v>
       </c>
       <c r="M4">
-        <v>34.61397497548971</v>
+        <v>51.92096246323457</v>
       </c>
       <c r="N4">
-        <v>1462.98602502451</v>
+        <v>1445.679037536765</v>
       </c>
       <c r="O4">
-        <v>241.3926941290442</v>
+        <v>238.5370411935663</v>
       </c>
       <c r="P4">
-        <v>1221.593330895466</v>
+        <v>1207.141996343199</v>
       </c>
       <c r="Q4">
-        <v>1985.493330895466</v>
+        <v>1971.041996343199</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07155197250780505</v>
+        <v>0.0717743858227135</v>
       </c>
       <c r="T4">
-        <v>0.501953876298343</v>
+        <v>0.5062891257835941</v>
       </c>
       <c r="U4">
         <v>0.0562366166625341</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>43.26576190860646</v>
+        <v>28.8438412724043</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07102988149542858</v>
+        <v>0.07099967843494387</v>
       </c>
       <c r="C5">
-        <v>29166.52401274776</v>
+        <v>28891.04912736523</v>
       </c>
       <c r="D5">
-        <v>26930.98301274775</v>
+        <v>26963.26112736523</v>
       </c>
       <c r="E5">
-        <v>-8134.241</v>
+        <v>-7826.488</v>
       </c>
       <c r="F5">
-        <v>923.2589999999999</v>
+        <v>1231.012</v>
       </c>
       <c r="G5">
         <v>3158.8</v>
@@ -1703,28 +1703,28 @@
         <v>1497.6</v>
       </c>
       <c r="M5">
-        <v>51.92096246323457</v>
+        <v>69.22794995097942</v>
       </c>
       <c r="N5">
-        <v>1445.679037536765</v>
+        <v>1428.372050049021</v>
       </c>
       <c r="O5">
-        <v>238.5370411935663</v>
+        <v>235.6813882580884</v>
       </c>
       <c r="P5">
-        <v>1207.141996343199</v>
+        <v>1192.690661790932</v>
       </c>
       <c r="Q5">
-        <v>1971.041996343199</v>
+        <v>1956.590661790932</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.0717743858227135</v>
+        <v>0.07200143274834921</v>
       </c>
       <c r="T5">
-        <v>0.5062891257835941</v>
+        <v>0.5107146929664544</v>
       </c>
       <c r="U5">
         <v>0.0562366166625341</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>28.8438412724043</v>
+        <v>21.63288095430323</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07099967843494387</v>
+        <v>0.07096947537445919</v>
       </c>
       <c r="C6">
-        <v>28891.04912736523</v>
+        <v>28615.65170866274</v>
       </c>
       <c r="D6">
-        <v>26963.26112736523</v>
+        <v>26995.61670866274</v>
       </c>
       <c r="E6">
-        <v>-7826.488</v>
+        <v>-7518.735</v>
       </c>
       <c r="F6">
-        <v>1231.012</v>
+        <v>1538.765</v>
       </c>
       <c r="G6">
         <v>3158.8</v>
@@ -1785,28 +1785,28 @@
         <v>1497.6</v>
       </c>
       <c r="M6">
-        <v>69.22794995097942</v>
+        <v>86.53493743872428</v>
       </c>
       <c r="N6">
-        <v>1428.372050049021</v>
+        <v>1411.065062561276</v>
       </c>
       <c r="O6">
-        <v>235.6813882580884</v>
+        <v>232.8257353226105</v>
       </c>
       <c r="P6">
-        <v>1192.690661790932</v>
+        <v>1178.239327238665</v>
       </c>
       <c r="Q6">
-        <v>1956.590661790932</v>
+        <v>1942.139327238665</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07200143274834921</v>
+        <v>0.07223325960926147</v>
       </c>
       <c r="T6">
-        <v>0.5107146929664544</v>
+        <v>0.5152334299847435</v>
       </c>
       <c r="U6">
         <v>0.0562366166625341</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>21.63288095430323</v>
+        <v>17.30630476344258</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07096947537445919</v>
+        <v>0.07093927231397448</v>
       </c>
       <c r="C7">
-        <v>28615.65170866274</v>
+        <v>28340.33203585259</v>
       </c>
       <c r="D7">
-        <v>26995.61670866274</v>
+        <v>27028.05003585259</v>
       </c>
       <c r="E7">
-        <v>-7518.735</v>
+        <v>-7210.982</v>
       </c>
       <c r="F7">
-        <v>1538.765</v>
+        <v>1846.518</v>
       </c>
       <c r="G7">
         <v>3158.8</v>
@@ -1867,28 +1867,28 @@
         <v>1497.6</v>
       </c>
       <c r="M7">
-        <v>86.53493743872428</v>
+        <v>103.8419249264691</v>
       </c>
       <c r="N7">
-        <v>1411.065062561276</v>
+        <v>1393.758075073531</v>
       </c>
       <c r="O7">
-        <v>232.8257353226105</v>
+        <v>229.9700823871326</v>
       </c>
       <c r="P7">
-        <v>1178.239327238665</v>
+        <v>1163.787992686398</v>
       </c>
       <c r="Q7">
-        <v>1942.139327238665</v>
+        <v>1927.687992686398</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07223325960926147</v>
+        <v>0.07247001895657609</v>
       </c>
       <c r="T7">
-        <v>0.5152334299847435</v>
+        <v>0.5198483103438472</v>
       </c>
       <c r="U7">
         <v>0.0562366166625341</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>17.30630476344258</v>
+        <v>14.42192063620215</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07093927231397448</v>
+        <v>0.07090906925348979</v>
       </c>
       <c r="C8">
-        <v>28340.33203585259</v>
+        <v>28065.09038949038</v>
       </c>
       <c r="D8">
-        <v>27028.05003585259</v>
+        <v>27060.56138949038</v>
       </c>
       <c r="E8">
-        <v>-7210.982</v>
+        <v>-6903.229</v>
       </c>
       <c r="F8">
-        <v>1846.518</v>
+        <v>2154.271</v>
       </c>
       <c r="G8">
         <v>3158.8</v>
@@ -1949,28 +1949,28 @@
         <v>1497.6</v>
       </c>
       <c r="M8">
-        <v>103.8419249264691</v>
+        <v>121.148912414214</v>
       </c>
       <c r="N8">
-        <v>1393.758075073531</v>
+        <v>1376.451087585786</v>
       </c>
       <c r="O8">
-        <v>229.9700823871326</v>
+        <v>227.1144294516547</v>
       </c>
       <c r="P8">
-        <v>1163.787992686398</v>
+        <v>1149.336658134131</v>
       </c>
       <c r="Q8">
-        <v>1927.687992686398</v>
+        <v>1913.236658134131</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07247001895657609</v>
+        <v>0.07271186990275771</v>
       </c>
       <c r="T8">
-        <v>0.5198483103438472</v>
+        <v>0.5245624354418562</v>
       </c>
       <c r="U8">
         <v>0.0562366166625341</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>14.42192063620215</v>
+        <v>12.36164625960185</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07090906925348978</v>
+        <v>0.0708788661930051</v>
       </c>
       <c r="C9">
-        <v>28065.0903894904</v>
+        <v>27789.92705148333</v>
       </c>
       <c r="D9">
-        <v>27060.5613894904</v>
+        <v>27093.15105148334</v>
       </c>
       <c r="E9">
-        <v>-6903.228999999999</v>
+        <v>-6595.476000000001</v>
       </c>
       <c r="F9">
-        <v>2154.271</v>
+        <v>2462.024</v>
       </c>
       <c r="G9">
         <v>3158.8</v>
@@ -2031,28 +2031,28 @@
         <v>1497.6</v>
       </c>
       <c r="M9">
-        <v>121.148912414214</v>
+        <v>138.4558999019588</v>
       </c>
       <c r="N9">
-        <v>1376.451087585786</v>
+        <v>1359.144100098041</v>
       </c>
       <c r="O9">
-        <v>227.1144294516547</v>
+        <v>224.2587765161768</v>
       </c>
       <c r="P9">
-        <v>1149.336658134131</v>
+        <v>1134.885323581864</v>
       </c>
       <c r="Q9">
-        <v>1913.236658134131</v>
+        <v>1898.785323581864</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07271186990275771</v>
+        <v>0.07295897847820415</v>
       </c>
       <c r="T9">
-        <v>0.5245624354418563</v>
+        <v>0.5293790415202568</v>
       </c>
       <c r="U9">
         <v>0.0562366166625341</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>12.36164625960184</v>
+        <v>10.81644047715161</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0708788661930051</v>
+        <v>0.07084866313252039</v>
       </c>
       <c r="C10">
-        <v>27789.92705148333</v>
+        <v>27514.84230509831</v>
       </c>
       <c r="D10">
-        <v>27093.15105148334</v>
+        <v>27125.81930509831</v>
       </c>
       <c r="E10">
-        <v>-6595.476000000001</v>
+        <v>-6287.723</v>
       </c>
       <c r="F10">
-        <v>2462.024</v>
+        <v>2769.777</v>
       </c>
       <c r="G10">
         <v>3158.8</v>
@@ -2113,28 +2113,28 @@
         <v>1497.6</v>
       </c>
       <c r="M10">
-        <v>138.4558999019588</v>
+        <v>155.7628873897037</v>
       </c>
       <c r="N10">
-        <v>1359.144100098041</v>
+        <v>1341.837112610296</v>
       </c>
       <c r="O10">
-        <v>224.2587765161768</v>
+        <v>221.4031235806989</v>
       </c>
       <c r="P10">
-        <v>1134.885323581864</v>
+        <v>1120.433989029597</v>
       </c>
       <c r="Q10">
-        <v>1898.785323581864</v>
+        <v>1884.333989029597</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07295897847820415</v>
+        <v>0.0732115180113527</v>
       </c>
       <c r="T10">
-        <v>0.5293790415202568</v>
+        <v>0.534301507072908</v>
       </c>
       <c r="U10">
         <v>0.0562366166625341</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>10.81644047715161</v>
+        <v>9.614613757468101</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07084866313252039</v>
+        <v>0.0709437100720357</v>
       </c>
       <c r="C11">
-        <v>27514.84230509831</v>
+        <v>27104.54969978913</v>
       </c>
       <c r="D11">
-        <v>27125.81930509831</v>
+        <v>27023.27969978913</v>
       </c>
       <c r="E11">
-        <v>-6287.723</v>
+        <v>-5979.97</v>
       </c>
       <c r="F11">
-        <v>2769.777</v>
+        <v>3077.53</v>
       </c>
       <c r="G11">
         <v>3158.8</v>
@@ -2195,45 +2195,45 @@
         <v>1497.6</v>
       </c>
       <c r="M11">
-        <v>155.7628873897037</v>
+        <v>177.6861698774485</v>
       </c>
       <c r="N11">
-        <v>1341.837112610296</v>
+        <v>1319.913830122551</v>
       </c>
       <c r="O11">
-        <v>221.4031235806989</v>
+        <v>217.785781970221</v>
       </c>
       <c r="P11">
-        <v>1120.433989029597</v>
+        <v>1102.12804815233</v>
       </c>
       <c r="Q11">
-        <v>1884.333989029597</v>
+        <v>1866.02804815233</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.0732115180113527</v>
+        <v>0.07346966953412679</v>
       </c>
       <c r="T11">
-        <v>0.534301507072908</v>
+        <v>0.5393333607489516</v>
       </c>
       <c r="U11">
-        <v>0.0562366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V11">
         <v>0.165</v>
       </c>
       <c r="W11">
-        <v>0.04695757491321597</v>
+        <v>0.04821007491321597</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>9.614613757468101</v>
+        <v>8.428343078321209</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0709437100720357</v>
+        <v>0.070926032011551</v>
       </c>
       <c r="C12">
-        <v>27104.54969978913</v>
+        <v>26815.80961726087</v>
       </c>
       <c r="D12">
-        <v>27023.27969978913</v>
+        <v>27042.29261726087</v>
       </c>
       <c r="E12">
-        <v>-5979.969999999999</v>
+        <v>-5672.217000000001</v>
       </c>
       <c r="F12">
-        <v>3077.53</v>
+        <v>3385.283</v>
       </c>
       <c r="G12">
         <v>3158.8</v>
@@ -2277,28 +2277,28 @@
         <v>1497.6</v>
       </c>
       <c r="M12">
-        <v>177.6861698774486</v>
+        <v>195.4547868651934</v>
       </c>
       <c r="N12">
-        <v>1319.913830122551</v>
+        <v>1302.145213134806</v>
       </c>
       <c r="O12">
-        <v>217.785781970221</v>
+        <v>214.8539601672431</v>
       </c>
       <c r="P12">
-        <v>1102.12804815233</v>
+        <v>1087.291252967563</v>
       </c>
       <c r="Q12">
-        <v>1866.02804815233</v>
+        <v>1851.191252967563</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07346966953412679</v>
+        <v>0.07373362221471601</v>
       </c>
       <c r="T12">
-        <v>0.5393333607489516</v>
+        <v>0.5444782897885015</v>
       </c>
       <c r="U12">
         <v>0.05773661666253409</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>8.428343078321209</v>
+        <v>7.662130071201099</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.070926032011551</v>
+        <v>0.0709083539510663</v>
       </c>
       <c r="C13">
-        <v>26815.80961726087</v>
+        <v>26527.09630761511</v>
       </c>
       <c r="D13">
-        <v>27042.29261726087</v>
+        <v>27061.33230761511</v>
       </c>
       <c r="E13">
-        <v>-5672.217000000001</v>
+        <v>-5364.464</v>
       </c>
       <c r="F13">
-        <v>3385.283</v>
+        <v>3693.036</v>
       </c>
       <c r="G13">
         <v>3158.8</v>
@@ -2359,28 +2359,28 @@
         <v>1497.6</v>
       </c>
       <c r="M13">
-        <v>195.4547868651934</v>
+        <v>213.2234038529382</v>
       </c>
       <c r="N13">
-        <v>1302.145213134806</v>
+        <v>1284.376596147062</v>
       </c>
       <c r="O13">
-        <v>214.8539601672431</v>
+        <v>211.9221383642652</v>
       </c>
       <c r="P13">
-        <v>1087.291252967563</v>
+        <v>1072.454457782796</v>
       </c>
       <c r="Q13">
-        <v>1851.191252967563</v>
+        <v>1836.354457782797</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07373362221471601</v>
+        <v>0.07400357381986408</v>
       </c>
       <c r="T13">
-        <v>0.5444782897885015</v>
+        <v>0.5497401490334959</v>
       </c>
       <c r="U13">
         <v>0.05773661666253409</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>7.662130071201099</v>
+        <v>7.023619231934341</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0709083539510663</v>
+        <v>0.07107521089058159</v>
       </c>
       <c r="C14">
-        <v>26527.09630761511</v>
+        <v>26040.69510137056</v>
       </c>
       <c r="D14">
-        <v>27061.33230761511</v>
+        <v>26882.68410137056</v>
       </c>
       <c r="E14">
-        <v>-5364.464</v>
+        <v>-5056.710999999999</v>
       </c>
       <c r="F14">
-        <v>3693.036</v>
+        <v>4000.789</v>
       </c>
       <c r="G14">
         <v>3158.8</v>
@@ -2441,45 +2441,45 @@
         <v>1497.6</v>
       </c>
       <c r="M14">
-        <v>213.2234038529382</v>
+        <v>237.7933621406831</v>
       </c>
       <c r="N14">
-        <v>1284.376596147062</v>
+        <v>1259.806637859317</v>
       </c>
       <c r="O14">
-        <v>211.9221383642652</v>
+        <v>207.8680952467872</v>
       </c>
       <c r="P14">
-        <v>1072.454457782796</v>
+        <v>1051.938542612529</v>
       </c>
       <c r="Q14">
-        <v>1836.354457782797</v>
+        <v>1815.838542612529</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07400357381986408</v>
+        <v>0.07427973120903854</v>
       </c>
       <c r="T14">
-        <v>0.5497401490334959</v>
+        <v>0.5551229705599844</v>
       </c>
       <c r="U14">
-        <v>0.05773661666253409</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V14">
         <v>0.165</v>
       </c>
       <c r="W14">
-        <v>0.04821007491321597</v>
+        <v>0.04962957491321596</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y14">
-        <v>7.023619231934341</v>
+        <v>6.297904981527578</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07107521089058159</v>
+        <v>0.07107172783009691</v>
       </c>
       <c r="C15">
-        <v>26040.69510137056</v>
+        <v>25736.64719092143</v>
       </c>
       <c r="D15">
-        <v>26882.68410137056</v>
+        <v>26886.38919092143</v>
       </c>
       <c r="E15">
-        <v>-5056.710999999999</v>
+        <v>-4748.958</v>
       </c>
       <c r="F15">
-        <v>4000.789</v>
+        <v>4308.542</v>
       </c>
       <c r="G15">
         <v>3158.8</v>
@@ -2523,28 +2523,28 @@
         <v>1497.6</v>
       </c>
       <c r="M15">
-        <v>237.7933621406831</v>
+        <v>256.085159228428</v>
       </c>
       <c r="N15">
-        <v>1259.806637859317</v>
+        <v>1241.514840771572</v>
       </c>
       <c r="O15">
-        <v>207.8680952467872</v>
+        <v>204.8499487273094</v>
       </c>
       <c r="P15">
-        <v>1051.938542612529</v>
+        <v>1036.664892044263</v>
       </c>
       <c r="Q15">
-        <v>1815.838542612529</v>
+        <v>1800.564892044263</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07427973120903854</v>
+        <v>0.07456231086307753</v>
       </c>
       <c r="T15">
-        <v>0.5551229705599844</v>
+        <v>0.5606309739824378</v>
       </c>
       <c r="U15">
         <v>0.05943661666253409</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>6.297904981527578</v>
+        <v>5.84805462570418</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07107172783009691</v>
+        <v>0.07116844476961222</v>
       </c>
       <c r="C16">
-        <v>25736.64719092143</v>
+        <v>25326.39010362798</v>
       </c>
       <c r="D16">
-        <v>26886.38919092143</v>
+        <v>26783.88510362798</v>
       </c>
       <c r="E16">
-        <v>-4748.958</v>
+        <v>-4441.204999999999</v>
       </c>
       <c r="F16">
-        <v>4308.542</v>
+        <v>4616.295000000001</v>
       </c>
       <c r="G16">
         <v>3158.8</v>
@@ -2605,45 +2605,45 @@
         <v>1497.6</v>
       </c>
       <c r="M16">
-        <v>256.085159228428</v>
+        <v>278.0699923161729</v>
       </c>
       <c r="N16">
-        <v>1241.514840771572</v>
+        <v>1219.530007683827</v>
       </c>
       <c r="O16">
-        <v>204.8499487273094</v>
+        <v>201.2224512678315</v>
       </c>
       <c r="P16">
-        <v>1036.664892044263</v>
+        <v>1018.307556415996</v>
       </c>
       <c r="Q16">
-        <v>1800.564892044263</v>
+        <v>1782.207556415995</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07456231086307753</v>
+        <v>0.07485153945015273</v>
       </c>
       <c r="T16">
-        <v>0.5606309739824378</v>
+        <v>0.5662685774854195</v>
       </c>
       <c r="U16">
-        <v>0.05943661666253409</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V16">
         <v>0.165</v>
       </c>
       <c r="W16">
-        <v>0.04962957491321596</v>
+        <v>0.05029757491321597</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y16">
-        <v>5.84805462570418</v>
+        <v>5.385694398470689</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07116844476961222</v>
+        <v>0.07117164170912751</v>
       </c>
       <c r="C17">
-        <v>25326.39010362799</v>
+        <v>25015.26221517407</v>
       </c>
       <c r="D17">
-        <v>26783.88510362798</v>
+        <v>26780.51021517407</v>
       </c>
       <c r="E17">
-        <v>-4441.205</v>
+        <v>-4133.452</v>
       </c>
       <c r="F17">
-        <v>4616.295</v>
+        <v>4924.048</v>
       </c>
       <c r="G17">
         <v>3158.8</v>
@@ -2687,28 +2687,28 @@
         <v>1497.6</v>
       </c>
       <c r="M17">
-        <v>278.0699923161728</v>
+        <v>296.6079918039177</v>
       </c>
       <c r="N17">
-        <v>1219.530007683827</v>
+        <v>1200.992008196082</v>
       </c>
       <c r="O17">
-        <v>201.2224512678315</v>
+        <v>198.1636813523536</v>
       </c>
       <c r="P17">
-        <v>1018.307556415996</v>
+        <v>1002.828326843729</v>
       </c>
       <c r="Q17">
-        <v>1782.207556415995</v>
+        <v>1766.728326843729</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07485153945015273</v>
+        <v>0.07514765443215829</v>
       </c>
       <c r="T17">
-        <v>0.5662685774854195</v>
+        <v>0.572040409643234</v>
       </c>
       <c r="U17">
         <v>0.0602366166625341</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.38569439847069</v>
+        <v>5.049088498566272</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07117164170912751</v>
+        <v>0.07117483864864281</v>
       </c>
       <c r="C18">
-        <v>25015.26221517407</v>
+        <v>24704.13517711487</v>
       </c>
       <c r="D18">
-        <v>26780.51021517407</v>
+        <v>26777.13617711487</v>
       </c>
       <c r="E18">
-        <v>-4133.452</v>
+        <v>-3825.699</v>
       </c>
       <c r="F18">
-        <v>4924.048</v>
+        <v>5231.801</v>
       </c>
       <c r="G18">
         <v>3158.8</v>
@@ -2769,28 +2769,28 @@
         <v>1497.6</v>
       </c>
       <c r="M18">
-        <v>296.6079918039177</v>
+        <v>315.1459912916626</v>
       </c>
       <c r="N18">
-        <v>1200.992008196082</v>
+        <v>1182.454008708337</v>
       </c>
       <c r="O18">
-        <v>198.1636813523536</v>
+        <v>195.1049114368757</v>
       </c>
       <c r="P18">
-        <v>1002.828326843729</v>
+        <v>987.3490972714617</v>
       </c>
       <c r="Q18">
-        <v>1766.728326843729</v>
+        <v>1751.249097271462</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07514765443215829</v>
+        <v>0.07545090471493507</v>
       </c>
       <c r="T18">
-        <v>0.572040409643234</v>
+        <v>0.5779513220940079</v>
       </c>
       <c r="U18">
         <v>0.0602366166625341</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.049088498566272</v>
+        <v>4.752083292768256</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07117483864864281</v>
+        <v>0.07117803558815813</v>
       </c>
       <c r="C19">
-        <v>24704.13517711487</v>
+        <v>24393.00898912896</v>
       </c>
       <c r="D19">
-        <v>26777.13617711487</v>
+        <v>26773.76298912896</v>
       </c>
       <c r="E19">
-        <v>-3825.699</v>
+        <v>-3517.946</v>
       </c>
       <c r="F19">
-        <v>5231.801</v>
+        <v>5539.554</v>
       </c>
       <c r="G19">
         <v>3158.8</v>
@@ -2851,28 +2851,28 @@
         <v>1497.6</v>
       </c>
       <c r="M19">
-        <v>315.1459912916626</v>
+        <v>333.6839907794074</v>
       </c>
       <c r="N19">
-        <v>1182.454008708337</v>
+        <v>1163.916009220593</v>
       </c>
       <c r="O19">
-        <v>195.1049114368757</v>
+        <v>192.0461415213978</v>
       </c>
       <c r="P19">
-        <v>987.3490972714617</v>
+        <v>971.8698676991947</v>
       </c>
       <c r="Q19">
-        <v>1751.249097271462</v>
+        <v>1735.769867699195</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07545090471493507</v>
+        <v>0.07576155134607226</v>
       </c>
       <c r="T19">
-        <v>0.5779513220940079</v>
+        <v>0.5840064031411422</v>
       </c>
       <c r="U19">
         <v>0.0602366166625341</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>4.752083292768256</v>
+        <v>4.488078665392242</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07117803558815813</v>
+        <v>0.07118123252767343</v>
       </c>
       <c r="C20">
-        <v>24393.00898912896</v>
+        <v>24081.8836508952</v>
       </c>
       <c r="D20">
-        <v>26773.76298912896</v>
+        <v>26770.3906508952</v>
       </c>
       <c r="E20">
-        <v>-3517.946</v>
+        <v>-3210.193</v>
       </c>
       <c r="F20">
-        <v>5539.554</v>
+        <v>5847.307</v>
       </c>
       <c r="G20">
         <v>3158.8</v>
@@ -2933,28 +2933,28 @@
         <v>1497.6</v>
       </c>
       <c r="M20">
-        <v>333.6839907794074</v>
+        <v>352.2219902671523</v>
       </c>
       <c r="N20">
-        <v>1163.916009220593</v>
+        <v>1145.378009732848</v>
       </c>
       <c r="O20">
-        <v>192.0461415213978</v>
+        <v>188.9873716059199</v>
       </c>
       <c r="P20">
-        <v>971.8698676991947</v>
+        <v>956.3906381269278</v>
       </c>
       <c r="Q20">
-        <v>1735.769867699195</v>
+        <v>1720.290638126928</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07576155134607226</v>
+        <v>0.07607986826439801</v>
       </c>
       <c r="T20">
-        <v>0.5840064031411422</v>
+        <v>0.5902109923622797</v>
       </c>
       <c r="U20">
         <v>0.0602366166625341</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>4.488078665392242</v>
+        <v>4.251863998792651</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07118123252767343</v>
+        <v>0.07135142946718873</v>
       </c>
       <c r="C21">
-        <v>24081.8836508952</v>
+        <v>23595.81426494653</v>
       </c>
       <c r="D21">
-        <v>26770.3906508952</v>
+        <v>26592.07426494654</v>
       </c>
       <c r="E21">
-        <v>-3210.193</v>
+        <v>-2902.44</v>
       </c>
       <c r="F21">
-        <v>5847.307</v>
+        <v>6155.06</v>
       </c>
       <c r="G21">
         <v>3158.8</v>
@@ -3015,45 +3015,45 @@
         <v>1497.6</v>
       </c>
       <c r="M21">
-        <v>352.2219902671523</v>
+        <v>376.9150497548972</v>
       </c>
       <c r="N21">
-        <v>1145.378009732848</v>
+        <v>1120.684950245103</v>
       </c>
       <c r="O21">
-        <v>188.9873716059199</v>
+        <v>184.913016790442</v>
       </c>
       <c r="P21">
-        <v>956.3906381269278</v>
+        <v>935.7719334546608</v>
       </c>
       <c r="Q21">
-        <v>1720.290638126928</v>
+        <v>1699.671933454661</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07607986826439801</v>
+        <v>0.07640614310568192</v>
       </c>
       <c r="T21">
-        <v>0.5902109923622797</v>
+        <v>0.5965706963139458</v>
       </c>
       <c r="U21">
-        <v>0.0602366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V21">
         <v>0.165</v>
       </c>
       <c r="W21">
-        <v>0.05029757491321597</v>
+        <v>0.05113257491321597</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y21">
-        <v>4.251863998792651</v>
+        <v>3.973309107646058</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07135142946718873</v>
+        <v>0.07136297640670403</v>
       </c>
       <c r="C22">
-        <v>23595.81426494653</v>
+        <v>23276.04947616895</v>
       </c>
       <c r="D22">
-        <v>26592.07426494654</v>
+        <v>26580.06247616895</v>
       </c>
       <c r="E22">
-        <v>-2902.44</v>
+        <v>-2594.687</v>
       </c>
       <c r="F22">
-        <v>6155.06</v>
+        <v>6462.813</v>
       </c>
       <c r="G22">
         <v>3158.8</v>
@@ -3097,28 +3097,28 @@
         <v>1497.6</v>
       </c>
       <c r="M22">
-        <v>376.9150497548972</v>
+        <v>395.760802242642</v>
       </c>
       <c r="N22">
-        <v>1120.684950245103</v>
+        <v>1101.839197757358</v>
       </c>
       <c r="O22">
-        <v>184.913016790442</v>
+        <v>181.803467629964</v>
       </c>
       <c r="P22">
-        <v>935.7719334546608</v>
+        <v>920.0357301273938</v>
       </c>
       <c r="Q22">
-        <v>1699.671933454661</v>
+        <v>1683.935730127394</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07640614310568192</v>
+        <v>0.07674067806952997</v>
       </c>
       <c r="T22">
-        <v>0.5965706963139458</v>
+        <v>0.603091405428945</v>
       </c>
       <c r="U22">
         <v>0.0612366166625341</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>3.973309107646058</v>
+        <v>3.784103912043864</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07136297640670403</v>
+        <v>0.07137452334621934</v>
       </c>
       <c r="C23">
-        <v>23276.04947616895</v>
+        <v>22956.29553407628</v>
       </c>
       <c r="D23">
-        <v>26580.06247616895</v>
+        <v>26568.06153407628</v>
       </c>
       <c r="E23">
-        <v>-2594.687000000001</v>
+        <v>-2286.934</v>
       </c>
       <c r="F23">
-        <v>6462.812999999999</v>
+        <v>6770.566</v>
       </c>
       <c r="G23">
         <v>3158.8</v>
@@ -3179,28 +3179,28 @@
         <v>1497.6</v>
       </c>
       <c r="M23">
-        <v>395.7608022426419</v>
+        <v>414.6065547303868</v>
       </c>
       <c r="N23">
-        <v>1101.839197757358</v>
+        <v>1082.993445269613</v>
       </c>
       <c r="O23">
-        <v>181.803467629964</v>
+        <v>178.6939184694861</v>
       </c>
       <c r="P23">
-        <v>920.0357301273938</v>
+        <v>904.2995268001268</v>
       </c>
       <c r="Q23">
-        <v>1683.935730127394</v>
+        <v>1668.199526800127</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07674067806952997</v>
+        <v>0.07708379085296388</v>
       </c>
       <c r="T23">
-        <v>0.603091405428945</v>
+        <v>0.6097793122135599</v>
       </c>
       <c r="U23">
         <v>0.0612366166625341</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>3.784103912043865</v>
+        <v>3.612099188769144</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07137452334621934</v>
+        <v>0.07138607028573464</v>
       </c>
       <c r="C24">
-        <v>22956.29553407628</v>
+        <v>22636.5524239833</v>
       </c>
       <c r="D24">
-        <v>26568.06153407628</v>
+        <v>26556.0714239833</v>
       </c>
       <c r="E24">
-        <v>-2286.934</v>
+        <v>-1979.181</v>
       </c>
       <c r="F24">
-        <v>6770.566</v>
+        <v>7078.319</v>
       </c>
       <c r="G24">
         <v>3158.8</v>
@@ -3261,28 +3261,28 @@
         <v>1497.6</v>
       </c>
       <c r="M24">
-        <v>414.6065547303868</v>
+        <v>433.4523072181317</v>
       </c>
       <c r="N24">
-        <v>1082.993445269613</v>
+        <v>1064.147692781868</v>
       </c>
       <c r="O24">
-        <v>178.6939184694861</v>
+        <v>175.5843693090083</v>
       </c>
       <c r="P24">
-        <v>904.2995268001268</v>
+        <v>888.56332347286</v>
       </c>
       <c r="Q24">
-        <v>1668.199526800127</v>
+        <v>1652.46332347286</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07708379085296388</v>
+        <v>0.0774358156567467</v>
       </c>
       <c r="T24">
-        <v>0.6097793122135599</v>
+        <v>0.6166409308627099</v>
       </c>
       <c r="U24">
         <v>0.0612366166625341</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>3.612099188769144</v>
+        <v>3.455051397953094</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07138607028573464</v>
+        <v>0.07139761722524994</v>
       </c>
       <c r="C25">
-        <v>22636.5524239833</v>
+        <v>22316.82013123123</v>
       </c>
       <c r="D25">
-        <v>26556.0714239833</v>
+        <v>26544.09213123123</v>
       </c>
       <c r="E25">
-        <v>-1979.181</v>
+        <v>-1671.428</v>
       </c>
       <c r="F25">
-        <v>7078.319</v>
+        <v>7386.072</v>
       </c>
       <c r="G25">
         <v>3158.8</v>
@@ -3343,28 +3343,28 @@
         <v>1497.6</v>
       </c>
       <c r="M25">
-        <v>433.4523072181317</v>
+        <v>452.2980597058765</v>
       </c>
       <c r="N25">
-        <v>1064.147692781868</v>
+        <v>1045.301940294123</v>
       </c>
       <c r="O25">
-        <v>175.5843693090083</v>
+        <v>172.4748201485304</v>
       </c>
       <c r="P25">
-        <v>888.56332347286</v>
+        <v>872.827120145593</v>
       </c>
       <c r="Q25">
-        <v>1652.46332347286</v>
+        <v>1636.727120145593</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.0774358156567467</v>
+        <v>0.07779710427115541</v>
       </c>
       <c r="T25">
-        <v>0.6166409308627099</v>
+        <v>0.6236831184236798</v>
       </c>
       <c r="U25">
         <v>0.0612366166625341</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>3.455051397953094</v>
+        <v>3.311090923038382</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07139761722524994</v>
+        <v>0.07140916416476525</v>
       </c>
       <c r="C26">
-        <v>22316.82013123123</v>
+        <v>21997.09864118773</v>
       </c>
       <c r="D26">
-        <v>26544.09213123123</v>
+        <v>26532.12364118774</v>
       </c>
       <c r="E26">
-        <v>-1671.428000000001</v>
+        <v>-1363.675</v>
       </c>
       <c r="F26">
-        <v>7386.071999999999</v>
+        <v>7693.825</v>
       </c>
       <c r="G26">
         <v>3158.8</v>
@@ -3425,28 +3425,28 @@
         <v>1497.6</v>
       </c>
       <c r="M26">
-        <v>452.2980597058765</v>
+        <v>471.1438121936214</v>
       </c>
       <c r="N26">
-        <v>1045.301940294123</v>
+        <v>1026.456187806378</v>
       </c>
       <c r="O26">
-        <v>172.4748201485304</v>
+        <v>169.3652709880525</v>
       </c>
       <c r="P26">
-        <v>872.827120145593</v>
+        <v>857.090916818326</v>
       </c>
       <c r="Q26">
-        <v>1636.727120145593</v>
+        <v>1620.990916818326</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07779710427115541</v>
+        <v>0.078168027248615</v>
       </c>
       <c r="T26">
-        <v>0.6236831184236798</v>
+        <v>0.6309130976529422</v>
       </c>
       <c r="U26">
         <v>0.0612366166625341</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.311090923038382</v>
+        <v>3.178647286116846</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07140916416476525</v>
+        <v>0.07142071110428055</v>
       </c>
       <c r="C27">
-        <v>21997.09864118773</v>
+        <v>21677.3879392469</v>
       </c>
       <c r="D27">
-        <v>26532.12364118774</v>
+        <v>26520.1659392469</v>
       </c>
       <c r="E27">
-        <v>-1363.675</v>
+        <v>-1055.922</v>
       </c>
       <c r="F27">
-        <v>7693.825</v>
+        <v>8001.578</v>
       </c>
       <c r="G27">
         <v>3158.8</v>
@@ -3507,28 +3507,28 @@
         <v>1497.6</v>
       </c>
       <c r="M27">
-        <v>471.1438121936214</v>
+        <v>489.9895646813663</v>
       </c>
       <c r="N27">
-        <v>1026.456187806378</v>
+        <v>1007.610435318634</v>
       </c>
       <c r="O27">
-        <v>169.3652709880525</v>
+        <v>166.2557218275745</v>
       </c>
       <c r="P27">
-        <v>857.090916818326</v>
+        <v>841.354713491059</v>
       </c>
       <c r="Q27">
-        <v>1620.990916818326</v>
+        <v>1605.254713491059</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.078168027248615</v>
+        <v>0.07854897517141135</v>
       </c>
       <c r="T27">
-        <v>0.6309130976529422</v>
+        <v>0.6383384817262389</v>
       </c>
       <c r="U27">
         <v>0.0612366166625341</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.178647286116846</v>
+        <v>3.056391621266198</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07142071110428055</v>
+        <v>0.07199588304379585</v>
       </c>
       <c r="C28">
-        <v>21677.3879392469</v>
+        <v>20787.34285716506</v>
       </c>
       <c r="D28">
-        <v>26520.1659392469</v>
+        <v>25937.87385716506</v>
       </c>
       <c r="E28">
-        <v>-1055.922</v>
+        <v>-748.1689999999999</v>
       </c>
       <c r="F28">
-        <v>8001.578</v>
+        <v>8309.331</v>
       </c>
       <c r="G28">
         <v>3158.8</v>
@@ -3589,45 +3589,45 @@
         <v>1497.6</v>
       </c>
       <c r="M28">
-        <v>489.9895646813663</v>
+        <v>529.6086446691111</v>
       </c>
       <c r="N28">
-        <v>1007.610435318634</v>
+        <v>967.9913553308888</v>
       </c>
       <c r="O28">
-        <v>166.2557218275745</v>
+        <v>159.7185736295967</v>
       </c>
       <c r="P28">
-        <v>841.354713491059</v>
+        <v>808.2727817012922</v>
       </c>
       <c r="Q28">
-        <v>1605.254713491059</v>
+        <v>1572.172781701292</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07854897517141135</v>
+        <v>0.07894036002359937</v>
       </c>
       <c r="T28">
-        <v>0.6383384817262389</v>
+        <v>0.6459673009796256</v>
       </c>
       <c r="U28">
-        <v>0.0612366166625341</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V28">
         <v>0.165</v>
       </c>
       <c r="W28">
-        <v>0.05113257491321597</v>
+        <v>0.05322007491321597</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y28">
-        <v>3.056391621266198</v>
+        <v>2.827748404551951</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07199588304379585</v>
+        <v>0.07202830498331116</v>
       </c>
       <c r="C29">
-        <v>20787.34285716506</v>
+        <v>20447.5269320966</v>
       </c>
       <c r="D29">
-        <v>25937.87385716506</v>
+        <v>25905.8109320966</v>
       </c>
       <c r="E29">
-        <v>-748.1689999999999</v>
+        <v>-440.4159999999993</v>
       </c>
       <c r="F29">
-        <v>8309.331</v>
+        <v>8617.084000000001</v>
       </c>
       <c r="G29">
         <v>3158.8</v>
@@ -3671,28 +3671,28 @@
         <v>1497.6</v>
       </c>
       <c r="M29">
-        <v>529.6086446691111</v>
+        <v>549.223779656856</v>
       </c>
       <c r="N29">
-        <v>967.9913553308888</v>
+        <v>948.3762203431439</v>
       </c>
       <c r="O29">
-        <v>159.7185736295967</v>
+        <v>156.4820763566188</v>
       </c>
       <c r="P29">
-        <v>808.2727817012922</v>
+        <v>791.8941439865251</v>
       </c>
       <c r="Q29">
-        <v>1572.172781701292</v>
+        <v>1555.794143986525</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07894036002359937</v>
+        <v>0.07934261667723706</v>
       </c>
       <c r="T29">
-        <v>0.6459673009796256</v>
+        <v>0.65380803187894</v>
       </c>
       <c r="U29">
         <v>0.06373661666253409</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.827748404551951</v>
+        <v>2.726757390103667</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07202830498331116</v>
+        <v>0.07206072692282646</v>
       </c>
       <c r="C30">
-        <v>20447.5269320966</v>
+        <v>20107.79017789194</v>
       </c>
       <c r="D30">
-        <v>25905.8109320966</v>
+        <v>25873.82717789194</v>
       </c>
       <c r="E30">
-        <v>-440.4159999999993</v>
+        <v>-132.6629999999986</v>
       </c>
       <c r="F30">
-        <v>8617.084000000001</v>
+        <v>8924.837000000001</v>
       </c>
       <c r="G30">
         <v>3158.8</v>
@@ -3753,28 +3753,28 @@
         <v>1497.6</v>
       </c>
       <c r="M30">
-        <v>549.223779656856</v>
+        <v>568.8389146446009</v>
       </c>
       <c r="N30">
-        <v>948.3762203431439</v>
+        <v>928.761085355399</v>
       </c>
       <c r="O30">
-        <v>156.4820763566188</v>
+        <v>153.2455790836408</v>
       </c>
       <c r="P30">
-        <v>791.8941439865251</v>
+        <v>775.5155062717581</v>
       </c>
       <c r="Q30">
-        <v>1555.794143986525</v>
+        <v>1539.415506271758</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07934261667723706</v>
+        <v>0.07975620450421667</v>
       </c>
       <c r="T30">
-        <v>0.65380803187894</v>
+        <v>0.6618696284373898</v>
       </c>
       <c r="U30">
         <v>0.06373661666253409</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.726757390103667</v>
+        <v>2.63273127320354</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07206072692282646</v>
+        <v>0.07209314886234176</v>
       </c>
       <c r="C31">
-        <v>20107.79017789194</v>
+        <v>19768.13230167559</v>
       </c>
       <c r="D31">
-        <v>25873.82717789194</v>
+        <v>25841.92230167559</v>
       </c>
       <c r="E31">
-        <v>-132.6630000000005</v>
+        <v>175.0900000000001</v>
       </c>
       <c r="F31">
-        <v>8924.837</v>
+        <v>9232.59</v>
       </c>
       <c r="G31">
         <v>3158.8</v>
@@ -3835,28 +3835,28 @@
         <v>1497.6</v>
       </c>
       <c r="M31">
-        <v>568.8389146446008</v>
+        <v>588.4540496323457</v>
       </c>
       <c r="N31">
-        <v>928.7610853553991</v>
+        <v>909.1459503676542</v>
       </c>
       <c r="O31">
-        <v>153.2455790836409</v>
+        <v>150.009081810663</v>
       </c>
       <c r="P31">
-        <v>775.5155062717582</v>
+        <v>759.1368685569912</v>
       </c>
       <c r="Q31">
-        <v>1539.415506271758</v>
+        <v>1523.036868556991</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07975620450421667</v>
+        <v>0.08018160912625283</v>
       </c>
       <c r="T31">
-        <v>0.6618696284373898</v>
+        <v>0.6701615563260812</v>
       </c>
       <c r="U31">
         <v>0.06373661666253409</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.63273127320354</v>
+        <v>2.544973564096756</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07209314886234176</v>
+        <v>0.07303154580185707</v>
       </c>
       <c r="C32">
-        <v>19768.13230167559</v>
+        <v>18569.86867934321</v>
       </c>
       <c r="D32">
-        <v>25841.92230167559</v>
+        <v>24951.4116793432</v>
       </c>
       <c r="E32">
-        <v>175.0900000000001</v>
+        <v>482.8429999999989</v>
       </c>
       <c r="F32">
-        <v>9232.59</v>
+        <v>9540.342999999999</v>
       </c>
       <c r="G32">
         <v>3158.8</v>
@@ -3917,45 +3917,45 @@
         <v>1497.6</v>
       </c>
       <c r="M32">
-        <v>588.4540496323457</v>
+        <v>641.4603851200905</v>
       </c>
       <c r="N32">
-        <v>909.1459503676542</v>
+        <v>856.1396148799095</v>
       </c>
       <c r="O32">
-        <v>150.009081810663</v>
+        <v>141.2630364551851</v>
       </c>
       <c r="P32">
-        <v>759.1368685569912</v>
+        <v>714.8765784247244</v>
       </c>
       <c r="Q32">
-        <v>1523.036868556991</v>
+        <v>1478.776578424724</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08018160912625283</v>
+        <v>0.08061934431704365</v>
       </c>
       <c r="T32">
-        <v>0.6701615563260812</v>
+        <v>0.6786938299506766</v>
       </c>
       <c r="U32">
-        <v>0.06373661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V32">
         <v>0.165</v>
       </c>
       <c r="W32">
-        <v>0.05322007491321597</v>
+        <v>0.05614257491321597</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>2.544973564096756</v>
+        <v>2.334672623188769</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07303154580185707</v>
+        <v>0.07309319274137235</v>
       </c>
       <c r="C33">
-        <v>18569.86867934321</v>
+        <v>18205.75810398758</v>
       </c>
       <c r="D33">
-        <v>24951.4116793432</v>
+        <v>24895.05410398758</v>
       </c>
       <c r="E33">
-        <v>482.8429999999989</v>
+        <v>790.5959999999995</v>
       </c>
       <c r="F33">
-        <v>9540.342999999999</v>
+        <v>9848.096</v>
       </c>
       <c r="G33">
         <v>3158.8</v>
@@ -3999,28 +3999,28 @@
         <v>1497.6</v>
       </c>
       <c r="M33">
-        <v>641.4603851200905</v>
+        <v>662.1526556078353</v>
       </c>
       <c r="N33">
-        <v>856.1396148799095</v>
+        <v>835.4473443921646</v>
       </c>
       <c r="O33">
-        <v>141.2630364551851</v>
+        <v>137.8488118247072</v>
       </c>
       <c r="P33">
-        <v>714.8765784247244</v>
+        <v>697.5985325674575</v>
       </c>
       <c r="Q33">
-        <v>1478.776578424724</v>
+        <v>1461.498532567457</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08061934431704365</v>
+        <v>0.0810699540722695</v>
       </c>
       <c r="T33">
-        <v>0.6786938299506766</v>
+        <v>0.6874770527995249</v>
       </c>
       <c r="U33">
         <v>0.0672366166625341</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.334672623188769</v>
+        <v>2.26171410371412</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07309319274137235</v>
+        <v>0.07392637968088767</v>
       </c>
       <c r="C34">
-        <v>18205.75810398758</v>
+        <v>17160.53962946495</v>
       </c>
       <c r="D34">
-        <v>24895.05410398758</v>
+        <v>24157.58862946495</v>
       </c>
       <c r="E34">
-        <v>790.5959999999995</v>
+        <v>1098.349</v>
       </c>
       <c r="F34">
-        <v>9848.096</v>
+        <v>10155.849</v>
       </c>
       <c r="G34">
         <v>3158.8</v>
@@ -4081,45 +4081,45 @@
         <v>1497.6</v>
       </c>
       <c r="M34">
-        <v>662.1526556078353</v>
+        <v>711.2813032955802</v>
       </c>
       <c r="N34">
-        <v>835.4473443921646</v>
+        <v>786.3186967044197</v>
       </c>
       <c r="O34">
-        <v>137.8488118247072</v>
+        <v>129.7425849562293</v>
       </c>
       <c r="P34">
-        <v>697.5985325674575</v>
+        <v>656.5761117481904</v>
       </c>
       <c r="Q34">
-        <v>1461.498532567457</v>
+        <v>1420.47611174819</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.0810699540722695</v>
+        <v>0.08153401486496478</v>
       </c>
       <c r="T34">
-        <v>0.6874770527995249</v>
+        <v>0.696522461405055</v>
       </c>
       <c r="U34">
-        <v>0.0672366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V34">
         <v>0.165</v>
       </c>
       <c r="W34">
-        <v>0.05614257491321597</v>
+        <v>0.05848057491321597</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y34">
-        <v>2.26171410371412</v>
+        <v>2.105496085811856</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07392637968088767</v>
+        <v>0.07401140662040297</v>
       </c>
       <c r="C35">
-        <v>17160.53962946495</v>
+        <v>16779.97757549358</v>
       </c>
       <c r="D35">
-        <v>24157.58862946495</v>
+        <v>24084.77957549359</v>
       </c>
       <c r="E35">
-        <v>1098.349</v>
+        <v>1406.102000000001</v>
       </c>
       <c r="F35">
-        <v>10155.849</v>
+        <v>10463.602</v>
       </c>
       <c r="G35">
         <v>3158.8</v>
@@ -4163,28 +4163,28 @@
         <v>1497.6</v>
       </c>
       <c r="M35">
-        <v>711.2813032955802</v>
+        <v>732.8352821833251</v>
       </c>
       <c r="N35">
-        <v>786.3186967044197</v>
+        <v>764.7647178166748</v>
       </c>
       <c r="O35">
-        <v>129.7425849562293</v>
+        <v>126.1861784397513</v>
       </c>
       <c r="P35">
-        <v>656.5761117481904</v>
+        <v>638.5785393769235</v>
       </c>
       <c r="Q35">
-        <v>1420.47611174819</v>
+        <v>1402.478539376923</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08153401486496478</v>
+        <v>0.08201213810592356</v>
       </c>
       <c r="T35">
-        <v>0.696522461405055</v>
+        <v>0.705841973301662</v>
       </c>
       <c r="U35">
         <v>0.07003661666253409</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.105496085811856</v>
+        <v>2.043569730346801</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07401140662040297</v>
+        <v>0.07637598355991829</v>
       </c>
       <c r="C36">
-        <v>16779.97757549358</v>
+        <v>14609.64134032409</v>
       </c>
       <c r="D36">
-        <v>24084.77957549359</v>
+        <v>22222.1963403241</v>
       </c>
       <c r="E36">
-        <v>1406.102000000001</v>
+        <v>1713.855000000001</v>
       </c>
       <c r="F36">
-        <v>10463.602</v>
+        <v>10771.355</v>
       </c>
       <c r="G36">
         <v>3158.8</v>
@@ -4245,45 +4245,45 @@
         <v>1497.6</v>
       </c>
       <c r="M36">
-        <v>732.8352821833251</v>
+        <v>838.4058300710702</v>
       </c>
       <c r="N36">
-        <v>764.7647178166748</v>
+        <v>659.1941699289297</v>
       </c>
       <c r="O36">
-        <v>126.1861784397513</v>
+        <v>108.7670380382734</v>
       </c>
       <c r="P36">
-        <v>638.5785393769235</v>
+        <v>550.4271318906563</v>
       </c>
       <c r="Q36">
-        <v>1402.478539376923</v>
+        <v>1314.327131890656</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08201213810592356</v>
+        <v>0.08250497283121953</v>
       </c>
       <c r="T36">
-        <v>0.705841973301662</v>
+        <v>0.7154482394104723</v>
       </c>
       <c r="U36">
-        <v>0.07003661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V36">
         <v>0.165</v>
       </c>
       <c r="W36">
-        <v>0.05848057491321597</v>
+        <v>0.06499357491321597</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y36">
-        <v>2.043569730346801</v>
+        <v>1.786247120768532</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07637598355991829</v>
+        <v>0.07769848049943358</v>
       </c>
       <c r="C37">
-        <v>14609.64134032409</v>
+        <v>13380.5658763933</v>
       </c>
       <c r="D37">
-        <v>22222.1963403241</v>
+        <v>21300.8738763933</v>
       </c>
       <c r="E37">
-        <v>1713.855000000001</v>
+        <v>2021.608</v>
       </c>
       <c r="F37">
-        <v>10771.355</v>
+        <v>11079.108</v>
       </c>
       <c r="G37">
         <v>3158.8</v>
@@ -4327,45 +4327,45 @@
         <v>1497.6</v>
       </c>
       <c r="M37">
-        <v>838.4058300710702</v>
+        <v>905.5688035588148</v>
       </c>
       <c r="N37">
-        <v>659.1941699289297</v>
+        <v>592.0311964411851</v>
       </c>
       <c r="O37">
-        <v>108.7670380382734</v>
+        <v>97.68514741279554</v>
       </c>
       <c r="P37">
-        <v>550.4271318906563</v>
+        <v>494.3460490283895</v>
       </c>
       <c r="Q37">
-        <v>1314.327131890656</v>
+        <v>1258.24604902839</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08250497283121953</v>
+        <v>0.08301320864168099</v>
       </c>
       <c r="T37">
-        <v>0.7154482394104723</v>
+        <v>0.7253547013351828</v>
       </c>
       <c r="U37">
-        <v>0.07783661666253411</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V37">
         <v>0.165</v>
       </c>
       <c r="W37">
-        <v>0.06499357491321597</v>
+        <v>0.06825007491321597</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y37">
-        <v>1.786247120768532</v>
+        <v>1.653767216929899</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07769848049943359</v>
+        <v>0.07788120243894889</v>
       </c>
       <c r="C38">
-        <v>13380.5658763933</v>
+        <v>12951.49145786255</v>
       </c>
       <c r="D38">
-        <v>21300.8738763933</v>
+        <v>21179.55245786255</v>
       </c>
       <c r="E38">
-        <v>2021.608</v>
+        <v>2329.360999999999</v>
       </c>
       <c r="F38">
-        <v>11079.108</v>
+        <v>11386.861</v>
       </c>
       <c r="G38">
         <v>3158.8</v>
@@ -4409,28 +4409,28 @@
         <v>1497.6</v>
       </c>
       <c r="M38">
-        <v>905.5688035588148</v>
+        <v>930.7234925465596</v>
       </c>
       <c r="N38">
-        <v>592.0311964411851</v>
+        <v>566.8765074534404</v>
       </c>
       <c r="O38">
-        <v>97.68514741279554</v>
+        <v>93.53462372981767</v>
       </c>
       <c r="P38">
-        <v>494.3460490283895</v>
+        <v>473.3418837236227</v>
       </c>
       <c r="Q38">
-        <v>1258.24604902839</v>
+        <v>1237.241883723623</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08301320864168099</v>
+        <v>0.08353757892231584</v>
       </c>
       <c r="T38">
-        <v>0.7253547013351828</v>
+        <v>0.735575654114646</v>
       </c>
       <c r="U38">
         <v>0.0817366166625341</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>1.653767216929899</v>
+        <v>1.609070805661524</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07788120243894889</v>
+        <v>0.07806392437846418</v>
       </c>
       <c r="C39">
-        <v>12951.49145786255</v>
+        <v>12523.79121096937</v>
       </c>
       <c r="D39">
-        <v>21179.55245786255</v>
+        <v>21059.60521096937</v>
       </c>
       <c r="E39">
-        <v>2329.360999999999</v>
+        <v>2637.114</v>
       </c>
       <c r="F39">
-        <v>11386.861</v>
+        <v>11694.614</v>
       </c>
       <c r="G39">
         <v>3158.8</v>
@@ -4491,28 +4491,28 @@
         <v>1497.6</v>
       </c>
       <c r="M39">
-        <v>930.7234925465596</v>
+        <v>955.8781815343044</v>
       </c>
       <c r="N39">
-        <v>566.8765074534404</v>
+        <v>541.7218184656955</v>
       </c>
       <c r="O39">
-        <v>93.53462372981767</v>
+        <v>89.38410004683976</v>
       </c>
       <c r="P39">
-        <v>473.3418837236227</v>
+        <v>452.3377184188557</v>
       </c>
       <c r="Q39">
-        <v>1237.241883723623</v>
+        <v>1216.237718418856</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08353757892231584</v>
+        <v>0.08407886437329373</v>
       </c>
       <c r="T39">
-        <v>0.735575654114646</v>
+        <v>0.7461263150482854</v>
       </c>
       <c r="U39">
         <v>0.0817366166625341</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>1.609070805661524</v>
+        <v>1.566726837091484</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07806392437846418</v>
+        <v>0.07824664631797949</v>
       </c>
       <c r="C40">
-        <v>12523.79121096937</v>
+        <v>12097.44191994243</v>
       </c>
       <c r="D40">
-        <v>21059.60521096937</v>
+        <v>20941.00891994243</v>
       </c>
       <c r="E40">
-        <v>2637.114</v>
+        <v>2944.867</v>
       </c>
       <c r="F40">
-        <v>11694.614</v>
+        <v>12002.367</v>
       </c>
       <c r="G40">
         <v>3158.8</v>
@@ -4573,28 +4573,28 @@
         <v>1497.6</v>
       </c>
       <c r="M40">
-        <v>955.8781815343044</v>
+        <v>981.0328705220494</v>
       </c>
       <c r="N40">
-        <v>541.7218184656955</v>
+        <v>516.5671294779505</v>
       </c>
       <c r="O40">
-        <v>89.38410004683976</v>
+        <v>85.23357636386184</v>
       </c>
       <c r="P40">
-        <v>452.3377184188557</v>
+        <v>431.3335531140887</v>
       </c>
       <c r="Q40">
-        <v>1216.237718418856</v>
+        <v>1195.233553114089</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08407886437329373</v>
+        <v>0.08463789688823814</v>
       </c>
       <c r="T40">
-        <v>0.7461263150482854</v>
+        <v>0.7570228992912246</v>
       </c>
       <c r="U40">
         <v>0.0817366166625341</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>1.566726837091484</v>
+        <v>1.526554354089138</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07824664631797949</v>
+        <v>0.08317216825749479</v>
       </c>
       <c r="C41">
-        <v>12097.44191994243</v>
+        <v>9029.73669667059</v>
       </c>
       <c r="D41">
-        <v>20941.00891994243</v>
+        <v>18181.05669667059</v>
       </c>
       <c r="E41">
-        <v>2944.867</v>
+        <v>3252.620000000001</v>
       </c>
       <c r="F41">
-        <v>12002.367</v>
+        <v>12310.12</v>
       </c>
       <c r="G41">
         <v>3158.8</v>
@@ -4655,45 +4655,45 @@
         <v>1497.6</v>
       </c>
       <c r="M41">
-        <v>981.0328705220494</v>
+        <v>1180.991263509794</v>
       </c>
       <c r="N41">
-        <v>516.5671294779505</v>
+        <v>316.6087364902055</v>
       </c>
       <c r="O41">
-        <v>85.23357636386184</v>
+        <v>52.24044152088391</v>
       </c>
       <c r="P41">
-        <v>431.3335531140887</v>
+        <v>264.3682949693216</v>
       </c>
       <c r="Q41">
-        <v>1195.233553114089</v>
+        <v>1028.268294969322</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08463789688823814</v>
+        <v>0.08521556382034734</v>
       </c>
       <c r="T41">
-        <v>0.7570228992912246</v>
+        <v>0.7682827030089284</v>
       </c>
       <c r="U41">
-        <v>0.0817366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V41">
         <v>0.165</v>
       </c>
       <c r="W41">
-        <v>0.06825007491321597</v>
+        <v>0.08010707491321598</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y41">
-        <v>1.526554354089138</v>
+        <v>1.268087280806188</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08317216825749479</v>
+        <v>0.09374070974902919</v>
       </c>
       <c r="C42">
-        <v>9029.73669667059</v>
+        <v>4713.965186627704</v>
       </c>
       <c r="D42">
-        <v>18181.05669667059</v>
+        <v>14173.03818662771</v>
       </c>
       <c r="E42">
-        <v>3252.620000000001</v>
+        <v>3560.373000000001</v>
       </c>
       <c r="F42">
-        <v>12310.12</v>
+        <v>12617.873</v>
       </c>
       <c r="G42">
         <v>3158.8</v>
@@ -4737,45 +4737,45 @@
         <v>1497.6</v>
       </c>
       <c r="M42">
-        <v>1180.991263509794</v>
+        <v>1571.387212897539</v>
       </c>
       <c r="N42">
-        <v>316.6087364902055</v>
+        <v>-73.78721289753935</v>
       </c>
       <c r="O42">
-        <v>52.24044152088391</v>
+        <v>-12.17489012809399</v>
       </c>
       <c r="P42">
-        <v>264.3682949693216</v>
+        <v>-61.61232276944536</v>
       </c>
       <c r="Q42">
-        <v>1028.268294969322</v>
+        <v>702.2876772305547</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08521556382034734</v>
+        <v>0.08594914091306874</v>
       </c>
       <c r="T42">
-        <v>0.7682827030089284</v>
+        <v>0.782581485952393</v>
       </c>
       <c r="U42">
-        <v>0.0959366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V42">
-        <v>0.165</v>
+        <v>0.1572521387292924</v>
       </c>
       <c r="W42">
-        <v>0.08010707491321598</v>
+        <v>0.1049529673422406</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y42">
-        <v>1.268087280806188</v>
+        <v>0.9530432650260146</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09374070974902919</v>
+        <v>0.09452807591565454</v>
       </c>
       <c r="C43">
-        <v>4713.965186627704</v>
+        <v>4177.19902456984</v>
       </c>
       <c r="D43">
-        <v>14173.03818662771</v>
+        <v>13944.02502456984</v>
       </c>
       <c r="E43">
-        <v>3560.373000000001</v>
+        <v>3868.126</v>
       </c>
       <c r="F43">
-        <v>12617.873</v>
+        <v>12925.626</v>
       </c>
       <c r="G43">
         <v>3158.8</v>
@@ -4819,37 +4819,37 @@
         <v>1497.6</v>
       </c>
       <c r="M43">
-        <v>1571.387212897539</v>
+        <v>1609.713730285284</v>
       </c>
       <c r="N43">
-        <v>-73.78721289753935</v>
+        <v>-112.1137302852842</v>
       </c>
       <c r="O43">
-        <v>-12.17489012809399</v>
+        <v>-18.49876549707189</v>
       </c>
       <c r="P43">
-        <v>-61.61232276944536</v>
+        <v>-93.61496478821229</v>
       </c>
       <c r="Q43">
-        <v>702.2876772305547</v>
+        <v>670.2850352117877</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08594914091306874</v>
+        <v>0.08664136748053544</v>
       </c>
       <c r="T43">
-        <v>0.782581485952393</v>
+        <v>0.7960742701929514</v>
       </c>
       <c r="U43">
         <v>0.1245366166625341</v>
       </c>
       <c r="V43">
-        <v>0.1572521387292924</v>
+        <v>0.1535080401881188</v>
       </c>
       <c r="W43">
-        <v>0.1049529673422406</v>
+        <v>0.1054192447070095</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.9530432650260146</v>
+        <v>0.9303517587158714</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09452807591565454</v>
+        <v>0.09531544208227988</v>
       </c>
       <c r="C44">
-        <v>4177.199024569842</v>
+        <v>3647.71613447456</v>
       </c>
       <c r="D44">
-        <v>13944.02502456984</v>
+        <v>13722.29513447456</v>
       </c>
       <c r="E44">
-        <v>3868.125999999998</v>
+        <v>4175.878999999999</v>
       </c>
       <c r="F44">
-        <v>12925.626</v>
+        <v>13233.379</v>
       </c>
       <c r="G44">
         <v>3158.8</v>
@@ -4901,37 +4901,37 @@
         <v>1497.6</v>
       </c>
       <c r="M44">
-        <v>1609.713730285284</v>
+        <v>1648.040247673029</v>
       </c>
       <c r="N44">
-        <v>-112.113730285284</v>
+        <v>-150.4402476730288</v>
       </c>
       <c r="O44">
-        <v>-18.49876549707185</v>
+        <v>-24.82264086604975</v>
       </c>
       <c r="P44">
-        <v>-93.61496478821211</v>
+        <v>-125.6176068069791</v>
       </c>
       <c r="Q44">
-        <v>670.2850352117879</v>
+        <v>638.2823931930209</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08664136748053544</v>
+        <v>0.08735788269949218</v>
       </c>
       <c r="T44">
-        <v>0.7960742701929513</v>
+        <v>0.8100404854594943</v>
       </c>
       <c r="U44">
         <v>0.1245366166625341</v>
       </c>
       <c r="V44">
-        <v>0.1535080401881188</v>
+        <v>0.1499380857651393</v>
       </c>
       <c r="W44">
-        <v>0.1054192447070095</v>
+        <v>0.1058638347524868</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.9303517587158715</v>
+        <v>0.9087156713038745</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09531544208227988</v>
+        <v>0.09610280824890521</v>
       </c>
       <c r="C45">
-        <v>3647.71613447456</v>
+        <v>3125.174511464274</v>
       </c>
       <c r="D45">
-        <v>13722.29513447456</v>
+        <v>13507.50651146427</v>
       </c>
       <c r="E45">
-        <v>4175.878999999999</v>
+        <v>4483.632</v>
       </c>
       <c r="F45">
-        <v>13233.379</v>
+        <v>13541.132</v>
       </c>
       <c r="G45">
         <v>3158.8</v>
@@ -4983,37 +4983,37 @@
         <v>1497.6</v>
       </c>
       <c r="M45">
-        <v>1648.040247673029</v>
+        <v>1686.366765060774</v>
       </c>
       <c r="N45">
-        <v>-150.4402476730288</v>
+        <v>-188.7667650607737</v>
       </c>
       <c r="O45">
-        <v>-24.82264086604975</v>
+        <v>-31.14651623502765</v>
       </c>
       <c r="P45">
-        <v>-125.6176068069791</v>
+        <v>-157.620248825746</v>
       </c>
       <c r="Q45">
-        <v>638.2823931930209</v>
+        <v>606.279751174254</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08735788269949218</v>
+        <v>0.08809998774769742</v>
       </c>
       <c r="T45">
-        <v>0.8100404854594943</v>
+        <v>0.8245054941284139</v>
       </c>
       <c r="U45">
         <v>0.1245366166625341</v>
       </c>
       <c r="V45">
-        <v>0.1499380857651393</v>
+        <v>0.1465304019977498</v>
       </c>
       <c r="W45">
-        <v>0.1058638347524868</v>
+        <v>0.1062882161595333</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.9087156713038745</v>
+        <v>0.8880630424106046</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09610280824890521</v>
+        <v>0.09689017441553055</v>
       </c>
       <c r="C46">
-        <v>3125.174511464274</v>
+        <v>2609.253233624817</v>
       </c>
       <c r="D46">
-        <v>13507.50651146427</v>
+        <v>13299.33823362482</v>
       </c>
       <c r="E46">
-        <v>4483.632</v>
+        <v>4791.385</v>
       </c>
       <c r="F46">
-        <v>13541.132</v>
+        <v>13848.885</v>
       </c>
       <c r="G46">
         <v>3158.8</v>
@@ -5065,37 +5065,37 @@
         <v>1497.6</v>
       </c>
       <c r="M46">
-        <v>1686.366765060774</v>
+        <v>1724.693282448519</v>
       </c>
       <c r="N46">
-        <v>-188.7667650607737</v>
+        <v>-227.0932824485187</v>
       </c>
       <c r="O46">
-        <v>-31.14651623502765</v>
+        <v>-37.47039160400559</v>
       </c>
       <c r="P46">
-        <v>-157.620248825746</v>
+        <v>-189.6228908445131</v>
       </c>
       <c r="Q46">
-        <v>606.279751174254</v>
+        <v>574.2771091554869</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08809998774769742</v>
+        <v>0.08886907843401919</v>
       </c>
       <c r="T46">
-        <v>0.8245054941284139</v>
+        <v>0.8394965031125668</v>
       </c>
       <c r="U46">
         <v>0.1245366166625341</v>
       </c>
       <c r="V46">
-        <v>0.1465304019977498</v>
+        <v>0.1432741708422442</v>
       </c>
       <c r="W46">
-        <v>0.1062882161595333</v>
+        <v>0.1066937361707111</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.8880630424106046</v>
+        <v>0.8683283081348133</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09689017441553055</v>
+        <v>0.09767754058215591</v>
       </c>
       <c r="C47">
-        <v>2609.253233624817</v>
+        <v>2099.650862082615</v>
       </c>
       <c r="D47">
-        <v>13299.33823362482</v>
+        <v>13097.48886208262</v>
       </c>
       <c r="E47">
-        <v>4791.385</v>
+        <v>5099.138000000001</v>
       </c>
       <c r="F47">
-        <v>13848.885</v>
+        <v>14156.638</v>
       </c>
       <c r="G47">
         <v>3158.8</v>
@@ -5147,37 +5147,37 @@
         <v>1497.6</v>
       </c>
       <c r="M47">
-        <v>1724.693282448519</v>
+        <v>1763.019799836263</v>
       </c>
       <c r="N47">
-        <v>-227.0932824485187</v>
+        <v>-265.4197998362636</v>
       </c>
       <c r="O47">
-        <v>-37.47039160400559</v>
+        <v>-43.79426697298349</v>
       </c>
       <c r="P47">
-        <v>-189.6228908445131</v>
+        <v>-221.6255328632801</v>
       </c>
       <c r="Q47">
-        <v>574.2771091554869</v>
+        <v>542.27446713672</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08886907843401919</v>
+        <v>0.0896666539605751</v>
       </c>
       <c r="T47">
-        <v>0.8394965031125668</v>
+        <v>0.8550427346516886</v>
       </c>
       <c r="U47">
         <v>0.1245366166625341</v>
       </c>
       <c r="V47">
-        <v>0.1432741708422442</v>
+        <v>0.1401595149543693</v>
       </c>
       <c r="W47">
-        <v>0.1066937361707111</v>
+        <v>0.1070816248770551</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.8683283081348133</v>
+        <v>0.8494516057840565</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09767754058215591</v>
+        <v>0.09846490674878125</v>
       </c>
       <c r="C48">
-        <v>2099.650862082615</v>
+        <v>1596.08398459968</v>
       </c>
       <c r="D48">
-        <v>13097.48886208262</v>
+        <v>12901.67498459968</v>
       </c>
       <c r="E48">
-        <v>5099.138000000001</v>
+        <v>5406.891000000001</v>
       </c>
       <c r="F48">
-        <v>14156.638</v>
+        <v>14464.391</v>
       </c>
       <c r="G48">
         <v>3158.8</v>
@@ -5229,37 +5229,37 @@
         <v>1497.6</v>
       </c>
       <c r="M48">
-        <v>1763.019799836263</v>
+        <v>1801.346317224009</v>
       </c>
       <c r="N48">
-        <v>-265.4197998362636</v>
+        <v>-303.7463172240086</v>
       </c>
       <c r="O48">
-        <v>-43.79426697298349</v>
+        <v>-50.11814234196143</v>
       </c>
       <c r="P48">
-        <v>-221.6255328632801</v>
+        <v>-253.6281748820472</v>
       </c>
       <c r="Q48">
-        <v>542.27446713672</v>
+        <v>510.2718251179527</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.0896666539605751</v>
+        <v>0.09049432667681237</v>
       </c>
       <c r="T48">
-        <v>0.8550427346516886</v>
+        <v>0.8711756164375695</v>
       </c>
       <c r="U48">
         <v>0.1245366166625341</v>
       </c>
       <c r="V48">
-        <v>0.1401595149543693</v>
+        <v>0.1371773976149147</v>
       </c>
       <c r="W48">
-        <v>0.1070816248770551</v>
+        <v>0.1074530076810015</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.8494516057840565</v>
+        <v>0.8313781673631191</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09846490674878125</v>
+        <v>0.09925227291540659</v>
       </c>
       <c r="C49">
-        <v>1596.08398459968</v>
+        <v>1098.285887887949</v>
       </c>
       <c r="D49">
-        <v>12901.67498459968</v>
+        <v>12711.62988788795</v>
       </c>
       <c r="E49">
-        <v>5406.891000000001</v>
+        <v>5714.644</v>
       </c>
       <c r="F49">
-        <v>14464.391</v>
+        <v>14772.144</v>
       </c>
       <c r="G49">
         <v>3158.8</v>
@@ -5311,37 +5311,37 @@
         <v>1497.6</v>
       </c>
       <c r="M49">
-        <v>1801.346317224009</v>
+        <v>1839.672834611753</v>
       </c>
       <c r="N49">
-        <v>-303.7463172240086</v>
+        <v>-342.0728346117533</v>
       </c>
       <c r="O49">
-        <v>-50.11814234196143</v>
+        <v>-56.44201771093929</v>
       </c>
       <c r="P49">
-        <v>-253.6281748820472</v>
+        <v>-285.630816900814</v>
       </c>
       <c r="Q49">
-        <v>510.2718251179527</v>
+        <v>478.269183099186</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09049432667681237</v>
+        <v>0.09135383295905876</v>
       </c>
       <c r="T49">
-        <v>0.8711756164375695</v>
+        <v>0.8879289936767535</v>
       </c>
       <c r="U49">
         <v>0.1245366166625341</v>
       </c>
       <c r="V49">
-        <v>0.1371773976149147</v>
+        <v>0.1343195351646039</v>
       </c>
       <c r="W49">
-        <v>0.1074530076810015</v>
+        <v>0.1078089162014501</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.8313781673631191</v>
+        <v>0.8140577888763876</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09925227291540659</v>
+        <v>0.1141590496513008</v>
       </c>
       <c r="C50">
-        <v>1098.285887887951</v>
+        <v>-1981.439947525212</v>
       </c>
       <c r="D50">
-        <v>12711.62988788795</v>
+        <v>9939.657052474786</v>
       </c>
       <c r="E50">
-        <v>5714.643999999998</v>
+        <v>6022.396999999999</v>
       </c>
       <c r="F50">
-        <v>14772.144</v>
+        <v>15079.897</v>
       </c>
       <c r="G50">
         <v>3158.8</v>
@@ -5393,45 +5393,45 @@
         <v>1497.6</v>
       </c>
       <c r="M50">
-        <v>1839.672834611753</v>
+        <v>2303.252447399498</v>
       </c>
       <c r="N50">
-        <v>-342.072834611753</v>
+        <v>-805.6524473994978</v>
       </c>
       <c r="O50">
-        <v>-56.44201771093925</v>
+        <v>-132.9326538209171</v>
       </c>
       <c r="P50">
-        <v>-285.6308169008138</v>
+        <v>-672.7197935785806</v>
       </c>
       <c r="Q50">
-        <v>478.2691830991862</v>
+        <v>91.18020642141937</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09135383295905876</v>
+        <v>0.09283804648623414</v>
       </c>
       <c r="T50">
-        <v>0.8879289936767535</v>
+        <v>0.9168590778865869</v>
       </c>
       <c r="U50">
-        <v>0.1245366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V50">
-        <v>0.134319535164604</v>
+        <v>0.1072848094784375</v>
       </c>
       <c r="W50">
-        <v>0.1078089162014501</v>
+        <v>0.136350297843513</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y50">
-        <v>0.8140577888763876</v>
+        <v>0.6502109665359848</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1141590496513008</v>
+        <v>0.1425760982821221</v>
       </c>
       <c r="C51">
-        <v>-1981.439947525212</v>
+        <v>-5207.844586181343</v>
       </c>
       <c r="D51">
-        <v>9939.657052474786</v>
+        <v>7021.005413818656</v>
       </c>
       <c r="E51">
-        <v>6022.396999999999</v>
+        <v>6330.15</v>
       </c>
       <c r="F51">
-        <v>15079.897</v>
+        <v>15387.65</v>
       </c>
       <c r="G51">
         <v>3158.8</v>
@@ -5475,45 +5475,45 @@
         <v>1497.6</v>
       </c>
       <c r="M51">
-        <v>2303.252447399498</v>
+        <v>3181.190699387243</v>
       </c>
       <c r="N51">
-        <v>-805.6524473994978</v>
+        <v>-1683.590699387243</v>
       </c>
       <c r="O51">
-        <v>-132.9326538209171</v>
+        <v>-277.792465398895</v>
       </c>
       <c r="P51">
-        <v>-672.7197935785806</v>
+        <v>-1405.798233988348</v>
       </c>
       <c r="Q51">
-        <v>91.18020642141937</v>
+        <v>-641.8982339883477</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09283804648623414</v>
+        <v>0.09447417234435083</v>
       </c>
       <c r="T51">
-        <v>0.9168590778865869</v>
+        <v>0.9487502161807397</v>
       </c>
       <c r="U51">
-        <v>0.1527366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V51">
-        <v>0.1072848094784375</v>
+        <v>0.07767657564433245</v>
       </c>
       <c r="W51">
-        <v>0.136350297843513</v>
+        <v>0.1906780242198934</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y51">
-        <v>0.6502109665359848</v>
+        <v>0.4707671251171663</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1425760982821221</v>
+        <v>0.1441854644487475</v>
       </c>
       <c r="C52">
-        <v>-5207.844586181343</v>
+        <v>-5630.445532796257</v>
       </c>
       <c r="D52">
-        <v>7021.005413818656</v>
+        <v>6906.157467203743</v>
       </c>
       <c r="E52">
-        <v>6330.15</v>
+        <v>6637.903</v>
       </c>
       <c r="F52">
-        <v>15387.65</v>
+        <v>15695.403</v>
       </c>
       <c r="G52">
         <v>3158.8</v>
@@ -5557,37 +5557,37 @@
         <v>1497.6</v>
       </c>
       <c r="M52">
-        <v>3181.190699387243</v>
+        <v>3244.814513374988</v>
       </c>
       <c r="N52">
-        <v>-1683.590699387243</v>
+        <v>-1747.214513374988</v>
       </c>
       <c r="O52">
-        <v>-277.792465398895</v>
+        <v>-288.290394706873</v>
       </c>
       <c r="P52">
-        <v>-1405.798233988348</v>
+        <v>-1458.924118668115</v>
       </c>
       <c r="Q52">
-        <v>-641.8982339883477</v>
+        <v>-695.0241186681147</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09447417234435083</v>
+        <v>0.095467522800358</v>
       </c>
       <c r="T52">
-        <v>0.9487502161807397</v>
+        <v>0.9681124654905509</v>
       </c>
       <c r="U52">
         <v>0.2067366166625341</v>
       </c>
       <c r="V52">
-        <v>0.07767657564433245</v>
+        <v>0.07615350553365925</v>
       </c>
       <c r="W52">
-        <v>0.1906780242198934</v>
+        <v>0.1909928985815138</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.4707671251171663</v>
+        <v>0.4615363971736924</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1441854644487475</v>
+        <v>0.1457948306153728</v>
       </c>
       <c r="C53">
-        <v>-5630.445532796257</v>
+        <v>-6049.349640315568</v>
       </c>
       <c r="D53">
-        <v>6906.157467203743</v>
+        <v>6795.006359684432</v>
       </c>
       <c r="E53">
-        <v>6637.903</v>
+        <v>6945.656000000001</v>
       </c>
       <c r="F53">
-        <v>15695.403</v>
+        <v>16003.156</v>
       </c>
       <c r="G53">
         <v>3158.8</v>
@@ -5639,37 +5639,37 @@
         <v>1497.6</v>
       </c>
       <c r="M53">
-        <v>3244.814513374988</v>
+        <v>3308.438327362733</v>
       </c>
       <c r="N53">
-        <v>-1747.214513374988</v>
+        <v>-1810.838327362733</v>
       </c>
       <c r="O53">
-        <v>-288.290394706873</v>
+        <v>-298.7883240148509</v>
       </c>
       <c r="P53">
-        <v>-1458.924118668115</v>
+        <v>-1512.050003347882</v>
       </c>
       <c r="Q53">
-        <v>-695.0241186681147</v>
+        <v>-748.150003347882</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.095467522800358</v>
+        <v>0.0965022628586988</v>
       </c>
       <c r="T53">
-        <v>0.9681124654905509</v>
+        <v>0.9882814751882707</v>
       </c>
       <c r="U53">
         <v>0.2067366166625341</v>
       </c>
       <c r="V53">
-        <v>0.07615350553365925</v>
+        <v>0.07468901504262734</v>
       </c>
       <c r="W53">
-        <v>0.1909928985815138</v>
+        <v>0.1912956623907642</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.4615363971736924</v>
+        <v>0.4526606972280445</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1457948306153728</v>
+        <v>0.1474041967819982</v>
       </c>
       <c r="C54">
-        <v>-6049.349640315568</v>
+        <v>-6464.732577696439</v>
       </c>
       <c r="D54">
-        <v>6795.006359684432</v>
+        <v>6687.37642230356</v>
       </c>
       <c r="E54">
-        <v>6945.656000000001</v>
+        <v>7253.409</v>
       </c>
       <c r="F54">
-        <v>16003.156</v>
+        <v>16310.909</v>
       </c>
       <c r="G54">
         <v>3158.8</v>
@@ -5721,37 +5721,37 @@
         <v>1497.6</v>
       </c>
       <c r="M54">
-        <v>3308.438327362733</v>
+        <v>3372.062141350477</v>
       </c>
       <c r="N54">
-        <v>-1810.838327362733</v>
+        <v>-1874.462141350477</v>
       </c>
       <c r="O54">
-        <v>-298.7883240148509</v>
+        <v>-309.2862533228288</v>
       </c>
       <c r="P54">
-        <v>-1512.050003347882</v>
+        <v>-1565.175888027649</v>
       </c>
       <c r="Q54">
-        <v>-748.150003347882</v>
+        <v>-801.2758880276486</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.0965022628586988</v>
+        <v>0.09758103440888388</v>
       </c>
       <c r="T54">
-        <v>0.9882814751882707</v>
+        <v>1.009308740617808</v>
       </c>
       <c r="U54">
         <v>0.2067366166625341</v>
       </c>
       <c r="V54">
-        <v>0.07468901504262734</v>
+        <v>0.07327978834370985</v>
       </c>
       <c r="W54">
-        <v>0.1912956623907642</v>
+        <v>0.1915870011506089</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.4526606972280445</v>
+        <v>0.4441199293558172</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1474041967819982</v>
+        <v>0.1490135629486235</v>
       </c>
       <c r="C55">
-        <v>-6464.732577696439</v>
+        <v>-6876.759057364034</v>
       </c>
       <c r="D55">
-        <v>6687.37642230356</v>
+        <v>6583.102942635966</v>
       </c>
       <c r="E55">
-        <v>7253.409</v>
+        <v>7561.162</v>
       </c>
       <c r="F55">
-        <v>16310.909</v>
+        <v>16618.662</v>
       </c>
       <c r="G55">
         <v>3158.8</v>
@@ -5803,37 +5803,37 @@
         <v>1497.6</v>
       </c>
       <c r="M55">
-        <v>3372.062141350477</v>
+        <v>3435.685955338222</v>
       </c>
       <c r="N55">
-        <v>-1874.462141350477</v>
+        <v>-1938.085955338222</v>
       </c>
       <c r="O55">
-        <v>-309.2862533228288</v>
+        <v>-319.7841826308067</v>
       </c>
       <c r="P55">
-        <v>-1565.175888027649</v>
+        <v>-1618.301772707416</v>
       </c>
       <c r="Q55">
-        <v>-801.2758880276486</v>
+        <v>-854.4017727074157</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09758103440888388</v>
+        <v>0.09870670906994655</v>
       </c>
       <c r="T55">
-        <v>1.009308740617808</v>
+        <v>1.031250234979065</v>
       </c>
       <c r="U55">
         <v>0.2067366166625341</v>
       </c>
       <c r="V55">
-        <v>0.07327978834370985</v>
+        <v>0.07192275522623374</v>
       </c>
       <c r="W55">
-        <v>0.1915870011506089</v>
+        <v>0.191867549586015</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.4441199293558172</v>
+        <v>0.4358954862195984</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1490135629486235</v>
+        <v>0.1506229291152488</v>
       </c>
       <c r="C56">
-        <v>-6876.759057364034</v>
+        <v>-7285.583676300019</v>
       </c>
       <c r="D56">
-        <v>6583.102942635966</v>
+        <v>6482.031323699981</v>
       </c>
       <c r="E56">
-        <v>7561.162</v>
+        <v>7868.915000000001</v>
       </c>
       <c r="F56">
-        <v>16618.662</v>
+        <v>16926.415</v>
       </c>
       <c r="G56">
         <v>3158.8</v>
@@ -5885,37 +5885,37 @@
         <v>1497.6</v>
       </c>
       <c r="M56">
-        <v>3435.685955338222</v>
+        <v>3499.309769325967</v>
       </c>
       <c r="N56">
-        <v>-1938.085955338222</v>
+        <v>-2001.709769325967</v>
       </c>
       <c r="O56">
-        <v>-319.7841826308067</v>
+        <v>-330.2821119387847</v>
       </c>
       <c r="P56">
-        <v>-1618.301772707416</v>
+        <v>-1671.427657387183</v>
       </c>
       <c r="Q56">
-        <v>-854.4017727074157</v>
+        <v>-907.5276573871828</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09870670906994655</v>
+        <v>0.09988241371594539</v>
       </c>
       <c r="T56">
-        <v>1.031250234979065</v>
+        <v>1.054166906867489</v>
       </c>
       <c r="U56">
         <v>0.2067366166625341</v>
       </c>
       <c r="V56">
-        <v>0.07192275522623374</v>
+        <v>0.07061506876757494</v>
       </c>
       <c r="W56">
-        <v>0.191867549586015</v>
+        <v>0.1921378962601335</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.4358954862195984</v>
+        <v>0.4279701137428784</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1506229291152488</v>
+        <v>0.1522322952818742</v>
       </c>
       <c r="C57">
-        <v>-7285.583676300019</v>
+        <v>-7691.351680822288</v>
       </c>
       <c r="D57">
-        <v>6482.031323699981</v>
+        <v>6384.016319177713</v>
       </c>
       <c r="E57">
-        <v>7868.915000000001</v>
+        <v>8176.668000000001</v>
       </c>
       <c r="F57">
-        <v>16926.415</v>
+        <v>17234.168</v>
       </c>
       <c r="G57">
         <v>3158.8</v>
@@ -5967,37 +5967,37 @@
         <v>1497.6</v>
       </c>
       <c r="M57">
-        <v>3499.309769325967</v>
+        <v>3562.933583313712</v>
       </c>
       <c r="N57">
-        <v>-2001.709769325967</v>
+        <v>-2065.333583313712</v>
       </c>
       <c r="O57">
-        <v>-330.2821119387847</v>
+        <v>-340.7800412467625</v>
       </c>
       <c r="P57">
-        <v>-1671.427657387183</v>
+        <v>-1724.55354206695</v>
       </c>
       <c r="Q57">
-        <v>-907.5276573871828</v>
+        <v>-960.6535420669496</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09988241371594539</v>
+        <v>0.1011115594822169</v>
       </c>
       <c r="T57">
-        <v>1.054166906867489</v>
+        <v>1.078125245659932</v>
       </c>
       <c r="U57">
         <v>0.2067366166625341</v>
       </c>
       <c r="V57">
-        <v>0.07061506876757494</v>
+        <v>0.0693540853967254</v>
       </c>
       <c r="W57">
-        <v>0.1921378962601335</v>
+        <v>0.1923985876958906</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.4279701137428784</v>
+        <v>0.4203277902831842</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1522322952818742</v>
+        <v>0.1538416614484995</v>
       </c>
       <c r="C58">
-        <v>-7691.351680822288</v>
+        <v>-8094.199663012712</v>
       </c>
       <c r="D58">
-        <v>6384.016319177713</v>
+        <v>6288.92133698729</v>
       </c>
       <c r="E58">
-        <v>8176.668000000001</v>
+        <v>8484.421000000002</v>
       </c>
       <c r="F58">
-        <v>17234.168</v>
+        <v>17541.921</v>
       </c>
       <c r="G58">
         <v>3158.8</v>
@@ -6049,37 +6049,37 @@
         <v>1497.6</v>
       </c>
       <c r="M58">
-        <v>3562.933583313712</v>
+        <v>3626.557397301457</v>
       </c>
       <c r="N58">
-        <v>-2065.333583313712</v>
+        <v>-2128.957397301457</v>
       </c>
       <c r="O58">
-        <v>-340.7800412467625</v>
+        <v>-351.2779705547404</v>
       </c>
       <c r="P58">
-        <v>-1724.55354206695</v>
+        <v>-1777.679426746717</v>
       </c>
       <c r="Q58">
-        <v>-960.6535420669496</v>
+        <v>-1013.779426746717</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1011115594822169</v>
+        <v>0.1023978748190126</v>
       </c>
       <c r="T58">
-        <v>1.078125245659932</v>
+        <v>1.103197925791558</v>
       </c>
       <c r="U58">
         <v>0.2067366166625341</v>
       </c>
       <c r="V58">
-        <v>0.0693540853967254</v>
+        <v>0.06813734705643196</v>
       </c>
       <c r="W58">
-        <v>0.1923985876958906</v>
+        <v>0.1926501320637265</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.4203277902831842</v>
+        <v>0.4129536185238301</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1538416614484995</v>
+        <v>0.1554510276151249</v>
       </c>
       <c r="C59">
-        <v>-8094.199663012712</v>
+        <v>-8494.256195815349</v>
       </c>
       <c r="D59">
-        <v>6288.92133698729</v>
+        <v>6196.617804184652</v>
       </c>
       <c r="E59">
-        <v>8484.421000000002</v>
+        <v>8792.174000000003</v>
       </c>
       <c r="F59">
-        <v>17541.921</v>
+        <v>17849.674</v>
       </c>
       <c r="G59">
         <v>3158.8</v>
@@ -6131,37 +6131,37 @@
         <v>1497.6</v>
       </c>
       <c r="M59">
-        <v>3626.557397301457</v>
+        <v>3690.181211289202</v>
       </c>
       <c r="N59">
-        <v>-2128.957397301457</v>
+        <v>-2192.581211289202</v>
       </c>
       <c r="O59">
-        <v>-351.2779705547404</v>
+        <v>-361.7758998627184</v>
       </c>
       <c r="P59">
-        <v>-1777.679426746717</v>
+        <v>-1830.805311426484</v>
       </c>
       <c r="Q59">
-        <v>-1013.779426746717</v>
+        <v>-1066.905311426484</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1023978748190126</v>
+        <v>0.1037454432670843</v>
       </c>
       <c r="T59">
-        <v>1.103197925791558</v>
+        <v>1.129464543072309</v>
       </c>
       <c r="U59">
         <v>0.2067366166625341</v>
       </c>
       <c r="V59">
-        <v>0.06813734705643196</v>
+        <v>0.0669625652106314</v>
       </c>
       <c r="W59">
-        <v>0.1926501320637265</v>
+        <v>0.1928930024878439</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.4129536185238301</v>
+        <v>0.4058337285492812</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1554510276151249</v>
+        <v>0.1570603937817502</v>
       </c>
       <c r="C60">
-        <v>-8494.256195815346</v>
+        <v>-8891.642413015037</v>
       </c>
       <c r="D60">
-        <v>6196.617804184652</v>
+        <v>6106.984586984961</v>
       </c>
       <c r="E60">
-        <v>8792.173999999999</v>
+        <v>9099.927</v>
       </c>
       <c r="F60">
-        <v>17849.674</v>
+        <v>18157.427</v>
       </c>
       <c r="G60">
         <v>3158.8</v>
@@ -6213,37 +6213,37 @@
         <v>1497.6</v>
       </c>
       <c r="M60">
-        <v>3690.181211289201</v>
+        <v>3753.805025276946</v>
       </c>
       <c r="N60">
-        <v>-2192.581211289201</v>
+        <v>-2256.205025276946</v>
       </c>
       <c r="O60">
-        <v>-361.7758998627182</v>
+        <v>-372.2738291706962</v>
       </c>
       <c r="P60">
-        <v>-1830.805311426483</v>
+        <v>-1883.93119610625</v>
       </c>
       <c r="Q60">
-        <v>-1066.905311426483</v>
+        <v>-1120.03119610625</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1037454432670843</v>
+        <v>0.1051587467614035</v>
       </c>
       <c r="T60">
-        <v>1.129464543072309</v>
+        <v>1.157012458757</v>
       </c>
       <c r="U60">
         <v>0.2067366166625341</v>
       </c>
       <c r="V60">
-        <v>0.06696256521063143</v>
+        <v>0.06582760647824784</v>
       </c>
       <c r="W60">
-        <v>0.1928930024878439</v>
+        <v>0.1931276400162284</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.4058337285492813</v>
+        <v>0.3989551907772596</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1570603937817502</v>
+        <v>0.1586697599483755</v>
       </c>
       <c r="C61">
-        <v>-8891.642413015037</v>
+        <v>-9286.472539597846</v>
       </c>
       <c r="D61">
-        <v>6106.984586984961</v>
+        <v>6019.907460402153</v>
       </c>
       <c r="E61">
-        <v>9099.927</v>
+        <v>9407.68</v>
       </c>
       <c r="F61">
-        <v>18157.427</v>
+        <v>18465.18</v>
       </c>
       <c r="G61">
         <v>3158.8</v>
@@ -6295,37 +6295,37 @@
         <v>1497.6</v>
       </c>
       <c r="M61">
-        <v>3753.805025276946</v>
+        <v>3817.428839264691</v>
       </c>
       <c r="N61">
-        <v>-2256.205025276946</v>
+        <v>-2319.828839264691</v>
       </c>
       <c r="O61">
-        <v>-372.2738291706962</v>
+        <v>-382.7717584786741</v>
       </c>
       <c r="P61">
-        <v>-1883.93119610625</v>
+        <v>-1937.057080786017</v>
       </c>
       <c r="Q61">
-        <v>-1120.03119610625</v>
+        <v>-1173.157080786017</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1051587467614035</v>
+        <v>0.1066427154304385</v>
       </c>
       <c r="T61">
-        <v>1.157012458757</v>
+        <v>1.185937770225925</v>
       </c>
       <c r="U61">
         <v>0.2067366166625341</v>
       </c>
       <c r="V61">
-        <v>0.06582760647824784</v>
+        <v>0.06473047970361037</v>
       </c>
       <c r="W61">
-        <v>0.1931276400162284</v>
+        <v>0.1933544562936668</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3989551907772596</v>
+        <v>0.3923059375976385</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1586697599483755</v>
+        <v>0.1602791261150009</v>
       </c>
       <c r="C62">
-        <v>-9286.472539597846</v>
+        <v>-9678.854377376138</v>
       </c>
       <c r="D62">
-        <v>6019.907460402153</v>
+        <v>5935.278622623862</v>
       </c>
       <c r="E62">
-        <v>9407.68</v>
+        <v>9715.433000000001</v>
       </c>
       <c r="F62">
-        <v>18465.18</v>
+        <v>18772.933</v>
       </c>
       <c r="G62">
         <v>3158.8</v>
@@ -6377,37 +6377,37 @@
         <v>1497.6</v>
       </c>
       <c r="M62">
-        <v>3817.428839264691</v>
+        <v>3881.052653252436</v>
       </c>
       <c r="N62">
-        <v>-2319.828839264691</v>
+        <v>-2383.452653252436</v>
       </c>
       <c r="O62">
-        <v>-382.7717584786741</v>
+        <v>-393.269687786652</v>
       </c>
       <c r="P62">
-        <v>-1937.057080786017</v>
+        <v>-1990.182965465784</v>
       </c>
       <c r="Q62">
-        <v>-1173.157080786017</v>
+        <v>-1226.282965465784</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1066427154304385</v>
+        <v>0.10820278505686</v>
       </c>
       <c r="T62">
-        <v>1.185937770225925</v>
+        <v>1.216346431000948</v>
       </c>
       <c r="U62">
         <v>0.2067366166625341</v>
       </c>
       <c r="V62">
-        <v>0.06473047970361037</v>
+        <v>0.06366932429863315</v>
       </c>
       <c r="W62">
-        <v>0.1933544562936668</v>
+        <v>0.193573835971845</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3923059375976385</v>
+        <v>0.3858746927189888</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1602791261150009</v>
+        <v>0.1618884922816262</v>
       </c>
       <c r="C63">
-        <v>-9678.854377376138</v>
+        <v>-10068.88975021954</v>
       </c>
       <c r="D63">
-        <v>5935.278622623862</v>
+        <v>5852.996249780456</v>
       </c>
       <c r="E63">
-        <v>9715.433000000001</v>
+        <v>10023.186</v>
       </c>
       <c r="F63">
-        <v>18772.933</v>
+        <v>19080.686</v>
       </c>
       <c r="G63">
         <v>3158.8</v>
@@ -6459,37 +6459,37 @@
         <v>1497.6</v>
       </c>
       <c r="M63">
-        <v>3881.052653252436</v>
+        <v>3944.676467240181</v>
       </c>
       <c r="N63">
-        <v>-2383.452653252436</v>
+        <v>-2447.076467240181</v>
       </c>
       <c r="O63">
-        <v>-393.269687786652</v>
+        <v>-403.7676170946298</v>
       </c>
       <c r="P63">
-        <v>-1990.182965465784</v>
+        <v>-2043.308850145551</v>
       </c>
       <c r="Q63">
-        <v>-1226.282965465784</v>
+        <v>-1279.408850145551</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.10820278505686</v>
+        <v>0.1098449636109879</v>
       </c>
       <c r="T63">
-        <v>1.216346431000948</v>
+        <v>1.248355547606236</v>
       </c>
       <c r="U63">
         <v>0.2067366166625341</v>
       </c>
       <c r="V63">
-        <v>0.06366932429863315</v>
+        <v>0.06264239971317133</v>
       </c>
       <c r="W63">
-        <v>0.193573835971845</v>
+        <v>0.193786138886211</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3858746927189888</v>
+        <v>0.3796509073525536</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1618884922816262</v>
+        <v>0.1634978584482516</v>
       </c>
       <c r="C64">
-        <v>-10068.88975021954</v>
+        <v>-10456.67491275819</v>
       </c>
       <c r="D64">
-        <v>5852.996249780456</v>
+        <v>5772.964087241804</v>
       </c>
       <c r="E64">
-        <v>10023.186</v>
+        <v>10330.939</v>
       </c>
       <c r="F64">
-        <v>19080.686</v>
+        <v>19388.439</v>
       </c>
       <c r="G64">
         <v>3158.8</v>
@@ -6541,37 +6541,37 @@
         <v>1497.6</v>
       </c>
       <c r="M64">
-        <v>3944.676467240181</v>
+        <v>4008.300281227926</v>
       </c>
       <c r="N64">
-        <v>-2447.076467240181</v>
+        <v>-2510.700281227926</v>
       </c>
       <c r="O64">
-        <v>-403.7676170946298</v>
+        <v>-414.2655464026078</v>
       </c>
       <c r="P64">
-        <v>-2043.308850145551</v>
+        <v>-2096.434734825318</v>
       </c>
       <c r="Q64">
-        <v>-1279.408850145551</v>
+        <v>-1332.534734825318</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1098449636109879</v>
+        <v>0.1115759085734471</v>
       </c>
       <c r="T64">
-        <v>1.248355547606236</v>
+        <v>1.282094886730729</v>
       </c>
       <c r="U64">
         <v>0.2067366166625341</v>
       </c>
       <c r="V64">
-        <v>0.06264239971317133</v>
+        <v>0.06164807590820035</v>
       </c>
       <c r="W64">
-        <v>0.193786138886211</v>
+        <v>0.1939917020255177</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3796509073525536</v>
+        <v>0.3736247024739415</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1634978584482516</v>
+        <v>0.1651072246148769</v>
       </c>
       <c r="C65">
-        <v>-10456.67491275819</v>
+        <v>-10842.30092600731</v>
       </c>
       <c r="D65">
-        <v>5772.964087241804</v>
+        <v>5695.091073992686</v>
       </c>
       <c r="E65">
-        <v>10330.939</v>
+        <v>10638.692</v>
       </c>
       <c r="F65">
-        <v>19388.439</v>
+        <v>19696.192</v>
       </c>
       <c r="G65">
         <v>3158.8</v>
@@ -6623,37 +6623,37 @@
         <v>1497.6</v>
       </c>
       <c r="M65">
-        <v>4008.300281227926</v>
+        <v>4071.924095215671</v>
       </c>
       <c r="N65">
-        <v>-2510.700281227926</v>
+        <v>-2574.324095215671</v>
       </c>
       <c r="O65">
-        <v>-414.2655464026078</v>
+        <v>-424.7634757105857</v>
       </c>
       <c r="P65">
-        <v>-2096.434734825318</v>
+        <v>-2149.560619505085</v>
       </c>
       <c r="Q65">
-        <v>-1332.534734825318</v>
+        <v>-1385.660619505085</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1115759085734471</v>
+        <v>0.1134030171449317</v>
       </c>
       <c r="T65">
-        <v>1.282094886730729</v>
+        <v>1.317708633584361</v>
       </c>
       <c r="U65">
         <v>0.2067366166625341</v>
       </c>
       <c r="V65">
-        <v>0.06164807590820035</v>
+        <v>0.06068482472213473</v>
       </c>
       <c r="W65">
-        <v>0.1939917020255177</v>
+        <v>0.194190841316721</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3736247024739415</v>
+        <v>0.3677868164977862</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1651072246148769</v>
+        <v>0.1667165907815022</v>
       </c>
       <c r="C66">
-        <v>-10842.30092600731</v>
+        <v>-11225.85400299506</v>
       </c>
       <c r="D66">
-        <v>5695.091073992686</v>
+        <v>5619.290997004938</v>
       </c>
       <c r="E66">
-        <v>10638.692</v>
+        <v>10946.445</v>
       </c>
       <c r="F66">
-        <v>19696.192</v>
+        <v>20003.945</v>
       </c>
       <c r="G66">
         <v>3158.8</v>
@@ -6705,37 +6705,37 @@
         <v>1497.6</v>
       </c>
       <c r="M66">
-        <v>4071.924095215671</v>
+        <v>4135.547909203416</v>
       </c>
       <c r="N66">
-        <v>-2574.324095215671</v>
+        <v>-2637.947909203416</v>
       </c>
       <c r="O66">
-        <v>-424.7634757105857</v>
+        <v>-435.2614050185636</v>
       </c>
       <c r="P66">
-        <v>-2149.560619505085</v>
+        <v>-2202.686504184852</v>
       </c>
       <c r="Q66">
-        <v>-1385.660619505085</v>
+        <v>-1438.786504184852</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1134030171449317</v>
+        <v>0.1153345319205012</v>
       </c>
       <c r="T66">
-        <v>1.317708633584361</v>
+        <v>1.355357451686771</v>
       </c>
       <c r="U66">
         <v>0.2067366166625341</v>
       </c>
       <c r="V66">
-        <v>0.06068482472213473</v>
+        <v>0.05975121203410188</v>
       </c>
       <c r="W66">
-        <v>0.194190841316721</v>
+        <v>0.1943838532451182</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3677868164977862</v>
+        <v>0.3621285577824356</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1667165907815022</v>
+        <v>0.1683259569481276</v>
       </c>
       <c r="C67">
-        <v>-11225.85400299506</v>
+        <v>-11607.41582715165</v>
       </c>
       <c r="D67">
-        <v>5619.290997004938</v>
+        <v>5545.482172848348</v>
       </c>
       <c r="E67">
-        <v>10946.445</v>
+        <v>11254.198</v>
       </c>
       <c r="F67">
-        <v>20003.945</v>
+        <v>20311.698</v>
       </c>
       <c r="G67">
         <v>3158.8</v>
@@ -6787,37 +6787,37 @@
         <v>1497.6</v>
       </c>
       <c r="M67">
-        <v>4135.547909203416</v>
+        <v>4199.171723191161</v>
       </c>
       <c r="N67">
-        <v>-2637.947909203416</v>
+        <v>-2701.571723191161</v>
       </c>
       <c r="O67">
-        <v>-435.2614050185636</v>
+        <v>-445.7593343265415</v>
       </c>
       <c r="P67">
-        <v>-2202.686504184852</v>
+        <v>-2255.812388864619</v>
       </c>
       <c r="Q67">
-        <v>-1438.786504184852</v>
+        <v>-1491.912388864619</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1153345319205012</v>
+        <v>0.1173796652122807</v>
       </c>
       <c r="T67">
-        <v>1.355357451686771</v>
+        <v>1.395220906148147</v>
       </c>
       <c r="U67">
         <v>0.2067366166625341</v>
       </c>
       <c r="V67">
-        <v>0.05975121203410188</v>
+        <v>0.05884589063964579</v>
       </c>
       <c r="W67">
-        <v>0.1943838532451182</v>
+        <v>0.1945710163272003</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3621285577824356</v>
+        <v>0.3566417614523987</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1683259569481276</v>
+        <v>0.169935323114753</v>
       </c>
       <c r="C68">
-        <v>-11607.41582715165</v>
+        <v>-11987.06384593173</v>
       </c>
       <c r="D68">
-        <v>5545.482172848348</v>
+        <v>5473.587154068271</v>
       </c>
       <c r="E68">
-        <v>11254.198</v>
+        <v>11561.951</v>
       </c>
       <c r="F68">
-        <v>20311.698</v>
+        <v>20619.451</v>
       </c>
       <c r="G68">
         <v>3158.8</v>
@@ -6869,37 +6869,37 @@
         <v>1497.6</v>
       </c>
       <c r="M68">
-        <v>4199.171723191161</v>
+        <v>4262.795537178906</v>
       </c>
       <c r="N68">
-        <v>-2701.571723191161</v>
+        <v>-2765.195537178906</v>
       </c>
       <c r="O68">
-        <v>-445.7593343265415</v>
+        <v>-456.2572636345195</v>
       </c>
       <c r="P68">
-        <v>-2255.812388864619</v>
+        <v>-2308.938273544386</v>
       </c>
       <c r="Q68">
-        <v>-1491.912388864619</v>
+        <v>-1545.038273544386</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1173796652122807</v>
+        <v>0.1195487459762892</v>
       </c>
       <c r="T68">
-        <v>1.395220906148147</v>
+        <v>1.437500327546576</v>
       </c>
       <c r="U68">
         <v>0.2067366166625341</v>
       </c>
       <c r="V68">
-        <v>0.05884589063964579</v>
+        <v>0.05796759376442719</v>
       </c>
       <c r="W68">
-        <v>0.1945710163272003</v>
+        <v>0.1947525924516082</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3566417614523987</v>
+        <v>0.3513187500874375</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.169935323114753</v>
+        <v>0.1715446892813783</v>
       </c>
       <c r="C69">
-        <v>-11987.06384593173</v>
+        <v>-12364.87154188888</v>
       </c>
       <c r="D69">
-        <v>5473.587154068271</v>
+        <v>5403.532458111125</v>
       </c>
       <c r="E69">
-        <v>11561.951</v>
+        <v>11869.704</v>
       </c>
       <c r="F69">
-        <v>20619.451</v>
+        <v>20927.204</v>
       </c>
       <c r="G69">
         <v>3158.8</v>
@@ -6951,37 +6951,37 @@
         <v>1497.6</v>
       </c>
       <c r="M69">
-        <v>4262.795537178906</v>
+        <v>4326.419351166651</v>
       </c>
       <c r="N69">
-        <v>-2765.195537178906</v>
+        <v>-2828.819351166651</v>
       </c>
       <c r="O69">
-        <v>-456.2572636345195</v>
+        <v>-466.7551929424974</v>
       </c>
       <c r="P69">
-        <v>-2308.938273544386</v>
+        <v>-2362.064158224153</v>
       </c>
       <c r="Q69">
-        <v>-1545.038273544386</v>
+        <v>-1598.164158224153</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1195487459762892</v>
+        <v>0.1218533942880482</v>
       </c>
       <c r="T69">
-        <v>1.437500327546576</v>
+        <v>1.482422212782406</v>
       </c>
       <c r="U69">
         <v>0.2067366166625341</v>
       </c>
       <c r="V69">
-        <v>0.05796759376442719</v>
+        <v>0.05711512915024444</v>
       </c>
       <c r="W69">
-        <v>0.1947525924516082</v>
+        <v>0.1949288281017689</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3513187500874375</v>
+        <v>0.3461522978802692</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1715446892813783</v>
+        <v>0.1731540554480036</v>
       </c>
       <c r="C70">
-        <v>-12364.87154188888</v>
+        <v>-12740.90868319678</v>
       </c>
       <c r="D70">
-        <v>5403.532458111125</v>
+        <v>5335.248316803225</v>
       </c>
       <c r="E70">
-        <v>11869.704</v>
+        <v>12177.457</v>
       </c>
       <c r="F70">
-        <v>20927.204</v>
+        <v>21234.957</v>
       </c>
       <c r="G70">
         <v>3158.8</v>
@@ -7033,37 +7033,37 @@
         <v>1497.6</v>
       </c>
       <c r="M70">
-        <v>4326.419351166651</v>
+        <v>4390.043165154396</v>
       </c>
       <c r="N70">
-        <v>-2828.819351166651</v>
+        <v>-2892.443165154396</v>
       </c>
       <c r="O70">
-        <v>-466.7551929424974</v>
+        <v>-477.2531222504754</v>
       </c>
       <c r="P70">
-        <v>-2362.064158224153</v>
+        <v>-2415.190042903921</v>
       </c>
       <c r="Q70">
-        <v>-1598.164158224153</v>
+        <v>-1651.29004290392</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1218533942880482</v>
+        <v>0.1243067295876627</v>
       </c>
       <c r="T70">
-        <v>1.482422212782406</v>
+        <v>1.530242284162484</v>
       </c>
       <c r="U70">
         <v>0.2067366166625341</v>
       </c>
       <c r="V70">
-        <v>0.05711512915024444</v>
+        <v>0.05628737365531335</v>
       </c>
       <c r="W70">
-        <v>0.1949288281017689</v>
+        <v>0.1950999554722148</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3461522978802692</v>
+        <v>0.34113559791099</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1731540554480036</v>
+        <v>0.174763421614629</v>
       </c>
       <c r="C71">
-        <v>-12740.90868319678</v>
+        <v>-13115.24155541253</v>
       </c>
       <c r="D71">
-        <v>5335.248316803225</v>
+        <v>5268.668444587474</v>
       </c>
       <c r="E71">
-        <v>12177.457</v>
+        <v>12485.21</v>
       </c>
       <c r="F71">
-        <v>21234.957</v>
+        <v>21542.71</v>
       </c>
       <c r="G71">
         <v>3158.8</v>
@@ -7115,37 +7115,37 @@
         <v>1497.6</v>
       </c>
       <c r="M71">
-        <v>4390.043165154396</v>
+        <v>4453.66697914214</v>
       </c>
       <c r="N71">
-        <v>-2892.443165154396</v>
+        <v>-2956.06697914214</v>
       </c>
       <c r="O71">
-        <v>-477.2531222504754</v>
+        <v>-487.7510515584531</v>
       </c>
       <c r="P71">
-        <v>-2415.190042903921</v>
+        <v>-2468.315927583687</v>
       </c>
       <c r="Q71">
-        <v>-1651.29004290392</v>
+        <v>-1704.415927583687</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1243067295876627</v>
+        <v>0.1269236205739181</v>
       </c>
       <c r="T71">
-        <v>1.530242284162484</v>
+        <v>1.581250360301233</v>
       </c>
       <c r="U71">
         <v>0.2067366166625341</v>
       </c>
       <c r="V71">
-        <v>0.05628737365531335</v>
+        <v>0.05548326831738031</v>
       </c>
       <c r="W71">
-        <v>0.1950999554722148</v>
+        <v>0.1952661934892193</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.34113559791099</v>
+        <v>0.3362622322265474</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.174763421614629</v>
+        <v>0.1763727877812543</v>
       </c>
       <c r="C72">
-        <v>-13115.24155541253</v>
+        <v>-13487.93317610041</v>
       </c>
       <c r="D72">
-        <v>5268.668444587474</v>
+        <v>5203.729823899596</v>
       </c>
       <c r="E72">
-        <v>12485.21</v>
+        <v>12792.963</v>
       </c>
       <c r="F72">
-        <v>21542.71</v>
+        <v>21850.463</v>
       </c>
       <c r="G72">
         <v>3158.8</v>
@@ -7197,37 +7197,37 @@
         <v>1497.6</v>
       </c>
       <c r="M72">
-        <v>4453.66697914214</v>
+        <v>4517.290793129885</v>
       </c>
       <c r="N72">
-        <v>-2956.06697914214</v>
+        <v>-3019.690793129885</v>
       </c>
       <c r="O72">
-        <v>-487.7510515584531</v>
+        <v>-498.2489808664311</v>
       </c>
       <c r="P72">
-        <v>-2468.315927583687</v>
+        <v>-2521.441812263454</v>
       </c>
       <c r="Q72">
-        <v>-1704.415927583687</v>
+        <v>-1757.541812263454</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1269236205739181</v>
+        <v>0.1297209868006049</v>
       </c>
       <c r="T72">
-        <v>1.581250360301233</v>
+        <v>1.63577623479438</v>
       </c>
       <c r="U72">
         <v>0.2067366166625341</v>
       </c>
       <c r="V72">
-        <v>0.05548326831738031</v>
+        <v>0.05470181383403693</v>
       </c>
       <c r="W72">
-        <v>0.1952661934892193</v>
+        <v>0.1954277487451815</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3362622322265474</v>
+        <v>0.3315261444487086</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1763727877812543</v>
+        <v>0.1779821539478796</v>
       </c>
       <c r="C73">
-        <v>-13487.9331761004</v>
+        <v>-13859.04349377693</v>
       </c>
       <c r="D73">
-        <v>5203.729823899596</v>
+        <v>5140.37250622307</v>
       </c>
       <c r="E73">
-        <v>12792.963</v>
+        <v>13100.716</v>
       </c>
       <c r="F73">
-        <v>21850.463</v>
+        <v>22158.216</v>
       </c>
       <c r="G73">
         <v>3158.8</v>
@@ -7279,37 +7279,37 @@
         <v>1497.6</v>
       </c>
       <c r="M73">
-        <v>4517.290793129885</v>
+        <v>4580.91460711763</v>
       </c>
       <c r="N73">
-        <v>-3019.690793129885</v>
+        <v>-3083.31460711763</v>
       </c>
       <c r="O73">
-        <v>-498.2489808664311</v>
+        <v>-508.746910174409</v>
       </c>
       <c r="P73">
-        <v>-2521.441812263454</v>
+        <v>-2574.567696943221</v>
       </c>
       <c r="Q73">
-        <v>-1757.541812263454</v>
+        <v>-1810.667696943221</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1297209868006049</v>
+        <v>0.1327181649006265</v>
       </c>
       <c r="T73">
-        <v>1.635776234794379</v>
+        <v>1.694196814608464</v>
       </c>
       <c r="U73">
         <v>0.2067366166625341</v>
       </c>
       <c r="V73">
-        <v>0.05470181383403693</v>
+        <v>0.0539420664196753</v>
       </c>
       <c r="W73">
-        <v>0.1954277487451815</v>
+        <v>0.1955848163551447</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3315261444487086</v>
+        <v>0.3269216146646988</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1779821539478796</v>
+        <v>0.179591520114505</v>
       </c>
       <c r="C74">
-        <v>-13859.04349377693</v>
+        <v>-14228.62957249736</v>
       </c>
       <c r="D74">
-        <v>5140.37250622307</v>
+        <v>5078.539427502638</v>
       </c>
       <c r="E74">
-        <v>13100.716</v>
+        <v>13408.469</v>
       </c>
       <c r="F74">
-        <v>22158.216</v>
+        <v>22465.969</v>
       </c>
       <c r="G74">
         <v>3158.8</v>
@@ -7361,37 +7361,37 @@
         <v>1497.6</v>
       </c>
       <c r="M74">
-        <v>4580.91460711763</v>
+        <v>4644.538421105374</v>
       </c>
       <c r="N74">
-        <v>-3083.31460711763</v>
+        <v>-3146.938421105374</v>
       </c>
       <c r="O74">
-        <v>-508.746910174409</v>
+        <v>-519.2448394823867</v>
       </c>
       <c r="P74">
-        <v>-2574.567696943221</v>
+        <v>-2627.693581622987</v>
       </c>
       <c r="Q74">
-        <v>-1810.667696943221</v>
+        <v>-1863.793581622987</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1327181649006265</v>
+        <v>0.1359373561932423</v>
       </c>
       <c r="T74">
-        <v>1.694196814608464</v>
+        <v>1.756944844779148</v>
       </c>
       <c r="U74">
         <v>0.2067366166625341</v>
       </c>
       <c r="V74">
-        <v>0.0539420664196753</v>
+        <v>0.05320313400296742</v>
       </c>
       <c r="W74">
-        <v>0.1955848163551447</v>
+        <v>0.1957375807429172</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3269216146646988</v>
+        <v>0.3224432363816208</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.179591520114505</v>
+        <v>0.1812008862811303</v>
       </c>
       <c r="C75">
-        <v>-14228.62957249736</v>
+        <v>-14596.74576327829</v>
       </c>
       <c r="D75">
-        <v>5078.539427502638</v>
+        <v>5018.176236721704</v>
       </c>
       <c r="E75">
-        <v>13408.469</v>
+        <v>13716.222</v>
       </c>
       <c r="F75">
-        <v>22465.969</v>
+        <v>22773.722</v>
       </c>
       <c r="G75">
         <v>3158.8</v>
@@ -7443,37 +7443,37 @@
         <v>1497.6</v>
       </c>
       <c r="M75">
-        <v>4644.538421105374</v>
+        <v>4708.162235093119</v>
       </c>
       <c r="N75">
-        <v>-3146.938421105374</v>
+        <v>-3210.562235093119</v>
       </c>
       <c r="O75">
-        <v>-519.2448394823867</v>
+        <v>-529.7427687903647</v>
       </c>
       <c r="P75">
-        <v>-2627.693581622987</v>
+        <v>-2680.819466302755</v>
       </c>
       <c r="Q75">
-        <v>-1863.793581622987</v>
+        <v>-1916.919466302755</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1359373561932423</v>
+        <v>0.1394041775852901</v>
       </c>
       <c r="T75">
-        <v>1.756944844779148</v>
+        <v>1.824519646501422</v>
       </c>
       <c r="U75">
         <v>0.2067366166625341</v>
       </c>
       <c r="V75">
-        <v>0.05320313400296742</v>
+        <v>0.05248417273265706</v>
       </c>
       <c r="W75">
-        <v>0.1957375807429172</v>
+        <v>0.1958862163634525</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3224432363816208</v>
+        <v>0.3180858953494367</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1812008862811303</v>
+        <v>0.1828102524477556</v>
       </c>
       <c r="C76">
-        <v>-14596.74576327829</v>
+        <v>-14963.44386343876</v>
       </c>
       <c r="D76">
-        <v>5018.176236721704</v>
+        <v>4959.23113656124</v>
       </c>
       <c r="E76">
-        <v>13716.222</v>
+        <v>14023.975</v>
       </c>
       <c r="F76">
-        <v>22773.722</v>
+        <v>23081.475</v>
       </c>
       <c r="G76">
         <v>3158.8</v>
@@ -7525,37 +7525,37 @@
         <v>1497.6</v>
       </c>
       <c r="M76">
-        <v>4708.162235093119</v>
+        <v>4771.786049080863</v>
       </c>
       <c r="N76">
-        <v>-3210.562235093119</v>
+        <v>-3274.186049080864</v>
       </c>
       <c r="O76">
-        <v>-529.7427687903647</v>
+        <v>-540.2406980983425</v>
       </c>
       <c r="P76">
-        <v>-2680.819466302755</v>
+        <v>-2733.945350982521</v>
       </c>
       <c r="Q76">
-        <v>-1916.919466302755</v>
+        <v>-1970.045350982521</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1394041775852901</v>
+        <v>0.1431483446887017</v>
       </c>
       <c r="T76">
-        <v>1.824519646501422</v>
+        <v>1.897500432361479</v>
       </c>
       <c r="U76">
         <v>0.2067366166625341</v>
       </c>
       <c r="V76">
-        <v>0.05248417273265706</v>
+        <v>0.0517843837628883</v>
       </c>
       <c r="W76">
-        <v>0.1958862163634525</v>
+        <v>0.1960308883674403</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3180858953494367</v>
+        <v>0.313844750078111</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1828102524477556</v>
+        <v>0.184419618614381</v>
       </c>
       <c r="C77">
-        <v>-14963.44386343876</v>
+        <v>-15328.77326484164</v>
       </c>
       <c r="D77">
-        <v>4959.23113656124</v>
+        <v>4901.654735158355</v>
       </c>
       <c r="E77">
-        <v>14023.975</v>
+        <v>14331.728</v>
       </c>
       <c r="F77">
-        <v>23081.475</v>
+        <v>23389.228</v>
       </c>
       <c r="G77">
         <v>3158.8</v>
@@ -7607,37 +7607,37 @@
         <v>1497.6</v>
       </c>
       <c r="M77">
-        <v>4771.786049080863</v>
+        <v>4835.409863068609</v>
       </c>
       <c r="N77">
-        <v>-3274.186049080864</v>
+        <v>-3337.809863068609</v>
       </c>
       <c r="O77">
-        <v>-540.2406980983425</v>
+        <v>-550.7386274063205</v>
       </c>
       <c r="P77">
-        <v>-2733.945350982521</v>
+        <v>-2787.071235662288</v>
       </c>
       <c r="Q77">
-        <v>-1970.045350982521</v>
+        <v>-2023.171235662288</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1431483446887017</v>
+        <v>0.1472045257173976</v>
       </c>
       <c r="T77">
-        <v>1.897500432361479</v>
+        <v>1.976562950376541</v>
       </c>
       <c r="U77">
         <v>0.2067366166625341</v>
       </c>
       <c r="V77">
-        <v>0.0517843837628883</v>
+        <v>0.05110301029232398</v>
       </c>
       <c r="W77">
-        <v>0.1960308883674403</v>
+        <v>0.1961717532134284</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.313844750078111</v>
+        <v>0.3097152138928726</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.184419618614381</v>
+        <v>0.1860289847810063</v>
       </c>
       <c r="C78">
-        <v>-15328.77326484164</v>
+        <v>-15692.78109192723</v>
       </c>
       <c r="D78">
-        <v>4901.654735158355</v>
+        <v>4845.399908072769</v>
       </c>
       <c r="E78">
-        <v>14331.728</v>
+        <v>14639.481</v>
       </c>
       <c r="F78">
-        <v>23389.228</v>
+        <v>23696.981</v>
       </c>
       <c r="G78">
         <v>3158.8</v>
@@ -7689,37 +7689,37 @@
         <v>1497.6</v>
       </c>
       <c r="M78">
-        <v>4835.409863068609</v>
+        <v>4899.033677056354</v>
       </c>
       <c r="N78">
-        <v>-3337.809863068609</v>
+        <v>-3401.433677056354</v>
       </c>
       <c r="O78">
-        <v>-550.7386274063205</v>
+        <v>-561.2365567142983</v>
       </c>
       <c r="P78">
-        <v>-2787.071235662288</v>
+        <v>-2840.197120342055</v>
       </c>
       <c r="Q78">
-        <v>-2023.171235662288</v>
+        <v>-2076.297120342055</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1472045257173976</v>
+        <v>0.1516134181398931</v>
       </c>
       <c r="T78">
-        <v>1.976562950376541</v>
+        <v>2.06250046995813</v>
       </c>
       <c r="U78">
         <v>0.2067366166625341</v>
       </c>
       <c r="V78">
-        <v>0.05110301029232398</v>
+        <v>0.05043933483398211</v>
       </c>
       <c r="W78">
-        <v>0.1961717532134284</v>
+        <v>0.1963089592322479</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3097152138928726</v>
+        <v>0.3056929383877703</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1860289847810063</v>
+        <v>0.1876383509476317</v>
       </c>
       <c r="C79">
-        <v>-15692.78109192723</v>
+        <v>-16055.51233034951</v>
       </c>
       <c r="D79">
-        <v>4845.399908072769</v>
+        <v>4790.42166965049</v>
       </c>
       <c r="E79">
-        <v>14639.481</v>
+        <v>14947.234</v>
       </c>
       <c r="F79">
-        <v>23696.981</v>
+        <v>24004.734</v>
       </c>
       <c r="G79">
         <v>3158.8</v>
@@ -7771,37 +7771,37 @@
         <v>1497.6</v>
       </c>
       <c r="M79">
-        <v>4899.033677056354</v>
+        <v>4962.657491044099</v>
       </c>
       <c r="N79">
-        <v>-3401.433677056354</v>
+        <v>-3465.057491044099</v>
       </c>
       <c r="O79">
-        <v>-561.2365567142983</v>
+        <v>-571.7344860222763</v>
       </c>
       <c r="P79">
-        <v>-2840.197120342055</v>
+        <v>-2893.323005021823</v>
       </c>
       <c r="Q79">
-        <v>-2076.297120342055</v>
+        <v>-2129.423005021823</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1516134181398931</v>
+        <v>0.1564231189644338</v>
       </c>
       <c r="T79">
-        <v>2.06250046995813</v>
+        <v>2.156250491319863</v>
       </c>
       <c r="U79">
         <v>0.2067366166625341</v>
       </c>
       <c r="V79">
-        <v>0.05043933483398211</v>
+        <v>0.0497926766950849</v>
       </c>
       <c r="W79">
-        <v>0.1963089592322479</v>
+        <v>0.1964426471480208</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3056929383877703</v>
+        <v>0.3017737981520296</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1876383509476317</v>
+        <v>0.189247717114257</v>
       </c>
       <c r="C80">
-        <v>-16055.51233034951</v>
+        <v>-16417.00994695337</v>
       </c>
       <c r="D80">
-        <v>4790.42166965049</v>
+        <v>4736.677053046633</v>
       </c>
       <c r="E80">
-        <v>14947.234</v>
+        <v>15254.987</v>
       </c>
       <c r="F80">
-        <v>24004.734</v>
+        <v>24312.487</v>
       </c>
       <c r="G80">
         <v>3158.8</v>
@@ -7853,37 +7853,37 @@
         <v>1497.6</v>
       </c>
       <c r="M80">
-        <v>4962.657491044099</v>
+        <v>5026.281305031844</v>
       </c>
       <c r="N80">
-        <v>-3465.057491044099</v>
+        <v>-3528.681305031844</v>
       </c>
       <c r="O80">
-        <v>-571.7344860222763</v>
+        <v>-582.2324153302543</v>
       </c>
       <c r="P80">
-        <v>-2893.323005021823</v>
+        <v>-2946.448889701589</v>
       </c>
       <c r="Q80">
-        <v>-2129.423005021823</v>
+        <v>-2182.548889701589</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1564231189644338</v>
+        <v>0.1616908865341687</v>
       </c>
       <c r="T80">
-        <v>2.156250491319863</v>
+        <v>2.258929086144619</v>
       </c>
       <c r="U80">
         <v>0.2067366166625341</v>
       </c>
       <c r="V80">
-        <v>0.0497926766950849</v>
+        <v>0.04916238964831167</v>
       </c>
       <c r="W80">
-        <v>0.1964426471480208</v>
+        <v>0.1965729505595969</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3017737981520296</v>
+        <v>0.2979538766564344</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.189247717114257</v>
+        <v>0.1908570832808824</v>
       </c>
       <c r="C81">
-        <v>-16417.00994695337</v>
+        <v>-16777.31500176508</v>
       </c>
       <c r="D81">
-        <v>4736.677053046633</v>
+        <v>4684.12499823492</v>
       </c>
       <c r="E81">
-        <v>15254.987</v>
+        <v>15562.74</v>
       </c>
       <c r="F81">
-        <v>24312.487</v>
+        <v>24620.24</v>
       </c>
       <c r="G81">
         <v>3158.8</v>
@@ -7935,37 +7935,37 @@
         <v>1497.6</v>
       </c>
       <c r="M81">
-        <v>5026.281305031844</v>
+        <v>5089.905119019589</v>
       </c>
       <c r="N81">
-        <v>-3528.681305031844</v>
+        <v>-3592.305119019589</v>
       </c>
       <c r="O81">
-        <v>-582.2324153302543</v>
+        <v>-592.7303446382322</v>
       </c>
       <c r="P81">
-        <v>-2946.448889701589</v>
+        <v>-2999.574774381357</v>
       </c>
       <c r="Q81">
-        <v>-2182.548889701589</v>
+        <v>-2235.674774381357</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1616908865341687</v>
+        <v>0.1674854308608771</v>
       </c>
       <c r="T81">
-        <v>2.258929086144619</v>
+        <v>2.37187554045185</v>
       </c>
       <c r="U81">
         <v>0.2067366166625341</v>
       </c>
       <c r="V81">
-        <v>0.04916238964831167</v>
+        <v>0.04854785977770777</v>
       </c>
       <c r="W81">
-        <v>0.1965729505595969</v>
+        <v>0.1966999963858836</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2979538766564344</v>
+        <v>0.2942294531982289</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1908570832808824</v>
+        <v>0.1924664494475077</v>
       </c>
       <c r="C82">
-        <v>-16777.31500176508</v>
+        <v>-17136.46675260961</v>
       </c>
       <c r="D82">
-        <v>4684.12499823492</v>
+        <v>4632.726247390397</v>
       </c>
       <c r="E82">
-        <v>15562.74</v>
+        <v>15870.493</v>
       </c>
       <c r="F82">
-        <v>24620.24</v>
+        <v>24927.993</v>
       </c>
       <c r="G82">
         <v>3158.8</v>
@@ -8017,37 +8017,37 @@
         <v>1497.6</v>
       </c>
       <c r="M82">
-        <v>5089.905119019589</v>
+        <v>5153.528933007334</v>
       </c>
       <c r="N82">
-        <v>-3592.305119019589</v>
+        <v>-3655.928933007334</v>
       </c>
       <c r="O82">
-        <v>-592.7303446382322</v>
+        <v>-603.2282739462102</v>
       </c>
       <c r="P82">
-        <v>-2999.574774381357</v>
+        <v>-3052.700659061124</v>
       </c>
       <c r="Q82">
-        <v>-2235.674774381357</v>
+        <v>-2288.800659061123</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1674854308608771</v>
+        <v>0.1738899272219759</v>
       </c>
       <c r="T82">
-        <v>2.37187554045185</v>
+        <v>2.496711095212474</v>
       </c>
       <c r="U82">
         <v>0.2067366166625341</v>
       </c>
       <c r="V82">
-        <v>0.04854785977770777</v>
+        <v>0.04794850348415583</v>
       </c>
       <c r="W82">
-        <v>0.1966999963858836</v>
+        <v>0.196823905278188</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2942294531982289</v>
+        <v>0.2905969908130656</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1924664494475077</v>
+        <v>0.1940758156141331</v>
       </c>
       <c r="C83">
-        <v>-17136.46675260961</v>
+        <v>-17494.50275291486</v>
       </c>
       <c r="D83">
-        <v>4632.726247390397</v>
+        <v>4582.443247085143</v>
       </c>
       <c r="E83">
-        <v>15870.493</v>
+        <v>16178.246</v>
       </c>
       <c r="F83">
-        <v>24927.993</v>
+        <v>25235.746</v>
       </c>
       <c r="G83">
         <v>3158.8</v>
@@ -8099,37 +8099,37 @@
         <v>1497.6</v>
       </c>
       <c r="M83">
-        <v>5153.528933007334</v>
+        <v>5217.152746995079</v>
       </c>
       <c r="N83">
-        <v>-3655.928933007334</v>
+        <v>-3719.552746995079</v>
       </c>
       <c r="O83">
-        <v>-603.2282739462102</v>
+        <v>-613.726203254188</v>
       </c>
       <c r="P83">
-        <v>-3052.700659061124</v>
+        <v>-3105.826543740891</v>
       </c>
       <c r="Q83">
-        <v>-2288.800659061123</v>
+        <v>-2341.926543740891</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1738899272219759</v>
+        <v>0.1810060342898635</v>
       </c>
       <c r="T83">
-        <v>2.496711095212474</v>
+        <v>2.635417267168723</v>
       </c>
       <c r="U83">
         <v>0.2067366166625341</v>
       </c>
       <c r="V83">
-        <v>0.04794850348415583</v>
+        <v>0.04736376563678807</v>
       </c>
       <c r="W83">
-        <v>0.196823905278188</v>
+        <v>0.1969447920023873</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2905969908130656</v>
+        <v>0.2870531250714429</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1940758156141331</v>
+        <v>0.1956851817807584</v>
       </c>
       <c r="C84">
-        <v>-17494.50275291486</v>
+        <v>-17851.45894321506</v>
       </c>
       <c r="D84">
-        <v>4582.443247085143</v>
+        <v>4533.240056784934</v>
       </c>
       <c r="E84">
-        <v>16178.246</v>
+        <v>16485.999</v>
       </c>
       <c r="F84">
-        <v>25235.746</v>
+        <v>25543.499</v>
       </c>
       <c r="G84">
         <v>3158.8</v>
@@ -8181,37 +8181,37 @@
         <v>1497.6</v>
       </c>
       <c r="M84">
-        <v>5217.152746995079</v>
+        <v>5280.776560982823</v>
       </c>
       <c r="N84">
-        <v>-3719.552746995079</v>
+        <v>-3783.176560982823</v>
       </c>
       <c r="O84">
-        <v>-613.726203254188</v>
+        <v>-624.2241325621658</v>
       </c>
       <c r="P84">
-        <v>-3105.826543740891</v>
+        <v>-3158.952428420657</v>
       </c>
       <c r="Q84">
-        <v>-2341.926543740891</v>
+        <v>-2395.052428420657</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1810060342898635</v>
+        <v>0.1889593304245614</v>
       </c>
       <c r="T84">
-        <v>2.635417267168723</v>
+        <v>2.790441812296295</v>
       </c>
       <c r="U84">
         <v>0.2067366166625341</v>
       </c>
       <c r="V84">
-        <v>0.04736376563678807</v>
+        <v>0.04679311785803159</v>
       </c>
       <c r="W84">
-        <v>0.1969447920023873</v>
+        <v>0.1970627657934734</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2870531250714429</v>
+        <v>0.28359465368504</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1956851817807584</v>
+        <v>0.1972945479473837</v>
       </c>
       <c r="C85">
-        <v>-17851.45894321506</v>
+        <v>-18207.3697368217</v>
       </c>
       <c r="D85">
-        <v>4533.240056784934</v>
+        <v>4485.0822631783</v>
       </c>
       <c r="E85">
-        <v>16485.999</v>
+        <v>16793.752</v>
       </c>
       <c r="F85">
-        <v>25543.499</v>
+        <v>25851.252</v>
       </c>
       <c r="G85">
         <v>3158.8</v>
@@ -8263,37 +8263,37 @@
         <v>1497.6</v>
       </c>
       <c r="M85">
-        <v>5280.776560982823</v>
+        <v>5344.400374970568</v>
       </c>
       <c r="N85">
-        <v>-3783.176560982823</v>
+        <v>-3846.800374970568</v>
       </c>
       <c r="O85">
-        <v>-624.2241325621658</v>
+        <v>-634.7220618701438</v>
       </c>
       <c r="P85">
-        <v>-3158.952428420657</v>
+        <v>-3212.078313100425</v>
       </c>
       <c r="Q85">
-        <v>-2395.052428420657</v>
+        <v>-2448.178313100424</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1889593304245614</v>
+        <v>0.1979067885760965</v>
       </c>
       <c r="T85">
-        <v>2.790441812296295</v>
+        <v>2.964844425564813</v>
       </c>
       <c r="U85">
         <v>0.2067366166625341</v>
       </c>
       <c r="V85">
-        <v>0.04679311785803159</v>
+        <v>0.04623605693115026</v>
       </c>
       <c r="W85">
-        <v>0.1970627657934734</v>
+        <v>0.1971779306847718</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.28359465368504</v>
+        <v>0.2802185268554561</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1972945479473837</v>
+        <v>0.1989039141140091</v>
       </c>
       <c r="C86">
-        <v>-18207.3697368217</v>
+        <v>-18562.26810009121</v>
       </c>
       <c r="D86">
-        <v>4485.0822631783</v>
+        <v>4437.936899908784</v>
       </c>
       <c r="E86">
-        <v>16793.752</v>
+        <v>17101.505</v>
       </c>
       <c r="F86">
-        <v>25851.252</v>
+        <v>26159.005</v>
       </c>
       <c r="G86">
         <v>3158.8</v>
@@ -8345,37 +8345,37 @@
         <v>1497.6</v>
       </c>
       <c r="M86">
-        <v>5344.400374970567</v>
+        <v>5408.024188958312</v>
       </c>
       <c r="N86">
-        <v>-3846.800374970567</v>
+        <v>-3910.424188958312</v>
       </c>
       <c r="O86">
-        <v>-634.7220618701436</v>
+        <v>-645.2199911781215</v>
       </c>
       <c r="P86">
-        <v>-3212.078313100424</v>
+        <v>-3265.204197780191</v>
       </c>
       <c r="Q86">
-        <v>-2448.178313100424</v>
+        <v>-2501.304197780191</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1979067885760963</v>
+        <v>0.2080472411478361</v>
       </c>
       <c r="T86">
-        <v>2.964844425564811</v>
+        <v>3.162500720602466</v>
       </c>
       <c r="U86">
         <v>0.2067366166625341</v>
       </c>
       <c r="V86">
-        <v>0.04623605693115027</v>
+        <v>0.04569210332019556</v>
       </c>
       <c r="W86">
-        <v>0.1971779306847718</v>
+        <v>0.1972903858139219</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2802185268554562</v>
+        <v>0.2769218383042155</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1989039141140091</v>
+        <v>0.2005132802806344</v>
       </c>
       <c r="C87">
-        <v>-18562.26810009121</v>
+        <v>-18916.18562768301</v>
       </c>
       <c r="D87">
-        <v>4437.936899908784</v>
+        <v>4391.772372316989</v>
       </c>
       <c r="E87">
-        <v>17101.505</v>
+        <v>17409.258</v>
       </c>
       <c r="F87">
-        <v>26159.005</v>
+        <v>26466.758</v>
       </c>
       <c r="G87">
         <v>3158.8</v>
@@ -8427,37 +8427,37 @@
         <v>1497.6</v>
       </c>
       <c r="M87">
-        <v>5408.024188958312</v>
+        <v>5471.648002946057</v>
       </c>
       <c r="N87">
-        <v>-3910.424188958312</v>
+        <v>-3974.048002946057</v>
       </c>
       <c r="O87">
-        <v>-645.2199911781215</v>
+        <v>-655.7179204860995</v>
       </c>
       <c r="P87">
-        <v>-3265.204197780191</v>
+        <v>-3318.330082459958</v>
       </c>
       <c r="Q87">
-        <v>-2501.304197780191</v>
+        <v>-2554.430082459958</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2080472411478361</v>
+        <v>0.219636329801253</v>
       </c>
       <c r="T87">
-        <v>3.162500720602466</v>
+        <v>3.388393629216928</v>
       </c>
       <c r="U87">
         <v>0.2067366166625341</v>
       </c>
       <c r="V87">
-        <v>0.04569210332019556</v>
+        <v>0.04516079979321654</v>
       </c>
       <c r="W87">
-        <v>0.1972903858139219</v>
+        <v>0.1974002257075105</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2769218383042155</v>
+        <v>0.2737018169285851</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2005132802806344</v>
+        <v>0.2021226464472597</v>
       </c>
       <c r="C88">
-        <v>-18916.18562768301</v>
+        <v>-19269.15261316854</v>
       </c>
       <c r="D88">
-        <v>4391.772372316989</v>
+        <v>4346.558386831461</v>
       </c>
       <c r="E88">
-        <v>17409.258</v>
+        <v>17717.011</v>
       </c>
       <c r="F88">
-        <v>26466.758</v>
+        <v>26774.511</v>
       </c>
       <c r="G88">
         <v>3158.8</v>
@@ -8509,37 +8509,37 @@
         <v>1497.6</v>
       </c>
       <c r="M88">
-        <v>5471.648002946057</v>
+        <v>5535.271816933802</v>
       </c>
       <c r="N88">
-        <v>-3974.048002946057</v>
+        <v>-4037.671816933802</v>
       </c>
       <c r="O88">
-        <v>-655.7179204860995</v>
+        <v>-666.2158497940774</v>
       </c>
       <c r="P88">
-        <v>-3318.330082459958</v>
+        <v>-3371.455967139725</v>
       </c>
       <c r="Q88">
-        <v>-2554.430082459958</v>
+        <v>-2607.555967139725</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.219636329801253</v>
+        <v>0.2330083551705801</v>
       </c>
       <c r="T88">
-        <v>3.388393629216928</v>
+        <v>3.649039293002845</v>
       </c>
       <c r="U88">
         <v>0.2067366166625341</v>
       </c>
       <c r="V88">
-        <v>0.04516079979321654</v>
+        <v>0.04464171014042095</v>
       </c>
       <c r="W88">
-        <v>0.1974002257075105</v>
+        <v>0.1975075405460739</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2737018169285851</v>
+        <v>0.2705558190328542</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2021226464472597</v>
+        <v>0.2037320126138851</v>
       </c>
       <c r="C89">
-        <v>-19269.15261316854</v>
+        <v>-19621.19811532344</v>
       </c>
       <c r="D89">
-        <v>4346.558386831461</v>
+        <v>4302.265884676557</v>
       </c>
       <c r="E89">
-        <v>17717.011</v>
+        <v>18024.764</v>
       </c>
       <c r="F89">
-        <v>26774.511</v>
+        <v>27082.264</v>
       </c>
       <c r="G89">
         <v>3158.8</v>
@@ -8591,37 +8591,37 @@
         <v>1497.6</v>
       </c>
       <c r="M89">
-        <v>5535.271816933802</v>
+        <v>5598.895630921547</v>
       </c>
       <c r="N89">
-        <v>-4037.671816933802</v>
+        <v>-4101.295630921548</v>
       </c>
       <c r="O89">
-        <v>-666.2158497940774</v>
+        <v>-676.7137791020555</v>
       </c>
       <c r="P89">
-        <v>-3371.455967139725</v>
+        <v>-3424.581851819492</v>
       </c>
       <c r="Q89">
-        <v>-2607.555967139725</v>
+        <v>-2660.681851819492</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2330083551705801</v>
+        <v>0.2486090514347952</v>
       </c>
       <c r="T89">
-        <v>3.649039293002845</v>
+        <v>3.953125900753083</v>
       </c>
       <c r="U89">
         <v>0.2067366166625341</v>
       </c>
       <c r="V89">
-        <v>0.04464171014042095</v>
+        <v>0.04413441797973434</v>
       </c>
       <c r="W89">
-        <v>0.1975075405460739</v>
+        <v>0.1976124164110337</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2705558190328542</v>
+        <v>0.267481321089299</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2037320126138851</v>
+        <v>0.2053413787805105</v>
       </c>
       <c r="C90">
-        <v>-19621.19811532344</v>
+        <v>-19972.35002040719</v>
       </c>
       <c r="D90">
-        <v>4302.265884676557</v>
+        <v>4258.866979592814</v>
       </c>
       <c r="E90">
-        <v>18024.764</v>
+        <v>18332.517</v>
       </c>
       <c r="F90">
-        <v>27082.264</v>
+        <v>27390.017</v>
       </c>
       <c r="G90">
         <v>3158.8</v>
@@ -8673,37 +8673,37 @@
         <v>1497.6</v>
       </c>
       <c r="M90">
-        <v>5598.895630921547</v>
+        <v>5662.519444909292</v>
       </c>
       <c r="N90">
-        <v>-4101.295630921548</v>
+        <v>-4164.919444909292</v>
       </c>
       <c r="O90">
-        <v>-676.7137791020555</v>
+        <v>-687.2117084100332</v>
       </c>
       <c r="P90">
-        <v>-3424.581851819492</v>
+        <v>-3477.707736499259</v>
       </c>
       <c r="Q90">
-        <v>-2660.681851819492</v>
+        <v>-2713.807736499259</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2486090514347952</v>
+        <v>0.2670462379288675</v>
       </c>
       <c r="T90">
-        <v>3.953125900753083</v>
+        <v>4.312500982639727</v>
       </c>
       <c r="U90">
         <v>0.2067366166625341</v>
       </c>
       <c r="V90">
-        <v>0.04413441797973434</v>
+        <v>0.04363852564288339</v>
       </c>
       <c r="W90">
-        <v>0.1976124164110337</v>
+        <v>0.1977149355149831</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.267481321089299</v>
+        <v>0.2644759129871721</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2053413787805105</v>
+        <v>0.2069507449471358</v>
       </c>
       <c r="C91">
-        <v>-19972.35002040719</v>
+        <v>-20322.63510071102</v>
       </c>
       <c r="D91">
-        <v>4258.866979592814</v>
+        <v>4216.334899288977</v>
       </c>
       <c r="E91">
-        <v>18332.517</v>
+        <v>18640.27</v>
       </c>
       <c r="F91">
-        <v>27390.017</v>
+        <v>27697.77</v>
       </c>
       <c r="G91">
         <v>3158.8</v>
@@ -8755,37 +8755,37 @@
         <v>1497.6</v>
       </c>
       <c r="M91">
-        <v>5662.519444909292</v>
+        <v>5726.143258897037</v>
       </c>
       <c r="N91">
-        <v>-4164.919444909292</v>
+        <v>-4228.543258897038</v>
       </c>
       <c r="O91">
-        <v>-687.2117084100332</v>
+        <v>-697.7096377180113</v>
       </c>
       <c r="P91">
-        <v>-3477.707736499259</v>
+        <v>-3530.833621179027</v>
       </c>
       <c r="Q91">
-        <v>-2713.807736499259</v>
+        <v>-2766.933621179026</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2670462379288675</v>
+        <v>0.2891708617217542</v>
       </c>
       <c r="T91">
-        <v>4.312500982639727</v>
+        <v>4.743751080903699</v>
       </c>
       <c r="U91">
         <v>0.2067366166625341</v>
       </c>
       <c r="V91">
-        <v>0.04363852564288339</v>
+        <v>0.04315365313574025</v>
       </c>
       <c r="W91">
-        <v>0.1977149355149831</v>
+        <v>0.1978151764166226</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2644759129871721</v>
+        <v>0.261537291731759</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2069507449471358</v>
+        <v>0.2085601111137611</v>
       </c>
       <c r="C92">
-        <v>-20322.63510071102</v>
+        <v>-20672.07906963236</v>
       </c>
       <c r="D92">
-        <v>4216.334899288977</v>
+        <v>4174.643930367645</v>
       </c>
       <c r="E92">
-        <v>18640.27</v>
+        <v>18948.023</v>
       </c>
       <c r="F92">
-        <v>27697.77</v>
+        <v>28005.523</v>
       </c>
       <c r="G92">
         <v>3158.8</v>
@@ -8837,37 +8837,37 @@
         <v>1497.6</v>
       </c>
       <c r="M92">
-        <v>5726.143258897037</v>
+        <v>5789.767072884782</v>
       </c>
       <c r="N92">
-        <v>-4228.543258897038</v>
+        <v>-4292.167072884782</v>
       </c>
       <c r="O92">
-        <v>-697.7096377180113</v>
+        <v>-708.2075670259891</v>
       </c>
       <c r="P92">
-        <v>-3530.833621179027</v>
+        <v>-3583.959505858793</v>
       </c>
       <c r="Q92">
-        <v>-2766.933621179026</v>
+        <v>-2820.059505858793</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2891708617217542</v>
+        <v>0.3162120685797269</v>
       </c>
       <c r="T92">
-        <v>4.743751080903699</v>
+        <v>5.270834534337444</v>
       </c>
       <c r="U92">
         <v>0.2067366166625341</v>
       </c>
       <c r="V92">
-        <v>0.04315365313574025</v>
+        <v>0.04267943716721562</v>
       </c>
       <c r="W92">
-        <v>0.1978151764166226</v>
+        <v>0.1979132142215227</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.261537291731759</v>
+        <v>0.2586632555588826</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2085601111137611</v>
+        <v>0.2101694772803864</v>
       </c>
       <c r="C93">
-        <v>-20672.07906963236</v>
+        <v>-21020.70663351371</v>
       </c>
       <c r="D93">
-        <v>4174.643930367645</v>
+        <v>4133.769366486289</v>
       </c>
       <c r="E93">
-        <v>18948.023</v>
+        <v>19255.776</v>
       </c>
       <c r="F93">
-        <v>28005.523</v>
+        <v>28313.276</v>
       </c>
       <c r="G93">
         <v>3158.8</v>
@@ -8919,37 +8919,37 @@
         <v>1497.6</v>
       </c>
       <c r="M93">
-        <v>5789.767072884782</v>
+        <v>5853.390886872527</v>
       </c>
       <c r="N93">
-        <v>-4292.167072884782</v>
+        <v>-4355.790886872526</v>
       </c>
       <c r="O93">
-        <v>-708.2075670259891</v>
+        <v>-718.7054963339668</v>
       </c>
       <c r="P93">
-        <v>-3583.959505858793</v>
+        <v>-3637.085390538559</v>
       </c>
       <c r="Q93">
-        <v>-2820.059505858793</v>
+        <v>-2873.185390538559</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3162120685797269</v>
+        <v>0.3500135771521929</v>
       </c>
       <c r="T93">
-        <v>5.270834534337444</v>
+        <v>5.929688851129627</v>
       </c>
       <c r="U93">
         <v>0.2067366166625341</v>
       </c>
       <c r="V93">
-        <v>0.04267943716721562</v>
+        <v>0.04221553024148503</v>
       </c>
       <c r="W93">
-        <v>0.1979132142215227</v>
+        <v>0.1980091207697946</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2586632555588826</v>
+        <v>0.2558516984332426</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2101694772803864</v>
+        <v>0.2117788434470118</v>
       </c>
       <c r="C94">
-        <v>-21020.70663351371</v>
+        <v>-21368.54154046578</v>
       </c>
       <c r="D94">
-        <v>4133.769366486289</v>
+        <v>4093.68745953422</v>
       </c>
       <c r="E94">
-        <v>19255.776</v>
+        <v>19563.529</v>
       </c>
       <c r="F94">
-        <v>28313.276</v>
+        <v>28621.029</v>
       </c>
       <c r="G94">
         <v>3158.8</v>
@@ -9001,37 +9001,37 @@
         <v>1497.6</v>
       </c>
       <c r="M94">
-        <v>5853.390886872527</v>
+        <v>5917.014700860272</v>
       </c>
       <c r="N94">
-        <v>-4355.790886872526</v>
+        <v>-4419.414700860272</v>
       </c>
       <c r="O94">
-        <v>-718.7054963339668</v>
+        <v>-729.2034256419449</v>
       </c>
       <c r="P94">
-        <v>-3637.085390538559</v>
+        <v>-3690.211275218328</v>
       </c>
       <c r="Q94">
-        <v>-2873.185390538559</v>
+        <v>-2926.311275218327</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3500135771521929</v>
+        <v>0.3934726596025062</v>
       </c>
       <c r="T94">
-        <v>5.929688851129627</v>
+        <v>6.77678725843386</v>
       </c>
       <c r="U94">
         <v>0.2067366166625341</v>
       </c>
       <c r="V94">
-        <v>0.04221553024148503</v>
+        <v>0.04176159980878089</v>
       </c>
       <c r="W94">
-        <v>0.1980091207697946</v>
+        <v>0.198102964811652</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2558516984332426</v>
+        <v>0.2531006049017023</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2117788434470118</v>
+        <v>0.2133882096136371</v>
       </c>
       <c r="C95">
-        <v>-21368.54154046578</v>
+        <v>-21715.60662637744</v>
       </c>
       <c r="D95">
-        <v>4093.68745953422</v>
+        <v>4054.375373622557</v>
       </c>
       <c r="E95">
-        <v>19563.529</v>
+        <v>19871.282</v>
       </c>
       <c r="F95">
-        <v>28621.029</v>
+        <v>28928.782</v>
       </c>
       <c r="G95">
         <v>3158.8</v>
@@ -9083,37 +9083,37 @@
         <v>1497.6</v>
       </c>
       <c r="M95">
-        <v>5917.014700860272</v>
+        <v>5980.638514848017</v>
       </c>
       <c r="N95">
-        <v>-4419.414700860272</v>
+        <v>-4483.038514848016</v>
       </c>
       <c r="O95">
-        <v>-729.2034256419449</v>
+        <v>-739.7013549499227</v>
       </c>
       <c r="P95">
-        <v>-3690.211275218328</v>
+        <v>-3743.337159898094</v>
       </c>
       <c r="Q95">
-        <v>-2926.311275218327</v>
+        <v>-2979.437159898094</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3934726596025062</v>
+        <v>0.4514181028695907</v>
       </c>
       <c r="T95">
-        <v>6.77678725843386</v>
+        <v>7.906251801506173</v>
       </c>
       <c r="U95">
         <v>0.2067366166625341</v>
       </c>
       <c r="V95">
-        <v>0.04176159980878089</v>
+        <v>0.0413173274703896</v>
       </c>
       <c r="W95">
-        <v>0.198102964811652</v>
+        <v>0.1981948121717678</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2531006049017023</v>
+        <v>0.2504080452750885</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2133882096136371</v>
+        <v>0.2149975757802625</v>
       </c>
       <c r="C96">
-        <v>-21715.60662637744</v>
+        <v>-22061.9238582999</v>
       </c>
       <c r="D96">
-        <v>4054.375373622557</v>
+        <v>4015.811141700101</v>
       </c>
       <c r="E96">
-        <v>19871.282</v>
+        <v>20179.035</v>
       </c>
       <c r="F96">
-        <v>28928.782</v>
+        <v>29236.535</v>
       </c>
       <c r="G96">
         <v>3158.8</v>
@@ -9165,37 +9165,37 @@
         <v>1497.6</v>
       </c>
       <c r="M96">
-        <v>5980.638514848017</v>
+        <v>6044.262328835761</v>
       </c>
       <c r="N96">
-        <v>-4483.038514848016</v>
+        <v>-4546.66232883576</v>
       </c>
       <c r="O96">
-        <v>-739.7013549499227</v>
+        <v>-750.1992842579006</v>
       </c>
       <c r="P96">
-        <v>-3743.337159898094</v>
+        <v>-3796.46304457786</v>
       </c>
       <c r="Q96">
-        <v>-2979.437159898094</v>
+        <v>-3032.56304457786</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4514181028695907</v>
+        <v>0.532541723443509</v>
       </c>
       <c r="T96">
-        <v>7.906251801506173</v>
+        <v>9.487502161807411</v>
       </c>
       <c r="U96">
         <v>0.2067366166625341</v>
       </c>
       <c r="V96">
-        <v>0.0413173274703896</v>
+        <v>0.04088240823385918</v>
       </c>
       <c r="W96">
-        <v>0.1981948121717678</v>
+        <v>0.1982847259032495</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2504080452750885</v>
+        <v>0.2477721711142982</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2149975757802625</v>
+        <v>0.2166069419468878</v>
       </c>
       <c r="C97">
-        <v>-22061.9238582999</v>
+        <v>-22407.51437537821</v>
       </c>
       <c r="D97">
-        <v>4015.811141700101</v>
+        <v>3977.97362462179</v>
       </c>
       <c r="E97">
-        <v>20179.035</v>
+        <v>20486.788</v>
       </c>
       <c r="F97">
-        <v>29236.535</v>
+        <v>29544.288</v>
       </c>
       <c r="G97">
         <v>3158.8</v>
@@ -9247,37 +9247,37 @@
         <v>1497.6</v>
       </c>
       <c r="M97">
-        <v>6044.262328835761</v>
+        <v>6107.886142823506</v>
       </c>
       <c r="N97">
-        <v>-4546.66232883576</v>
+        <v>-4610.286142823506</v>
       </c>
       <c r="O97">
-        <v>-750.1992842579006</v>
+        <v>-760.6972135658787</v>
       </c>
       <c r="P97">
-        <v>-3796.46304457786</v>
+        <v>-3849.588929257628</v>
       </c>
       <c r="Q97">
-        <v>-3032.56304457786</v>
+        <v>-3085.688929257627</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.532541723443509</v>
+        <v>0.6542271543043866</v>
       </c>
       <c r="T97">
-        <v>9.487502161807411</v>
+        <v>11.85937770225927</v>
       </c>
       <c r="U97">
         <v>0.2067366166625341</v>
       </c>
       <c r="V97">
-        <v>0.04088240823385918</v>
+        <v>0.04045654981475648</v>
       </c>
       <c r="W97">
-        <v>0.1982847259032495</v>
+        <v>0.1983727664319921</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2477721711142982</v>
+        <v>0.245191210998524</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2166069419468878</v>
+        <v>0.2182163081135132</v>
       </c>
       <c r="C98">
-        <v>-22407.5143753782</v>
+        <v>-22752.39852749045</v>
       </c>
       <c r="D98">
-        <v>3977.973624621796</v>
+        <v>3940.842472509548</v>
       </c>
       <c r="E98">
-        <v>20486.788</v>
+        <v>20794.541</v>
       </c>
       <c r="F98">
-        <v>29544.288</v>
+        <v>29852.041</v>
       </c>
       <c r="G98">
         <v>3158.8</v>
@@ -9329,37 +9329,37 @@
         <v>1497.6</v>
       </c>
       <c r="M98">
-        <v>6107.886142823506</v>
+        <v>6171.50995681125</v>
       </c>
       <c r="N98">
-        <v>-4610.286142823506</v>
+        <v>-4673.909956811251</v>
       </c>
       <c r="O98">
-        <v>-760.6972135658787</v>
+        <v>-771.1951428738564</v>
       </c>
       <c r="P98">
-        <v>-3849.588929257628</v>
+        <v>-3902.714813937394</v>
       </c>
       <c r="Q98">
-        <v>-3085.688929257627</v>
+        <v>-3138.814813937394</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6542271543043849</v>
+        <v>0.8570362057391799</v>
       </c>
       <c r="T98">
-        <v>11.85937770225924</v>
+        <v>15.81250360301232</v>
       </c>
       <c r="U98">
         <v>0.2067366166625341</v>
       </c>
       <c r="V98">
-        <v>0.04045654981475648</v>
+        <v>0.04003947198161467</v>
       </c>
       <c r="W98">
-        <v>0.1983727664319921</v>
+        <v>0.1984589916921008</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.245191210998524</v>
+        <v>0.2426634665552403</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2182163081135132</v>
+        <v>0.2198256742801385</v>
       </c>
       <c r="C99">
-        <v>-22752.39852749045</v>
+        <v>-23096.59591174289</v>
       </c>
       <c r="D99">
-        <v>3940.842472509548</v>
+        <v>3904.398088257105</v>
       </c>
       <c r="E99">
-        <v>20794.541</v>
+        <v>21102.294</v>
       </c>
       <c r="F99">
-        <v>29852.041</v>
+        <v>30159.794</v>
       </c>
       <c r="G99">
         <v>3158.8</v>
@@ -9411,37 +9411,37 @@
         <v>1497.6</v>
       </c>
       <c r="M99">
-        <v>6171.50995681125</v>
+        <v>6235.133770798995</v>
       </c>
       <c r="N99">
-        <v>-4673.909956811251</v>
+        <v>-4737.533770798995</v>
       </c>
       <c r="O99">
-        <v>-771.1951428738564</v>
+        <v>-781.6930721818342</v>
       </c>
       <c r="P99">
-        <v>-3902.714813937394</v>
+        <v>-3955.84069861716</v>
       </c>
       <c r="Q99">
-        <v>-3138.814813937394</v>
+        <v>-3191.94069861716</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.8570362057391799</v>
+        <v>1.26265430860877</v>
       </c>
       <c r="T99">
-        <v>15.81250360301232</v>
+        <v>23.71875540451847</v>
       </c>
       <c r="U99">
         <v>0.2067366166625341</v>
       </c>
       <c r="V99">
-        <v>0.04003947198161467</v>
+        <v>0.03963090594098594</v>
       </c>
       <c r="W99">
-        <v>0.1984589916921008</v>
+        <v>0.1985434572530235</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2426634665552403</v>
+        <v>0.2401873087332482</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2198256742801385</v>
+        <v>0.2214350404467638</v>
       </c>
       <c r="C100">
-        <v>-23096.59591174289</v>
+        <v>-23440.12540695874</v>
       </c>
       <c r="D100">
-        <v>3904.398088257105</v>
+        <v>3868.621593041262</v>
       </c>
       <c r="E100">
-        <v>21102.294</v>
+        <v>21410.047</v>
       </c>
       <c r="F100">
-        <v>30159.794</v>
+        <v>30467.547</v>
       </c>
       <c r="G100">
         <v>3158.8</v>
@@ -9493,37 +9493,37 @@
         <v>1497.6</v>
       </c>
       <c r="M100">
-        <v>6235.133770798995</v>
+        <v>6298.75758478674</v>
       </c>
       <c r="N100">
-        <v>-4737.533770798995</v>
+        <v>-4801.157584786741</v>
       </c>
       <c r="O100">
-        <v>-781.6930721818342</v>
+        <v>-792.1910014898123</v>
       </c>
       <c r="P100">
-        <v>-3955.84069861716</v>
+        <v>-4008.966583296929</v>
       </c>
       <c r="Q100">
-        <v>-3191.94069861716</v>
+        <v>-3245.066583296928</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.26265430860877</v>
+        <v>2.479508617217539</v>
       </c>
       <c r="T100">
-        <v>23.71875540451847</v>
+        <v>47.43751080903694</v>
       </c>
       <c r="U100">
         <v>0.2067366166625341</v>
       </c>
       <c r="V100">
-        <v>0.03963090594098594</v>
+        <v>0.03923059375976386</v>
       </c>
       <c r="W100">
-        <v>0.1985434572530235</v>
+        <v>0.1986262164389782</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2401873087332482</v>
+        <v>0.237761174301599</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2214350404467638</v>
-      </c>
-      <c r="C101">
-        <v>-23440.12540695874</v>
-      </c>
-      <c r="D101">
-        <v>3868.621593041262</v>
-      </c>
-      <c r="E101">
-        <v>21410.047</v>
-      </c>
-      <c r="F101">
-        <v>30467.547</v>
-      </c>
-      <c r="G101">
-        <v>3158.8</v>
-      </c>
-      <c r="H101">
-        <v>21717.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2261.5</v>
-      </c>
-      <c r="K101">
-        <v>763.9</v>
-      </c>
-      <c r="L101">
-        <v>1497.6</v>
-      </c>
-      <c r="M101">
-        <v>6298.75758478674</v>
-      </c>
-      <c r="N101">
-        <v>-4801.157584786741</v>
-      </c>
-      <c r="O101">
-        <v>-792.1910014898123</v>
-      </c>
-      <c r="P101">
-        <v>-4008.966583296929</v>
-      </c>
-      <c r="Q101">
-        <v>-3245.066583296928</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.479508617217539</v>
-      </c>
-      <c r="T101">
-        <v>47.43751080903694</v>
-      </c>
-      <c r="U101">
-        <v>0.2067366166625341</v>
-      </c>
-      <c r="V101">
-        <v>0.03923059375976386</v>
-      </c>
-      <c r="W101">
-        <v>0.1986262164389782</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.237761174301599</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
